--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -46,7 +46,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -55,23 +55,26 @@
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="29" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="10" max="10" width="60" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="29" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
     <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17" customWidth="1"/>
-    <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="17" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="10" customWidth="1"/>
+    <col min="25" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -117,75 +120,90 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mouser Link</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Basic</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">RoHS</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Country of Origin</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Dist P/N</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Unit Price</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Ext Price</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Stock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Lifecycle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Min Qty</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Final Qty</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Order Unit Cost</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Cost @ Qty</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tariff %</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tax/Tariff</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Total Cost</t>
         </is>
@@ -222,7 +240,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -232,51 +250,72 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116009</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M2"/>
-      <c r="N2">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-560112116009</t>
+        </is>
+      </c>
+      <c r="P2">
         <v>0.11</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>0.44</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>12356</v>
       </c>
-      <c r="Q2"/>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
         <v>12</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>0.102</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>1.224</v>
       </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
         <v>1.224</v>
       </c>
     </row>
@@ -311,7 +350,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -321,48 +360,69 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B104KO5NNNC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J3"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M3"/>
-      <c r="N3">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05B104KO5NNNC</t>
+        </is>
+      </c>
+      <c r="P3">
         <v>0.1</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>4290139</v>
       </c>
-      <c r="Q3"/>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
         <v>180</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>0.01</v>
-      </c>
-      <c r="U3">
-        <v>1.8</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
       </c>
       <c r="W3">
         <v>1.8</v>
+      </c>
+      <c r="X3">
+        <v>8</v>
+      </c>
+      <c r="Y3">
+        <v>0.144</v>
+      </c>
+      <c r="Z3">
+        <v>1.944</v>
       </c>
     </row>
     <row r="4">
@@ -396,7 +456,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -406,51 +466,72 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-2102ELF</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M4"/>
-      <c r="N4">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-2102ELF</t>
+        </is>
+      </c>
+      <c r="P4">
         <v>0.1</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>0.1</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>137114</v>
       </c>
-      <c r="Q4"/>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
         <v>10</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>0.012</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>0.12</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
         <v>0.12</v>
       </c>
     </row>
@@ -485,7 +566,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -495,52 +576,73 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04023R32FKED</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M5"/>
-      <c r="N5">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0402-3.32-E3</t>
+        </is>
+      </c>
+      <c r="P5">
         <v>0.1</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>0.1</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>91174</v>
       </c>
-      <c r="Q5"/>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
         <v>10</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>0.025</v>
-      </c>
-      <c r="U5">
-        <v>0.25</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
       </c>
       <c r="W5">
         <v>0.25</v>
+      </c>
+      <c r="X5">
+        <v>10</v>
+      </c>
+      <c r="Y5">
+        <v>0.025</v>
+      </c>
+      <c r="Z5">
+        <v>0.275</v>
       </c>
     </row>
     <row r="6">
@@ -584,48 +686,69 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QTH-060-01-L-D-A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
         </is>
       </c>
-      <c r="J6"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malaysia</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M6"/>
-      <c r="N6">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200-QTH06001LDA</t>
+        </is>
+      </c>
+      <c r="P6">
         <v>5.75</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>5.75</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>5176</v>
       </c>
-      <c r="Q6"/>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
         <v>3</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>5.75</v>
-      </c>
-      <c r="U6">
-        <v>17.25</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
       </c>
       <c r="W6">
         <v>17.25</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>1.38</v>
+      </c>
+      <c r="Z6">
+        <v>18.63</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +782,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">VSSOP-8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -669,48 +792,69 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G74DCUR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Flip Flops</t>
         </is>
       </c>
-      <c r="J7"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M7"/>
-      <c r="N7">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-SN74LVC1G74DCUR</t>
+        </is>
+      </c>
+      <c r="P7">
         <v>0.6</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>0.6</v>
       </c>
-      <c r="P7">
-        <v>52601</v>
-      </c>
-      <c r="Q7"/>
       <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
+        <v>52599</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
         <v>3</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>0.6</v>
-      </c>
-      <c r="U7">
-        <v>1.8</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
       </c>
       <c r="W7">
         <v>1.8</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>0.144</v>
+      </c>
+      <c r="Z7">
+        <v>1.944</v>
       </c>
     </row>
     <row r="8">
@@ -744,7 +888,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT23-6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -754,47 +898,68 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22917LDBVR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Load Switch SOT23-6</t>
         </is>
       </c>
-      <c r="J8"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M8"/>
-      <c r="N8">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS22917LDBVR</t>
+        </is>
+      </c>
+      <c r="P8">
         <v>0.52</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>3.64</v>
       </c>
-      <c r="P8">
-        <v>194</v>
-      </c>
-      <c r="Q8"/>
       <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
+        <v>171</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
         <v>21</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>0.367</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>7.707</v>
       </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
         <v>7.707</v>
       </c>
     </row>
@@ -829,7 +994,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -839,48 +1004,69 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/2N7002</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t xml:space="preserve">MOSFETs</t>
         </is>
       </c>
-      <c r="J9"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M9"/>
-      <c r="N9">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">512-2N7002</t>
+        </is>
+      </c>
+      <c r="P9">
         <v>1.09</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>1.09</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>526042</v>
       </c>
-      <c r="Q9"/>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
         <v>3</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>1.09</v>
-      </c>
-      <c r="U9">
-        <v>3.27</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
       </c>
       <c r="W9">
         <v>3.27</v>
+      </c>
+      <c r="X9">
+        <v>7.98</v>
+      </c>
+      <c r="Y9">
+        <v>0.2609</v>
+      </c>
+      <c r="Z9">
+        <v>3.5309</v>
       </c>
     </row>
     <row r="10">
@@ -914,7 +1100,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -924,51 +1110,72 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/TE-Connectivity-Holsworthy/CRG0603F1M0-10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M10"/>
-      <c r="N10">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279-CRG0603F1M0/10</t>
+        </is>
+      </c>
+      <c r="P10">
         <v>0.24</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>0.48</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>18238</v>
       </c>
-      <c r="Q10"/>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
         <v>10</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>0.06</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>0.6</v>
       </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
         <v>0.6</v>
       </c>
     </row>
@@ -1003,7 +1210,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">1206 (3216 metric)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1013,48 +1220,69 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A106KBHNNNE</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J11"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M11"/>
-      <c r="N11">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL31A106KBHNNNE</t>
+        </is>
+      </c>
+      <c r="P11">
         <v>0.36</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>1.8</v>
       </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11"/>
       <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>15</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>0.155</v>
-      </c>
-      <c r="U11">
-        <v>2.325</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
       </c>
       <c r="W11">
         <v>2.325</v>
+      </c>
+      <c r="X11">
+        <v>8.06</v>
+      </c>
+      <c r="Y11">
+        <v>0.1874</v>
+      </c>
+      <c r="Z11">
+        <v>2.5124</v>
       </c>
     </row>
     <row r="12">
@@ -1088,7 +1316,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">VQFN-16</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1098,48 +1326,69 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/BQ24074RGTT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Battery Management</t>
         </is>
       </c>
-      <c r="J12"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M12"/>
-      <c r="N12">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-BQ24074RGTT</t>
+        </is>
+      </c>
+      <c r="P12">
         <v>3.19</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>3.19</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>1351</v>
       </c>
-      <c r="Q12"/>
-      <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
         <v>3</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>3.19</v>
-      </c>
-      <c r="U12">
-        <v>9.57</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
       </c>
       <c r="W12">
         <v>9.57</v>
+      </c>
+      <c r="X12">
+        <v>37.93</v>
+      </c>
+      <c r="Y12">
+        <v>3.6299</v>
+      </c>
+      <c r="Z12">
+        <v>13.1999</v>
       </c>
     </row>
     <row r="13">
@@ -1173,7 +1422,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1183,51 +1432,72 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116004</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M13"/>
-      <c r="N13">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-560112116004</t>
+        </is>
+      </c>
+      <c r="P13">
         <v>0.11</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>0.88</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>9744</v>
       </c>
-      <c r="Q13"/>
-      <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
         <v>24</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>0.102</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>2.448</v>
       </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
         <v>2.448</v>
       </c>
     </row>
@@ -1262,7 +1532,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1272,48 +1542,69 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A225KO8NNNC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J14"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M14"/>
-      <c r="N14">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL10A225KO8NNNC</t>
+        </is>
+      </c>
+      <c r="P14">
         <v>0.1</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>0.4</v>
       </c>
-      <c r="P14">
-        <v>220182</v>
-      </c>
-      <c r="Q14"/>
       <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14">
+        <v>220172</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
         <v>12</v>
       </c>
-      <c r="T14">
+      <c r="V14">
         <v>0.033</v>
-      </c>
-      <c r="U14">
-        <v>0.396</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
       </c>
       <c r="W14">
         <v>0.396</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>0.0317</v>
+      </c>
+      <c r="Z14">
+        <v>0.4277</v>
       </c>
     </row>
     <row r="15">
@@ -1347,7 +1638,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1357,51 +1648,72 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1022V</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M15"/>
-      <c r="N15">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667-ERJ-H3EF1022V</t>
+        </is>
+      </c>
+      <c r="P15">
         <v>0.28</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>0.28</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>9828</v>
       </c>
-      <c r="Q15"/>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
         <v>3</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>0.28</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>0.84</v>
       </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
         <v>0.84</v>
       </c>
     </row>
@@ -1436,7 +1748,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">TSSOP-16</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1446,47 +1758,68 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC138AQPWREP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Encoders, Decoders, Multiplexers &amp; Demultiplexers</t>
         </is>
       </c>
-      <c r="J16"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malaysia</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M16"/>
-      <c r="N16">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-N74LVC138AQPWREP</t>
+        </is>
+      </c>
+      <c r="P16">
         <v>2.73</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>2.73</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>1995</v>
       </c>
-      <c r="Q16"/>
-      <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
         <v>3</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>2.73</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>8.19</v>
       </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
         <v>8.19</v>
       </c>
     </row>
@@ -1531,47 +1864,68 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300811121</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Headers &amp; Wire Housings</t>
         </is>
       </c>
-      <c r="J17"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M17"/>
-      <c r="N17">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-61300811121</t>
+        </is>
+      </c>
+      <c r="P17">
         <v>0.39</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>3.12</v>
       </c>
-      <c r="P17">
-        <v>21535</v>
-      </c>
-      <c r="Q17"/>
       <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17">
+        <v>21510</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
         <v>25</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>0.28</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>7</v>
       </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
         <v>7</v>
       </c>
     </row>
@@ -1606,7 +1960,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1616,48 +1970,69 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B102KB5NNNC</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J18"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M18"/>
-      <c r="N18">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05B102KB5NNNC</t>
+        </is>
+      </c>
+      <c r="P18">
         <v>0.1</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>0.2</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>600321</v>
       </c>
-      <c r="Q18"/>
-      <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
         <v>10</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>0.015</v>
-      </c>
-      <c r="U18">
-        <v>0.15</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
       </c>
       <c r="W18">
         <v>0.15</v>
+      </c>
+      <c r="X18">
+        <v>8</v>
+      </c>
+      <c r="Y18">
+        <v>0.012</v>
+      </c>
+      <c r="Z18">
+        <v>0.162</v>
       </c>
     </row>
     <row r="19">
@@ -1691,7 +2066,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1701,51 +2076,72 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603249KFKEC</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M19"/>
-      <c r="N19">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0603249KFKEC</t>
+        </is>
+      </c>
+      <c r="P19">
         <v>0.25</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>0.25</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>53712</v>
       </c>
-      <c r="Q19"/>
-      <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
         <v>10</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>0.063</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>0.63</v>
       </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
         <v>0.63</v>
       </c>
     </row>
@@ -1790,51 +2186,72 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74438357010</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Wurth 74438357010</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Korea, Republic of</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M20"/>
-      <c r="N20">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-74438357010</t>
+        </is>
+      </c>
+      <c r="P20">
         <v>1.68</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>1.68</v>
       </c>
-      <c r="P20">
-        <v>11706</v>
-      </c>
-      <c r="Q20"/>
       <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20">
+        <v>11702</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
         <v>3</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>1.68</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>5.04</v>
       </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
         <v>5.04</v>
       </c>
     </row>
@@ -1869,7 +2286,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1879,51 +2296,72 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X4703FTL</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M21"/>
-      <c r="N21">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791-MR06X4703FTL</t>
+        </is>
+      </c>
+      <c r="P21">
         <v>0.13</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>0.13</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>70598</v>
       </c>
-      <c r="Q21"/>
-      <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
         <v>10</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>0.033</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>0.33</v>
       </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
         <v>0.33</v>
       </c>
     </row>
@@ -1958,7 +2396,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1968,51 +2406,72 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-S03F1002V</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M22"/>
-      <c r="N22">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667-ERJ-S03F1002V</t>
+        </is>
+      </c>
+      <c r="P22">
         <v>0.23</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>7.82</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>58284</v>
       </c>
-      <c r="Q22"/>
-      <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22">
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
         <v>102</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>0.072</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>7.344</v>
       </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
         <v>7.344</v>
       </c>
     </row>
@@ -2047,7 +2506,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2057,47 +2516,68 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22918TDBVRQ1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
         </is>
       </c>
-      <c r="J23"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M23"/>
-      <c r="N23">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS22918TDBVRQ1</t>
+        </is>
+      </c>
+      <c r="P23">
         <v>0.76</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>1.52</v>
       </c>
-      <c r="P23">
-        <v>10229</v>
-      </c>
-      <c r="Q23"/>
       <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23">
+        <v>10139</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
         <v>6</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>0.76</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>4.56</v>
       </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
         <v>4.56</v>
       </c>
     </row>
@@ -2132,7 +2612,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-353-5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2142,48 +2622,69 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Diodes-Incorporated/74AHC1G32QSE-7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single OR Gate, Low-Voltage CMOS</t>
         </is>
       </c>
-      <c r="J24"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M24"/>
-      <c r="N24">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621-74AHC1G32QSE-7</t>
+        </is>
+      </c>
+      <c r="P24">
         <v>0.14</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>0.56</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>7036</v>
       </c>
-      <c r="Q24"/>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
         <v>12</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>0.092</v>
-      </c>
-      <c r="U24">
-        <v>1.104</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
       </c>
       <c r="W24">
         <v>1.104</v>
+      </c>
+      <c r="X24">
+        <v>37.86</v>
+      </c>
+      <c r="Y24">
+        <v>0.418</v>
+      </c>
+      <c r="Z24">
+        <v>1.522</v>
       </c>
     </row>
     <row r="25">
@@ -2217,7 +2718,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2227,51 +2728,72 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-P03F1101V</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M25"/>
-      <c r="N25">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667-ERJ-P03F1101V</t>
+        </is>
+      </c>
+      <c r="P25">
         <v>0.31</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>0.31</v>
       </c>
-      <c r="P25">
+      <c r="R25">
         <v>5616</v>
       </c>
-      <c r="Q25"/>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
         <v>3</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>0.31</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>0.93</v>
       </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
         <v>0.93</v>
       </c>
     </row>
@@ -2306,7 +2828,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2316,51 +2838,72 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4422ELF</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M26"/>
-      <c r="N26">
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-4422ELF</t>
+        </is>
+      </c>
+      <c r="P26">
         <v>0.1</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>0.1</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>331735</v>
       </c>
-      <c r="Q26"/>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
         <v>10</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>0.016</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>0.16</v>
       </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
         <v>0.16</v>
       </c>
     </row>
@@ -2405,52 +2948,73 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74439346068</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Power Inductors - SMD</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M27"/>
-      <c r="N27">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-74439346068</t>
+        </is>
+      </c>
+      <c r="P27">
         <v>4.05</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>4.05</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>6579</v>
       </c>
-      <c r="Q27"/>
-      <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="S27">
+      <c r="S27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
         <v>3</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>4.05</v>
-      </c>
-      <c r="U27">
-        <v>12.15</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
       </c>
       <c r="W27">
         <v>12.15</v>
+      </c>
+      <c r="X27">
+        <v>35.06</v>
+      </c>
+      <c r="Y27">
+        <v>4.2598</v>
+      </c>
+      <c r="Z27">
+        <v>16.4098</v>
       </c>
     </row>
     <row r="28">
@@ -2484,7 +3048,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2494,51 +3058,72 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X47R0FTL</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M28"/>
-      <c r="N28">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791-MR06X47R0FTL</t>
+        </is>
+      </c>
+      <c r="P28">
         <v>0.13</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>0.13</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>49137</v>
       </c>
-      <c r="Q28"/>
-      <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="S28">
+      <c r="S28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
         <v>10</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>0.033</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>0.33</v>
       </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
         <v>0.33</v>
       </c>
     </row>
@@ -2573,7 +3158,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-563-6</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2583,47 +3168,68 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS61023DRLT</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Boost converter 6-SOT-5X3</t>
         </is>
       </c>
-      <c r="J29"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M29"/>
-      <c r="N29">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS61023DRLT</t>
+        </is>
+      </c>
+      <c r="P29">
         <v>1.43</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>1.43</v>
       </c>
-      <c r="P29">
+      <c r="R29">
         <v>47115</v>
       </c>
-      <c r="Q29"/>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
+      <c r="S29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
         <v>3</v>
       </c>
-      <c r="T29">
+      <c r="V29">
         <v>1.43</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>4.29</v>
       </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
         <v>4.29</v>
       </c>
     </row>
@@ -2658,7 +3264,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2668,51 +3274,72 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3162ELF</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M30"/>
-      <c r="N30">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-3162ELF</t>
+        </is>
+      </c>
+      <c r="P30">
         <v>0.1</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>0.1</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>828379</v>
       </c>
-      <c r="Q30"/>
-      <c r="R30">
-        <v>1</v>
-      </c>
-      <c r="S30">
+      <c r="S30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30">
         <v>10</v>
       </c>
-      <c r="T30">
+      <c r="V30">
         <v>0.012</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>0.12</v>
       </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
         <v>0.12</v>
       </c>
     </row>
@@ -2747,7 +3374,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">3.2 mm x 2.5 mm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2757,48 +3384,69 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ABRACON/ABM8-25.000MHZ-B2-T</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Crystals</t>
         </is>
       </c>
-      <c r="J31"/>
-      <c r="K31" t="inlineStr">
+      <c r="K31"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M31"/>
-      <c r="N31">
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815-ABM8-25-B2-T</t>
+        </is>
+      </c>
+      <c r="P31">
         <v>0.5</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>0.5</v>
       </c>
-      <c r="P31">
-        <v>14301</v>
-      </c>
-      <c r="Q31"/>
       <c r="R31">
-        <v>1</v>
-      </c>
-      <c r="S31">
+        <v>14291</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
         <v>3</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>0.5</v>
-      </c>
-      <c r="U31">
-        <v>1.5</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
       </c>
       <c r="W31">
         <v>1.5</v>
+      </c>
+      <c r="X31">
+        <v>30</v>
+      </c>
+      <c r="Y31">
+        <v>0.45</v>
+      </c>
+      <c r="Z31">
+        <v>1.95</v>
       </c>
     </row>
     <row r="32">
@@ -2842,48 +3490,69 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/E-Switch/EG1218</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Slide Switches</t>
         </is>
       </c>
-      <c r="J32"/>
-      <c r="K32" t="inlineStr">
+      <c r="K32"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M32"/>
-      <c r="N32">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612-EG1218</t>
+        </is>
+      </c>
+      <c r="P32">
         <v>0.71</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>0.71</v>
       </c>
-      <c r="P32">
+      <c r="R32">
         <v>12328</v>
       </c>
-      <c r="Q32"/>
-      <c r="R32">
-        <v>1</v>
-      </c>
-      <c r="S32">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
         <v>3</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>0.71</v>
-      </c>
-      <c r="U32">
-        <v>2.13</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
       </c>
       <c r="W32">
         <v>2.13</v>
+      </c>
+      <c r="X32">
+        <v>30</v>
+      </c>
+      <c r="Y32">
+        <v>0.639</v>
+      </c>
+      <c r="Z32">
+        <v>2.769</v>
       </c>
     </row>
     <row r="33">
@@ -2918,46 +3587,67 @@
       <c r="G33"/>
       <c r="H33" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/167/1/Scotch_300_Series_Barricade_Tapes_Data_Sheet_78_8125_9670_4_F.pdf</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t xml:space="preserve">https://www.adafruit.com/product/358</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">358</t>
         </is>
       </c>
-      <c r="J33"/>
       <c r="K33"/>
       <c r="L33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Details</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M33"/>
-      <c r="N33">
+      <c r="O33"/>
+      <c r="P33">
         <v>19.95</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>19.95</v>
       </c>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33">
-        <v>1</v>
-      </c>
-      <c r="S33">
+      <c r="R33"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33">
         <v>3</v>
       </c>
-      <c r="T33">
+      <c r="V33">
         <v>19.95</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>59.85</v>
       </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
         <v>59.85</v>
       </c>
     </row>
@@ -2992,7 +3682,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3002,51 +3692,72 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1872V</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M34"/>
-      <c r="N34">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667-ERJ-H3EF1872V</t>
+        </is>
+      </c>
+      <c r="P34">
         <v>0.28</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>0.28</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>9748</v>
       </c>
-      <c r="Q34"/>
-      <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="S34">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34">
         <v>3</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>0.28</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>0.84</v>
       </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
         <v>0.84</v>
       </c>
     </row>
@@ -3081,7 +3792,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3091,52 +3802,73 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04024K12FKED</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M35"/>
-      <c r="N35">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0402-4.12K-E3</t>
+        </is>
+      </c>
+      <c r="P35">
         <v>0.15</v>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>0.15</v>
       </c>
-      <c r="P35">
+      <c r="R35">
         <v>10238</v>
       </c>
-      <c r="Q35"/>
-      <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="S35">
+      <c r="S35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35">
         <v>3</v>
       </c>
-      <c r="T35">
+      <c r="V35">
         <v>0.15</v>
-      </c>
-      <c r="U35">
-        <v>0.45</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
       </c>
       <c r="W35">
         <v>0.45</v>
+      </c>
+      <c r="X35">
+        <v>10</v>
+      </c>
+      <c r="Y35">
+        <v>0.045</v>
+      </c>
+      <c r="Z35">
+        <v>0.495</v>
       </c>
     </row>
     <row r="36">
@@ -3170,7 +3902,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3180,51 +3912,72 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4642ELF</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M36"/>
-      <c r="N36">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-4642ELF</t>
+        </is>
+      </c>
+      <c r="P36">
         <v>0.1</v>
       </c>
-      <c r="O36">
+      <c r="Q36">
         <v>0.1</v>
       </c>
-      <c r="P36">
+      <c r="R36">
         <v>85609</v>
       </c>
-      <c r="Q36"/>
-      <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="S36">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+      <c r="U36">
         <v>10</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>0.016</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>0.16</v>
       </c>
-      <c r="V36">
-        <v>0</v>
-      </c>
-      <c r="W36">
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
         <v>0.16</v>
       </c>
     </row>
@@ -3259,7 +4012,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3269,51 +4022,72 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-1181ELF</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M37"/>
-      <c r="N37">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-1181ELF</t>
+        </is>
+      </c>
+      <c r="P37">
         <v>0.1</v>
       </c>
-      <c r="O37">
+      <c r="Q37">
         <v>0.1</v>
       </c>
-      <c r="P37">
+      <c r="R37">
         <v>51357</v>
       </c>
-      <c r="Q37"/>
-      <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="S37">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="U37">
         <v>10</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>0.016</v>
       </c>
-      <c r="U37">
+      <c r="W37">
         <v>0.16</v>
       </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
         <v>0.16</v>
       </c>
     </row>
@@ -3348,7 +4122,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3358,47 +4132,68 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS3700DDCR</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Analog Comparators</t>
         </is>
       </c>
-      <c r="J38"/>
-      <c r="K38" t="inlineStr">
+      <c r="K38"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M38"/>
-      <c r="N38">
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS3700DDCR</t>
+        </is>
+      </c>
+      <c r="P38">
         <v>2.52</v>
       </c>
-      <c r="O38">
+      <c r="Q38">
         <v>2.52</v>
       </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38"/>
       <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
         <v>3</v>
       </c>
-      <c r="T38">
+      <c r="V38">
         <v>2.52</v>
       </c>
-      <c r="U38">
+      <c r="W38">
         <v>7.56</v>
       </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
         <v>7.56</v>
       </c>
     </row>
@@ -3433,7 +4228,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3443,48 +4238,69 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A106KOQNNNE</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J39"/>
-      <c r="K39" t="inlineStr">
+      <c r="K39"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M39"/>
-      <c r="N39">
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL21A106KOQNNNE</t>
+        </is>
+      </c>
+      <c r="P39">
         <v>0.11</v>
       </c>
-      <c r="O39">
+      <c r="Q39">
         <v>0.22</v>
       </c>
-      <c r="P39">
+      <c r="R39">
         <v>189</v>
       </c>
-      <c r="Q39"/>
-      <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39">
+      <c r="S39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39">
         <v>10</v>
       </c>
-      <c r="T39">
+      <c r="V39">
         <v>0.042</v>
-      </c>
-      <c r="U39">
-        <v>0.42</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
       </c>
       <c r="W39">
         <v>0.42</v>
+      </c>
+      <c r="X39">
+        <v>8.18</v>
+      </c>
+      <c r="Y39">
+        <v>0.0344</v>
+      </c>
+      <c r="Z39">
+        <v>0.4544</v>
       </c>
     </row>
     <row r="40">
@@ -3518,7 +4334,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,48 +4344,69 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TS5A3166DBVR</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t xml:space="preserve">SPST Analog Switch SOT-23-5</t>
         </is>
       </c>
-      <c r="J40"/>
-      <c r="K40" t="inlineStr">
+      <c r="K40"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M40"/>
-      <c r="N40">
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TS5A3166DBVR</t>
+        </is>
+      </c>
+      <c r="P40">
         <v>0.43</v>
       </c>
-      <c r="O40">
+      <c r="Q40">
         <v>1.72</v>
       </c>
-      <c r="P40">
-        <v>6529</v>
-      </c>
-      <c r="Q40"/>
       <c r="R40">
-        <v>1</v>
-      </c>
-      <c r="S40">
+        <v>6188</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40">
         <v>12</v>
       </c>
-      <c r="T40">
+      <c r="V40">
         <v>0.302</v>
-      </c>
-      <c r="U40">
-        <v>3.624</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
       </c>
       <c r="W40">
         <v>3.624</v>
+      </c>
+      <c r="X40">
+        <v>7.91</v>
+      </c>
+      <c r="Y40">
+        <v>0.2867</v>
+      </c>
+      <c r="Z40">
+        <v>3.9107</v>
       </c>
     </row>
     <row r="41">
@@ -3603,7 +4440,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3613,51 +4450,72 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116040</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M41"/>
-      <c r="N41">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-560112116040</t>
+        </is>
+      </c>
+      <c r="P41">
         <v>0.11</v>
       </c>
-      <c r="O41">
+      <c r="Q41">
         <v>0.66</v>
       </c>
-      <c r="P41">
+      <c r="R41">
         <v>13073</v>
       </c>
-      <c r="Q41"/>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41">
+      <c r="S41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
         <v>18</v>
       </c>
-      <c r="T41">
+      <c r="V41">
         <v>0.102</v>
       </c>
-      <c r="U41">
+      <c r="W41">
         <v>1.836</v>
       </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
         <v>1.836</v>
       </c>
     </row>
@@ -3692,7 +4550,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3702,51 +4560,72 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4700ELF</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M42"/>
-      <c r="N42">
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-4700ELF</t>
+        </is>
+      </c>
+      <c r="P42">
         <v>0.1</v>
       </c>
-      <c r="O42">
+      <c r="Q42">
         <v>0.1</v>
       </c>
-      <c r="P42">
+      <c r="R42">
         <v>874450</v>
       </c>
-      <c r="Q42"/>
-      <c r="R42">
-        <v>1</v>
-      </c>
-      <c r="S42">
+      <c r="S42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42">
         <v>10</v>
       </c>
-      <c r="T42">
+      <c r="V42">
         <v>0.012</v>
       </c>
-      <c r="U42">
+      <c r="W42">
         <v>0.12</v>
       </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
         <v>0.12</v>
       </c>
     </row>
@@ -3791,47 +4670,68 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300411121</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Headers &amp; Wire Housings</t>
         </is>
       </c>
-      <c r="J43"/>
-      <c r="K43" t="inlineStr">
+      <c r="K43"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M43"/>
-      <c r="N43">
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-61300411121</t>
+        </is>
+      </c>
+      <c r="P43">
         <v>0.19</v>
       </c>
-      <c r="O43">
+      <c r="Q43">
         <v>0.57</v>
       </c>
-      <c r="P43">
-        <v>52015</v>
-      </c>
-      <c r="Q43"/>
       <c r="R43">
-        <v>1</v>
-      </c>
-      <c r="S43">
+        <v>51814</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="U43">
         <v>10</v>
       </c>
-      <c r="T43">
+      <c r="V43">
         <v>0.163</v>
       </c>
-      <c r="U43">
+      <c r="W43">
         <v>1.63</v>
       </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
         <v>1.63</v>
       </c>
     </row>
@@ -3866,7 +4766,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3876,47 +4776,68 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Analog-Devices-Maxim-Integrated/MAX4995BAUT%2bT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
         </is>
       </c>
-      <c r="J44"/>
-      <c r="K44" t="inlineStr">
+      <c r="K44"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M44"/>
-      <c r="N44">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">700-MAX4995BAUTT</t>
+        </is>
+      </c>
+      <c r="P44">
         <v>6.99</v>
       </c>
-      <c r="O44">
+      <c r="Q44">
         <v>6.99</v>
       </c>
-      <c r="P44">
+      <c r="R44">
         <v>3754</v>
       </c>
-      <c r="Q44"/>
-      <c r="R44">
-        <v>1</v>
-      </c>
-      <c r="S44">
+      <c r="S44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="U44">
         <v>3</v>
       </c>
-      <c r="T44">
+      <c r="V44">
         <v>6.99</v>
       </c>
-      <c r="U44">
+      <c r="W44">
         <v>20.97</v>
       </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
         <v>20.97</v>
       </c>
     </row>
@@ -3951,7 +4872,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3961,51 +4882,72 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603133KFKTA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">No - RoHS Version Available</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M45"/>
-      <c r="N45">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0603-133K</t>
+        </is>
+      </c>
+      <c r="P45">
         <v>0.16</v>
       </c>
-      <c r="O45">
+      <c r="Q45">
         <v>0.16</v>
       </c>
-      <c r="P45">
+      <c r="R45">
         <v>7217</v>
       </c>
-      <c r="Q45"/>
-      <c r="R45">
-        <v>1</v>
-      </c>
-      <c r="S45">
+      <c r="S45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="U45">
         <v>3</v>
       </c>
-      <c r="T45">
+      <c r="V45">
         <v>0.16</v>
       </c>
-      <c r="U45">
+      <c r="W45">
         <v>0.48</v>
       </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
         <v>0.48</v>
       </c>
     </row>
@@ -4040,7 +4982,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-23-5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4050,48 +4992,69 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G08DBVT</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single AND Gate, Low-Voltage CMOS</t>
         </is>
       </c>
-      <c r="J46"/>
-      <c r="K46" t="inlineStr">
+      <c r="K46"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M46"/>
-      <c r="N46">
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-SN74LVC1G08DBVT</t>
+        </is>
+      </c>
+      <c r="P46">
         <v>0.9</v>
       </c>
-      <c r="O46">
+      <c r="Q46">
         <v>4.5</v>
       </c>
-      <c r="P46">
+      <c r="R46">
         <v>5486</v>
       </c>
-      <c r="Q46"/>
-      <c r="R46">
-        <v>1</v>
-      </c>
-      <c r="S46">
+      <c r="S46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46">
         <v>15</v>
       </c>
-      <c r="T46">
+      <c r="V46">
         <v>0.643</v>
-      </c>
-      <c r="U46">
-        <v>9.645</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
       </c>
       <c r="W46">
         <v>9.645</v>
+      </c>
+      <c r="X46">
+        <v>8</v>
+      </c>
+      <c r="Y46">
+        <v>0.7716</v>
+      </c>
+      <c r="Z46">
+        <v>10.4166</v>
       </c>
     </row>
     <row r="47">
@@ -4125,7 +5088,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4135,51 +5098,72 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-22R0ELF</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M47"/>
-      <c r="N47">
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-22R0ELF</t>
+        </is>
+      </c>
+      <c r="P47">
         <v>0.1</v>
       </c>
-      <c r="O47">
+      <c r="Q47">
         <v>0.4</v>
       </c>
-      <c r="P47">
+      <c r="R47">
         <v>67949</v>
       </c>
-      <c r="Q47"/>
-      <c r="R47">
-        <v>1</v>
-      </c>
-      <c r="S47">
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="U47">
         <v>12</v>
       </c>
-      <c r="T47">
+      <c r="V47">
         <v>0.012</v>
       </c>
-      <c r="U47">
+      <c r="W47">
         <v>0.144</v>
       </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
         <v>0.144</v>
       </c>
     </row>
@@ -4214,7 +5198,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4224,51 +5208,72 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3300ELF</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M48"/>
-      <c r="N48">
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-3300ELF</t>
+        </is>
+      </c>
+      <c r="P48">
         <v>0.1</v>
       </c>
-      <c r="O48">
+      <c r="Q48">
         <v>0.2</v>
       </c>
-      <c r="P48">
+      <c r="R48">
         <v>1487770</v>
       </c>
-      <c r="Q48"/>
-      <c r="R48">
-        <v>1</v>
-      </c>
-      <c r="S48">
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
+      <c r="U48">
         <v>10</v>
       </c>
-      <c r="T48">
+      <c r="V48">
         <v>0.012</v>
       </c>
-      <c r="U48">
+      <c r="W48">
         <v>0.12</v>
       </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
         <v>0.12</v>
       </c>
     </row>
@@ -4303,7 +5308,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4313,48 +5318,69 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B222KB5NNNC</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J49"/>
-      <c r="K49" t="inlineStr">
+      <c r="K49"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M49"/>
-      <c r="N49">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05B222KB5NNNC</t>
+        </is>
+      </c>
+      <c r="P49">
         <v>0.1</v>
       </c>
-      <c r="O49">
+      <c r="Q49">
         <v>0.1</v>
       </c>
-      <c r="P49">
+      <c r="R49">
         <v>12169</v>
       </c>
-      <c r="Q49"/>
-      <c r="R49">
-        <v>1</v>
-      </c>
-      <c r="S49">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49">
         <v>10</v>
       </c>
-      <c r="T49">
+      <c r="V49">
         <v>0.016</v>
-      </c>
-      <c r="U49">
-        <v>0.16</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
       </c>
       <c r="W49">
         <v>0.16</v>
+      </c>
+      <c r="X49">
+        <v>8</v>
+      </c>
+      <c r="Y49">
+        <v>0.0128</v>
+      </c>
+      <c r="Z49">
+        <v>0.1728</v>
       </c>
     </row>
     <row r="50">
@@ -4388,7 +5414,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">VQFN-HR-10</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4398,47 +5424,68 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS259470LRPWR</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hot Swap Voltage Controllers</t>
         </is>
       </c>
-      <c r="J50"/>
-      <c r="K50" t="inlineStr">
+      <c r="K50"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M50"/>
-      <c r="N50">
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS259470LRPWR</t>
+        </is>
+      </c>
+      <c r="P50">
         <v>1.71</v>
       </c>
-      <c r="O50">
+      <c r="Q50">
         <v>1.71</v>
       </c>
-      <c r="P50">
-        <v>5699</v>
-      </c>
-      <c r="Q50"/>
       <c r="R50">
-        <v>1</v>
-      </c>
-      <c r="S50">
+        <v>5669</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50">
         <v>3</v>
       </c>
-      <c r="T50">
+      <c r="V50">
         <v>1.71</v>
       </c>
-      <c r="U50">
+      <c r="W50">
         <v>5.13</v>
       </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
         <v>5.13</v>
       </c>
     </row>
@@ -4473,7 +5520,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-583-8</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4483,47 +5530,68 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS62933PDRLR</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Buck Converter SOT583-8</t>
         </is>
       </c>
-      <c r="J51"/>
-      <c r="K51" t="inlineStr">
+      <c r="K51"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M51"/>
-      <c r="N51">
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS62933PDRLR</t>
+        </is>
+      </c>
+      <c r="P51">
         <v>1.38</v>
       </c>
-      <c r="O51">
+      <c r="Q51">
         <v>2.76</v>
       </c>
-      <c r="P51">
-        <v>12149</v>
-      </c>
-      <c r="Q51"/>
       <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51">
+        <v>10754</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51">
         <v>6</v>
       </c>
-      <c r="T51">
+      <c r="V51">
         <v>1.38</v>
       </c>
-      <c r="U51">
+      <c r="W51">
         <v>8.28</v>
       </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
         <v>8.28</v>
       </c>
     </row>
@@ -4558,7 +5626,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4568,48 +5636,69 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0402FR-0710KL</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Thick Film Resistors - SMD</t>
         </is>
       </c>
-      <c r="J52"/>
-      <c r="K52" t="inlineStr">
+      <c r="K52"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M52"/>
-      <c r="N52">
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603-RC0402FR-0710KL</t>
+        </is>
+      </c>
+      <c r="P52">
         <v>0.1</v>
       </c>
-      <c r="O52">
+      <c r="Q52">
         <v>0.1</v>
       </c>
-      <c r="P52">
+      <c r="R52">
         <v>6976557</v>
       </c>
-      <c r="Q52"/>
-      <c r="R52">
-        <v>1</v>
-      </c>
-      <c r="S52">
+      <c r="S52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52">
         <v>10</v>
       </c>
-      <c r="T52">
+      <c r="V52">
         <v>0.009</v>
-      </c>
-      <c r="U52">
-        <v>0.09</v>
-      </c>
-      <c r="V52">
-        <v>0</v>
       </c>
       <c r="W52">
         <v>0.09</v>
+      </c>
+      <c r="X52">
+        <v>8</v>
+      </c>
+      <c r="Y52">
+        <v>0.0072</v>
+      </c>
+      <c r="Z52">
+        <v>0.0972</v>
       </c>
     </row>
     <row r="53">
@@ -4643,7 +5732,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4653,51 +5742,72 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-5101ELF</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M53"/>
-      <c r="N53">
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-5101ELF</t>
+        </is>
+      </c>
+      <c r="P53">
         <v>0.1</v>
       </c>
-      <c r="O53">
+      <c r="Q53">
         <v>0.2</v>
       </c>
-      <c r="P53">
+      <c r="R53">
         <v>1496328</v>
       </c>
-      <c r="Q53"/>
-      <c r="R53">
-        <v>1</v>
-      </c>
-      <c r="S53">
+      <c r="S53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="U53">
         <v>10</v>
       </c>
-      <c r="T53">
+      <c r="V53">
         <v>0.012</v>
       </c>
-      <c r="U53">
+      <c r="W53">
         <v>0.12</v>
       </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
         <v>0.12</v>
       </c>
     </row>
@@ -4732,7 +5842,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4742,48 +5852,69 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060RS75000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single Color LEDs</t>
         </is>
       </c>
-      <c r="J54"/>
-      <c r="K54" t="inlineStr">
+      <c r="K54"/>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M54"/>
-      <c r="N54">
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-150060RS75000</t>
+        </is>
+      </c>
+      <c r="P54">
         <v>0.16</v>
       </c>
-      <c r="O54">
+      <c r="Q54">
         <v>0.16</v>
       </c>
-      <c r="P54">
-        <v>368836</v>
-      </c>
-      <c r="Q54"/>
       <c r="R54">
-        <v>1</v>
-      </c>
-      <c r="S54">
+        <v>368610</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="U54">
         <v>3</v>
       </c>
-      <c r="T54">
+      <c r="V54">
         <v>0.16</v>
-      </c>
-      <c r="U54">
-        <v>0.48</v>
-      </c>
-      <c r="V54">
-        <v>0</v>
       </c>
       <c r="W54">
         <v>0.48</v>
+      </c>
+      <c r="X54">
+        <v>35</v>
+      </c>
+      <c r="Y54">
+        <v>0.168</v>
+      </c>
+      <c r="Z54">
+        <v>0.648</v>
       </c>
     </row>
     <row r="55">
@@ -4817,7 +5948,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOD-923-2</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4827,47 +5958,68 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/ESD9X5.0ST5G</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t xml:space="preserve">5V 1200W TVS unidirectional diode</t>
         </is>
       </c>
-      <c r="J55"/>
-      <c r="K55" t="inlineStr">
+      <c r="K55"/>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M55"/>
-      <c r="N55">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">863-ESD9X5.0ST5G</t>
+        </is>
+      </c>
+      <c r="P55">
         <v>0.16</v>
       </c>
-      <c r="O55">
+      <c r="Q55">
         <v>0.8</v>
       </c>
-      <c r="P55">
+      <c r="R55">
         <v>64742</v>
       </c>
-      <c r="Q55"/>
-      <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55">
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55">
         <v>15</v>
       </c>
-      <c r="T55">
+      <c r="V55">
         <v>0.101</v>
       </c>
-      <c r="U55">
+      <c r="W55">
         <v>1.515</v>
       </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
-      <c r="W55">
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
         <v>1.515</v>
       </c>
     </row>
@@ -4902,7 +6054,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tray</t>
+          <t xml:space="preserve">LQFP-144</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4912,47 +6064,68 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/STMicroelectronics/STM32H753ZIT6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Arm Cortex-M7 MCU LQFP144</t>
         </is>
       </c>
-      <c r="J56"/>
-      <c r="K56" t="inlineStr">
+      <c r="K56"/>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">France</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M56"/>
-      <c r="N56">
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511-STM32H753ZIT6</t>
+        </is>
+      </c>
+      <c r="P56">
         <v>17.13</v>
       </c>
-      <c r="O56">
+      <c r="Q56">
         <v>17.13</v>
       </c>
-      <c r="P56">
+      <c r="R56">
         <v>14</v>
       </c>
-      <c r="Q56"/>
-      <c r="R56">
-        <v>1</v>
-      </c>
-      <c r="S56">
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56">
         <v>3</v>
       </c>
-      <c r="T56">
+      <c r="V56">
         <v>17.13</v>
       </c>
-      <c r="U56">
+      <c r="W56">
         <v>51.39</v>
       </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
         <v>51.39</v>
       </c>
     </row>
@@ -4997,47 +6170,68 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Keystone-Electronics/1043</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cylindrical Battery Contacts, Clips, Holders &amp; Springs</t>
         </is>
       </c>
-      <c r="J57"/>
-      <c r="K57" t="inlineStr">
+      <c r="K57"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M57"/>
-      <c r="N57">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">534-1043</t>
+        </is>
+      </c>
+      <c r="P57">
         <v>2.99</v>
       </c>
-      <c r="O57">
+      <c r="Q57">
         <v>2.99</v>
       </c>
-      <c r="P57">
+      <c r="R57">
         <v>9773</v>
       </c>
-      <c r="Q57"/>
-      <c r="R57">
-        <v>1</v>
-      </c>
-      <c r="S57">
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57">
         <v>3</v>
       </c>
-      <c r="T57">
+      <c r="V57">
         <v>2.99</v>
       </c>
-      <c r="U57">
+      <c r="W57">
         <v>8.97</v>
       </c>
-      <c r="V57">
-        <v>0</v>
-      </c>
-      <c r="W57">
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
         <v>8.97</v>
       </c>
     </row>
@@ -5070,49 +6264,76 @@
           <t xml:space="preserve">MyFootprints:SWITCH_43SMTR92LFS</t>
         </is>
       </c>
-      <c r="G58"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reel</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/2/240/pts645-3050759.pdf</t>
+          <t xml:space="preserve">https://ckswitches.com/media/1471/pts645.pdf</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/PTS645SM43SMTR92-LFS</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t xml:space="preserve">PTS645</t>
         </is>
       </c>
-      <c r="J58"/>
       <c r="K58"/>
       <c r="L58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Details</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M58"/>
-      <c r="N58">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">611-PTS645SM43SMTR92</t>
+        </is>
+      </c>
+      <c r="P58">
         <v>0.36</v>
       </c>
-      <c r="O58">
+      <c r="Q58">
         <v>0.72</v>
       </c>
-      <c r="P58"/>
-      <c r="Q58"/>
-      <c r="R58">
-        <v>1</v>
-      </c>
-      <c r="S58">
+      <c r="R58"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
         <v>6</v>
       </c>
-      <c r="T58">
+      <c r="V58">
         <v>0.36</v>
       </c>
-      <c r="U58">
+      <c r="W58">
         <v>2.16</v>
       </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
+      <c r="X58"/>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
         <v>2.16</v>
       </c>
     </row>
@@ -5157,48 +6378,69 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/SRP7028A-4R7M</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Power Inductors - SMD</t>
         </is>
       </c>
-      <c r="J59"/>
-      <c r="K59" t="inlineStr">
+      <c r="K59"/>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M59"/>
-      <c r="N59">
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-SRP7028A-4R7M</t>
+        </is>
+      </c>
+      <c r="P59">
         <v>1.1</v>
       </c>
-      <c r="O59">
+      <c r="Q59">
         <v>1.1</v>
       </c>
-      <c r="P59">
+      <c r="R59">
         <v>16159</v>
       </c>
-      <c r="Q59"/>
-      <c r="R59">
-        <v>1</v>
-      </c>
-      <c r="S59">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+      <c r="U59">
         <v>3</v>
       </c>
-      <c r="T59">
+      <c r="V59">
         <v>1.1</v>
-      </c>
-      <c r="U59">
-        <v>3.3</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
       </c>
       <c r="W59">
         <v>3.3</v>
+      </c>
+      <c r="X59">
+        <v>8</v>
+      </c>
+      <c r="Y59">
+        <v>0.264</v>
+      </c>
+      <c r="Z59">
+        <v>3.564</v>
       </c>
     </row>
     <row r="60">
@@ -5232,7 +6474,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5242,52 +6484,73 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RT0603BRD0794K2L</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M60"/>
-      <c r="N60">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603-RT0603BRD0794K2L</t>
+        </is>
+      </c>
+      <c r="P60">
         <v>0.1</v>
       </c>
-      <c r="O60">
+      <c r="Q60">
         <v>0.1</v>
       </c>
-      <c r="P60">
+      <c r="R60">
         <v>8529</v>
       </c>
-      <c r="Q60"/>
-      <c r="R60">
-        <v>1</v>
-      </c>
-      <c r="S60">
+      <c r="S60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+      <c r="U60">
         <v>3</v>
       </c>
-      <c r="T60">
+      <c r="V60">
         <v>0.1</v>
-      </c>
-      <c r="U60">
-        <v>0.3</v>
-      </c>
-      <c r="V60">
-        <v>0</v>
       </c>
       <c r="W60">
         <v>0.3</v>
+      </c>
+      <c r="X60">
+        <v>8</v>
+      </c>
+      <c r="Y60">
+        <v>0.024</v>
+      </c>
+      <c r="Z60">
+        <v>0.324</v>
       </c>
     </row>
     <row r="61">
@@ -5321,7 +6584,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5331,48 +6594,69 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C220JB5NNNC</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J61"/>
-      <c r="K61" t="inlineStr">
+      <c r="K61"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M61"/>
-      <c r="N61">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05C220JB5NNNC</t>
+        </is>
+      </c>
+      <c r="P61">
         <v>0.1</v>
       </c>
-      <c r="O61">
+      <c r="Q61">
         <v>0.1</v>
       </c>
-      <c r="P61">
+      <c r="R61">
         <v>101965</v>
       </c>
-      <c r="Q61"/>
-      <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61">
+      <c r="S61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="U61">
         <v>10</v>
       </c>
-      <c r="T61">
+      <c r="V61">
         <v>0.021</v>
-      </c>
-      <c r="U61">
-        <v>0.21</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
       </c>
       <c r="W61">
         <v>0.21</v>
+      </c>
+      <c r="X61">
+        <v>8</v>
+      </c>
+      <c r="Y61">
+        <v>0.0168</v>
+      </c>
+      <c r="Z61">
+        <v>0.2268</v>
       </c>
     </row>
     <row r="62">
@@ -5406,7 +6690,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5416,48 +6700,69 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C100JB5NNNC</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J62"/>
-      <c r="K62" t="inlineStr">
+      <c r="K62"/>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M62"/>
-      <c r="N62">
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05C100JB5NNNC</t>
+        </is>
+      </c>
+      <c r="P62">
         <v>0.1</v>
       </c>
-      <c r="O62">
+      <c r="Q62">
         <v>0.3</v>
       </c>
-      <c r="P62">
+      <c r="R62">
         <v>118171</v>
       </c>
-      <c r="Q62"/>
-      <c r="R62">
-        <v>1</v>
-      </c>
-      <c r="S62">
+      <c r="S62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+      <c r="U62">
         <v>10</v>
       </c>
-      <c r="T62">
+      <c r="V62">
         <v>0.019</v>
-      </c>
-      <c r="U62">
-        <v>0.19</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
       </c>
       <c r="W62">
         <v>0.19</v>
+      </c>
+      <c r="X62">
+        <v>8</v>
+      </c>
+      <c r="Y62">
+        <v>0.0152</v>
+      </c>
+      <c r="Z62">
+        <v>0.2052</v>
       </c>
     </row>
     <row r="63">
@@ -5489,7 +6794,11 @@
           <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
-      <c r="G63"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0402 (1005 metric)</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C750JB5NNN</t>
@@ -5497,41 +6806,64 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C750JB5NNNC</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t xml:space="preserve">75pF</t>
         </is>
       </c>
-      <c r="J63"/>
       <c r="K63"/>
       <c r="L63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Details</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M63"/>
-      <c r="N63">
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05C750JB5NNNC</t>
+        </is>
+      </c>
+      <c r="P63">
         <v>0.1</v>
       </c>
-      <c r="O63">
+      <c r="Q63">
         <v>0.1</v>
       </c>
-      <c r="P63"/>
-      <c r="Q63"/>
-      <c r="R63">
-        <v>1</v>
-      </c>
-      <c r="S63">
+      <c r="R63"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63">
         <v>10</v>
       </c>
-      <c r="T63">
+      <c r="V63">
         <v>0.021</v>
       </c>
-      <c r="U63">
+      <c r="W63">
         <v>0.21</v>
       </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
+      <c r="X63"/>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
         <v>0.21</v>
       </c>
     </row>
@@ -5566,7 +6898,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5576,48 +6908,69 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Dialight/599-0160-137F</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Light emitting diode</t>
         </is>
       </c>
-      <c r="J64"/>
-      <c r="K64" t="inlineStr">
+      <c r="K64"/>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M64"/>
-      <c r="N64">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">645-599-0160-137F</t>
+        </is>
+      </c>
+      <c r="P64">
         <v>0.29</v>
       </c>
-      <c r="O64">
+      <c r="Q64">
         <v>0.87</v>
       </c>
-      <c r="P64">
+      <c r="R64">
         <v>11820</v>
       </c>
-      <c r="Q64"/>
-      <c r="R64">
-        <v>1</v>
-      </c>
-      <c r="S64">
+      <c r="S64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+      <c r="U64">
         <v>10</v>
       </c>
-      <c r="T64">
+      <c r="V64">
         <v>0.195</v>
-      </c>
-      <c r="U64">
-        <v>1.95</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
       </c>
       <c r="W64">
         <v>1.95</v>
+      </c>
+      <c r="X64">
+        <v>7.93</v>
+      </c>
+      <c r="Y64">
+        <v>0.1546</v>
+      </c>
+      <c r="Z64">
+        <v>2.1046</v>
       </c>
     </row>
     <row r="65">
@@ -5651,7 +7004,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">1206 (3216 metric)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5661,48 +7014,69 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A226KAHNNNE</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J65"/>
-      <c r="K65" t="inlineStr">
+      <c r="K65"/>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M65"/>
-      <c r="N65">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL31A226KAHNNNE</t>
+        </is>
+      </c>
+      <c r="P65">
         <v>0.38</v>
       </c>
-      <c r="O65">
+      <c r="Q65">
         <v>3.04</v>
       </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65"/>
       <c r="R65">
-        <v>1</v>
-      </c>
-      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65">
         <v>24</v>
       </c>
-      <c r="T65">
+      <c r="V65">
         <v>0.166</v>
-      </c>
-      <c r="U65">
-        <v>3.984</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
       </c>
       <c r="W65">
         <v>3.984</v>
+      </c>
+      <c r="X65">
+        <v>7.89</v>
+      </c>
+      <c r="Y65">
+        <v>0.3143</v>
+      </c>
+      <c r="Z65">
+        <v>4.2983</v>
       </c>
     </row>
     <row r="66">
@@ -5736,7 +7110,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">VQFN-12</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5746,47 +7120,68 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS2121RUXR</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
         </is>
       </c>
-      <c r="J66"/>
-      <c r="K66" t="inlineStr">
+      <c r="K66"/>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M66"/>
-      <c r="N66">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPS2121RUXR</t>
+        </is>
+      </c>
+      <c r="P66">
         <v>2.44</v>
       </c>
-      <c r="O66">
+      <c r="Q66">
         <v>2.44</v>
       </c>
-      <c r="P66">
-        <v>14171</v>
-      </c>
-      <c r="Q66"/>
       <c r="R66">
-        <v>1</v>
-      </c>
-      <c r="S66">
+        <v>16194</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+      <c r="U66">
         <v>3</v>
       </c>
-      <c r="T66">
+      <c r="V66">
         <v>2.44</v>
       </c>
-      <c r="U66">
+      <c r="W66">
         <v>7.32</v>
       </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
         <v>7.32</v>
       </c>
     </row>
@@ -5821,7 +7216,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5831,51 +7226,72 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6652ELF</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M67"/>
-      <c r="N67">
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603-FX6652ELF</t>
+        </is>
+      </c>
+      <c r="P67">
         <v>0.1</v>
       </c>
-      <c r="O67">
+      <c r="Q67">
         <v>0.1</v>
       </c>
-      <c r="P67">
+      <c r="R67">
         <v>368665</v>
       </c>
-      <c r="Q67"/>
-      <c r="R67">
-        <v>1</v>
-      </c>
-      <c r="S67">
+      <c r="S67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+      <c r="U67">
         <v>10</v>
       </c>
-      <c r="T67">
+      <c r="V67">
         <v>0.016</v>
       </c>
-      <c r="U67">
+      <c r="W67">
         <v>0.16</v>
       </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
         <v>0.16</v>
       </c>
     </row>
@@ -5910,7 +7326,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">Top-Mount</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5920,46 +7336,69 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/GCT/USB4105-GF-A</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t xml:space="preserve">USB4105-GF-A GCT USB Connectors USB Type C,2.0, Rec,SMT, 0.95mmTH Shell Stakes,G/F,RA,Top Mnt,T&amp;R datasheet, inventory, &amp; pricing.</t>
         </is>
       </c>
-      <c r="J68"/>
-      <c r="K68" t="inlineStr">
+      <c r="K68"/>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M68"/>
-      <c r="N68">
-        <v>0.8</v>
-      </c>
-      <c r="O68">
-        <v>0.8</v>
-      </c>
-      <c r="P68"/>
-      <c r="Q68"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640-USB4105-GF-A</t>
+        </is>
+      </c>
+      <c r="P68">
+        <v>0.93</v>
+      </c>
+      <c r="Q68">
+        <v>0.93</v>
+      </c>
       <c r="R68">
-        <v>1</v>
-      </c>
-      <c r="S68">
+        <v>481287</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68">
         <v>3</v>
       </c>
-      <c r="T68">
-        <v>0.8</v>
-      </c>
-      <c r="U68">
-        <v>2.4</v>
-      </c>
       <c r="V68">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="W68">
-        <v>2.4</v>
+        <v>2.79</v>
+      </c>
+      <c r="X68">
+        <v>30</v>
+      </c>
+      <c r="Y68">
+        <v>0.837</v>
+      </c>
+      <c r="Z68">
+        <v>3.627</v>
       </c>
     </row>
     <row r="69">
@@ -5993,7 +7432,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6003,48 +7442,69 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A475KAQNNNE</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J69"/>
-      <c r="K69" t="inlineStr">
+      <c r="K69"/>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M69"/>
-      <c r="N69">
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL21A475KAQNNNE</t>
+        </is>
+      </c>
+      <c r="P69">
         <v>0.11</v>
       </c>
-      <c r="O69">
+      <c r="Q69">
         <v>0.22</v>
       </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69"/>
       <c r="R69">
-        <v>1</v>
-      </c>
-      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+      <c r="U69">
         <v>10</v>
       </c>
-      <c r="T69">
+      <c r="V69">
         <v>0.042</v>
-      </c>
-      <c r="U69">
-        <v>0.42</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
       </c>
       <c r="W69">
         <v>0.42</v>
+      </c>
+      <c r="X69">
+        <v>8.18</v>
+      </c>
+      <c r="Y69">
+        <v>0.0344</v>
+      </c>
+      <c r="Z69">
+        <v>0.4544</v>
       </c>
     </row>
     <row r="70">
@@ -6078,7 +7538,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6088,48 +7548,69 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0603FR-07220RL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Thick Film Resistors - SMD</t>
         </is>
       </c>
-      <c r="J70"/>
-      <c r="K70" t="inlineStr">
+      <c r="K70"/>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M70"/>
-      <c r="N70">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603-RC0603FR-07220RL</t>
+        </is>
+      </c>
+      <c r="P70">
         <v>0.1</v>
       </c>
-      <c r="O70">
+      <c r="Q70">
         <v>0.1</v>
       </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70"/>
       <c r="R70">
-        <v>1</v>
-      </c>
-      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+      <c r="U70">
         <v>10</v>
       </c>
-      <c r="T70">
+      <c r="V70">
         <v>0.014</v>
-      </c>
-      <c r="U70">
-        <v>0.14</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
       </c>
       <c r="W70">
         <v>0.14</v>
+      </c>
+      <c r="X70">
+        <v>8</v>
+      </c>
+      <c r="Y70">
+        <v>0.0112</v>
+      </c>
+      <c r="Z70">
+        <v>0.1512</v>
       </c>
     </row>
     <row r="71">
@@ -6163,7 +7644,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SC-59-3 (SOT-23-3)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6173,47 +7654,68 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPD2E009DBZR</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t xml:space="preserve">ESD Protection Diodes / TVS Diodes</t>
         </is>
       </c>
-      <c r="J71"/>
-      <c r="K71" t="inlineStr">
+      <c r="K71"/>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M71"/>
-      <c r="N71">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TPD2E009DBZR</t>
+        </is>
+      </c>
+      <c r="P71">
         <v>0.79</v>
       </c>
-      <c r="O71">
+      <c r="Q71">
         <v>0.79</v>
       </c>
-      <c r="P71">
-        <v>4392</v>
-      </c>
-      <c r="Q71"/>
       <c r="R71">
-        <v>1</v>
-      </c>
-      <c r="S71">
+        <v>10330</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+      <c r="U71">
         <v>3</v>
       </c>
-      <c r="T71">
+      <c r="V71">
         <v>0.79</v>
       </c>
-      <c r="U71">
+      <c r="W71">
         <v>2.37</v>
       </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
         <v>2.37</v>
       </c>
     </row>
@@ -6248,7 +7750,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6258,48 +7760,69 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060GS75000</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single Color LEDs</t>
         </is>
       </c>
-      <c r="J72"/>
-      <c r="K72" t="inlineStr">
+      <c r="K72"/>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M72"/>
-      <c r="N72">
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-150060GS75000</t>
+        </is>
+      </c>
+      <c r="P72">
         <v>0.16</v>
       </c>
-      <c r="O72">
+      <c r="Q72">
         <v>0.16</v>
       </c>
-      <c r="P72">
-        <v>143068</v>
-      </c>
-      <c r="Q72"/>
       <c r="R72">
-        <v>1</v>
-      </c>
-      <c r="S72">
+        <v>146494</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+      <c r="U72">
         <v>3</v>
       </c>
-      <c r="T72">
+      <c r="V72">
         <v>0.16</v>
-      </c>
-      <c r="U72">
-        <v>0.48</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
       </c>
       <c r="W72">
         <v>0.48</v>
+      </c>
+      <c r="X72">
+        <v>35</v>
+      </c>
+      <c r="Y72">
+        <v>0.168</v>
+      </c>
+      <c r="Z72">
+        <v>0.648</v>
       </c>
     </row>
     <row r="73">
@@ -6333,7 +7856,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6343,48 +7866,69 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B332KB5NNNC</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J73"/>
-      <c r="K73" t="inlineStr">
+      <c r="K73"/>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M73"/>
-      <c r="N73">
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05B332KB5NNNC</t>
+        </is>
+      </c>
+      <c r="P73">
         <v>0.1</v>
       </c>
-      <c r="O73">
+      <c r="Q73">
         <v>0.1</v>
       </c>
-      <c r="P73">
-        <v>125442</v>
-      </c>
-      <c r="Q73"/>
       <c r="R73">
-        <v>1</v>
-      </c>
-      <c r="S73">
+        <v>125342</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T73">
+        <v>1</v>
+      </c>
+      <c r="U73">
         <v>10</v>
       </c>
-      <c r="T73">
+      <c r="V73">
         <v>0.012</v>
-      </c>
-      <c r="U73">
-        <v>0.12</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
       </c>
       <c r="W73">
         <v>0.12</v>
+      </c>
+      <c r="X73">
+        <v>8</v>
+      </c>
+      <c r="Y73">
+        <v>0.0096</v>
+      </c>
+      <c r="Z73">
+        <v>0.1296</v>
       </c>
     </row>
     <row r="74">
@@ -6418,7 +7962,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6428,47 +7972,68 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74AHC1G125DRLR</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single Buffer Gate Tri-State, Low-Voltage CMOS</t>
         </is>
       </c>
-      <c r="J74"/>
-      <c r="K74" t="inlineStr">
+      <c r="K74"/>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M74"/>
-      <c r="N74">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-SN74AHC1G125DRLR</t>
+        </is>
+      </c>
+      <c r="P74">
         <v>0.22</v>
       </c>
-      <c r="O74">
+      <c r="Q74">
         <v>2.64</v>
       </c>
-      <c r="P74">
+      <c r="R74">
         <v>6492</v>
       </c>
-      <c r="Q74"/>
-      <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74">
+      <c r="S74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+      <c r="U74">
         <v>36</v>
       </c>
-      <c r="T74">
+      <c r="V74">
         <v>0.131</v>
       </c>
-      <c r="U74">
+      <c r="W74">
         <v>4.716</v>
       </c>
-      <c r="V74">
-        <v>0</v>
-      </c>
-      <c r="W74">
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
         <v>4.716</v>
       </c>
     </row>
@@ -6509,48 +8074,69 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Yamaichi-Electronics/IC51-0644-807</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t xml:space="preserve">IC &amp; Component Sockets</t>
         </is>
       </c>
-      <c r="J75"/>
-      <c r="K75" t="inlineStr">
+      <c r="K75"/>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M75"/>
-      <c r="N75">
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945-IC51-0644-807</t>
+        </is>
+      </c>
+      <c r="P75">
         <v>126.53</v>
       </c>
-      <c r="O75">
+      <c r="Q75">
         <v>126.53</v>
       </c>
-      <c r="P75">
+      <c r="R75">
         <v>9</v>
       </c>
-      <c r="Q75"/>
-      <c r="R75">
-        <v>1</v>
-      </c>
-      <c r="S75">
+      <c r="S75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T75">
+        <v>1</v>
+      </c>
+      <c r="U75">
         <v>3</v>
       </c>
-      <c r="T75">
+      <c r="V75">
         <v>126.53</v>
-      </c>
-      <c r="U75">
-        <v>379.59</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
       </c>
       <c r="W75">
         <v>379.59</v>
+      </c>
+      <c r="X75">
+        <v>8</v>
+      </c>
+      <c r="Y75">
+        <v>30.3672</v>
+      </c>
+      <c r="Z75">
+        <v>409.9572</v>
       </c>
     </row>
     <row r="76">
@@ -6584,7 +8170,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6594,47 +8180,68 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1GU04DRLR</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Single Inverter Gate, SOT-553</t>
         </is>
       </c>
-      <c r="J76"/>
-      <c r="K76" t="inlineStr">
+      <c r="K76"/>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M76"/>
-      <c r="N76">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-SN74LVC1GU04DRLR</t>
+        </is>
+      </c>
+      <c r="P76">
         <v>0.36</v>
       </c>
-      <c r="O76">
+      <c r="Q76">
         <v>2.52</v>
       </c>
-      <c r="P76">
+      <c r="R76">
         <v>6693</v>
       </c>
-      <c r="Q76"/>
-      <c r="R76">
-        <v>1</v>
-      </c>
-      <c r="S76">
+      <c r="S76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="U76">
         <v>21</v>
       </c>
-      <c r="T76">
+      <c r="V76">
         <v>0.246</v>
       </c>
-      <c r="U76">
+      <c r="W76">
         <v>5.166</v>
       </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
         <v>5.166</v>
       </c>
     </row>
@@ -6669,7 +8276,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6679,48 +8286,69 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J77"/>
-      <c r="K77" t="inlineStr">
+      <c r="K77"/>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M77"/>
-      <c r="N77">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="P77">
         <v>0.12</v>
       </c>
-      <c r="O77">
+      <c r="Q77">
         <v>0.12</v>
       </c>
-      <c r="P77">
+      <c r="R77">
         <v>389441</v>
       </c>
-      <c r="Q77"/>
-      <c r="R77">
-        <v>1</v>
-      </c>
-      <c r="S77">
+      <c r="S77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="U77">
         <v>3</v>
       </c>
-      <c r="T77">
+      <c r="V77">
         <v>0.12</v>
-      </c>
-      <c r="U77">
-        <v>0.36</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
       </c>
       <c r="W77">
         <v>0.36</v>
+      </c>
+      <c r="X77">
+        <v>8.33</v>
+      </c>
+      <c r="Y77">
+        <v>0.03</v>
+      </c>
+      <c r="Z77">
+        <v>0.39</v>
       </c>
     </row>
     <row r="78">
@@ -6754,7 +8382,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">VSSOP-8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6764,47 +8392,68 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Voltage-Level Shifter VSSOP-8</t>
         </is>
       </c>
-      <c r="J78"/>
-      <c r="K78" t="inlineStr">
+      <c r="K78"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thailand</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M78"/>
-      <c r="N78">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595-TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="P78">
         <v>0.63</v>
       </c>
-      <c r="O78">
+      <c r="Q78">
         <v>1.26</v>
       </c>
-      <c r="P78">
-        <v>111490</v>
-      </c>
-      <c r="Q78"/>
       <c r="R78">
-        <v>1</v>
-      </c>
-      <c r="S78">
+        <v>111487</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+      <c r="U78">
         <v>6</v>
       </c>
-      <c r="T78">
+      <c r="V78">
         <v>0.63</v>
       </c>
-      <c r="U78">
+      <c r="W78">
         <v>3.78</v>
       </c>
-      <c r="V78">
-        <v>0</v>
-      </c>
-      <c r="W78">
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
         <v>3.78</v>
       </c>
     </row>
@@ -6839,7 +8488,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6849,52 +8498,73 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/AC0603FR-07255KL</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M79"/>
-      <c r="N79">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603-AC0603FR-07255KL</t>
+        </is>
+      </c>
+      <c r="P79">
         <v>0.1</v>
       </c>
-      <c r="O79">
+      <c r="Q79">
         <v>0.1</v>
       </c>
-      <c r="P79">
+      <c r="R79">
         <v>27471</v>
       </c>
-      <c r="Q79"/>
-      <c r="R79">
-        <v>1</v>
-      </c>
-      <c r="S79">
+      <c r="S79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="U79">
         <v>10</v>
       </c>
-      <c r="T79">
+      <c r="V79">
         <v>0.017</v>
-      </c>
-      <c r="U79">
-        <v>0.17</v>
-      </c>
-      <c r="V79">
-        <v>0</v>
       </c>
       <c r="W79">
         <v>0.17</v>
+      </c>
+      <c r="X79">
+        <v>30</v>
+      </c>
+      <c r="Y79">
+        <v>0.051</v>
+      </c>
+      <c r="Z79">
+        <v>0.221</v>
       </c>
     </row>
     <row r="80">
@@ -6928,7 +8598,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6938,51 +8608,72 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06035K05FKEA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M80"/>
-      <c r="N80">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0603-5.05K-E3</t>
+        </is>
+      </c>
+      <c r="P80">
         <v>0.1</v>
       </c>
-      <c r="O80">
+      <c r="Q80">
         <v>0.3</v>
       </c>
-      <c r="P80">
+      <c r="R80">
         <v>7092</v>
       </c>
-      <c r="Q80"/>
-      <c r="R80">
-        <v>1</v>
-      </c>
-      <c r="S80">
+      <c r="S80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80">
         <v>10</v>
       </c>
-      <c r="T80">
+      <c r="V80">
         <v>0.029</v>
       </c>
-      <c r="U80">
+      <c r="W80">
         <v>0.29</v>
       </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
         <v>0.29</v>
       </c>
     </row>
@@ -7027,48 +8718,69 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/JS102011SAQN</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Slide Switches</t>
         </is>
       </c>
-      <c r="J81"/>
-      <c r="K81" t="inlineStr">
+      <c r="K81"/>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M81"/>
-      <c r="N81">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">611-JS102011SAQN</t>
+        </is>
+      </c>
+      <c r="P81">
         <v>0.84</v>
       </c>
-      <c r="O81">
+      <c r="Q81">
         <v>1.68</v>
       </c>
-      <c r="P81">
+      <c r="R81">
         <v>6938</v>
       </c>
-      <c r="Q81"/>
-      <c r="R81">
-        <v>1</v>
-      </c>
-      <c r="S81">
+      <c r="S81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="U81">
         <v>6</v>
       </c>
-      <c r="T81">
+      <c r="V81">
         <v>0.84</v>
-      </c>
-      <c r="U81">
-        <v>5.04</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
       </c>
       <c r="W81">
         <v>5.04</v>
+      </c>
+      <c r="X81">
+        <v>7.98</v>
+      </c>
+      <c r="Y81">
+        <v>0.4022</v>
+      </c>
+      <c r="Z81">
+        <v>5.4422</v>
       </c>
     </row>
     <row r="82">
@@ -7102,7 +8814,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7112,51 +8824,72 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ROHM-Semiconductor/KTR03EZPF3403</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M82"/>
-      <c r="N82">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755-KTR03EZPF3403</t>
+        </is>
+      </c>
+      <c r="P82">
         <v>0.19</v>
       </c>
-      <c r="O82">
+      <c r="Q82">
         <v>0.19</v>
       </c>
-      <c r="P82">
+      <c r="R82">
         <v>13778</v>
       </c>
-      <c r="Q82"/>
-      <c r="R82">
-        <v>1</v>
-      </c>
-      <c r="S82">
+      <c r="S82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+      <c r="U82">
         <v>3</v>
       </c>
-      <c r="T82">
+      <c r="V82">
         <v>0.19</v>
       </c>
-      <c r="U82">
+      <c r="W82">
         <v>0.57</v>
       </c>
-      <c r="V82">
-        <v>0</v>
-      </c>
-      <c r="W82">
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
         <v>0.57</v>
       </c>
     </row>
@@ -7191,7 +8924,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7201,51 +8934,72 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06033R32FKTA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">No - RoHS Version Available</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M83"/>
-      <c r="N83">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71-CRCW0603-3.32</t>
+        </is>
+      </c>
+      <c r="P83">
         <v>0.29</v>
       </c>
-      <c r="O83">
+      <c r="Q83">
         <v>0.29</v>
       </c>
-      <c r="P83">
+      <c r="R83">
         <v>2600</v>
       </c>
-      <c r="Q83"/>
-      <c r="R83">
-        <v>1</v>
-      </c>
-      <c r="S83">
+      <c r="S83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83">
         <v>3</v>
       </c>
-      <c r="T83">
+      <c r="V83">
         <v>0.29</v>
       </c>
-      <c r="U83">
+      <c r="W83">
         <v>0.87</v>
       </c>
-      <c r="V83">
-        <v>0</v>
-      </c>
-      <c r="W83">
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
         <v>0.87</v>
       </c>
     </row>
@@ -7280,7 +9034,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7290,51 +9044,72 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6800ELF</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M84"/>
-      <c r="N84">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652-CR0603FX-6800ELF</t>
+        </is>
+      </c>
+      <c r="P84">
         <v>0.1</v>
       </c>
-      <c r="O84">
+      <c r="Q84">
         <v>0.1</v>
       </c>
-      <c r="P84">
+      <c r="R84">
         <v>971001</v>
       </c>
-      <c r="Q84"/>
-      <c r="R84">
-        <v>1</v>
-      </c>
-      <c r="S84">
+      <c r="S84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84">
         <v>10</v>
       </c>
-      <c r="T84">
+      <c r="V84">
         <v>0.011</v>
       </c>
-      <c r="U84">
+      <c r="W84">
         <v>0.11</v>
       </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84">
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
         <v>0.11</v>
       </c>
     </row>
@@ -7369,7 +9144,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7379,47 +9154,68 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/742792022</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ferrite Beads</t>
         </is>
       </c>
-      <c r="J85"/>
-      <c r="K85" t="inlineStr">
+      <c r="K85"/>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M85"/>
-      <c r="N85">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-742792022</t>
+        </is>
+      </c>
+      <c r="P85">
         <v>0.16</v>
       </c>
-      <c r="O85">
+      <c r="Q85">
         <v>0.16</v>
       </c>
-      <c r="P85">
-        <v>145767</v>
-      </c>
-      <c r="Q85"/>
       <c r="R85">
-        <v>1</v>
-      </c>
-      <c r="S85">
+        <v>145687</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+      <c r="U85">
         <v>3</v>
       </c>
-      <c r="T85">
+      <c r="V85">
         <v>0.16</v>
       </c>
-      <c r="U85">
+      <c r="W85">
         <v>0.48</v>
       </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
-      <c r="W85">
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
         <v>0.48</v>
       </c>
     </row>
@@ -7454,7 +9250,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7464,51 +9260,72 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116151</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M86"/>
-      <c r="N86">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710-560112116151</t>
+        </is>
+      </c>
+      <c r="P86">
         <v>0.11</v>
       </c>
-      <c r="O86">
+      <c r="Q86">
         <v>0.11</v>
       </c>
-      <c r="P86">
+      <c r="R86">
         <v>9795</v>
       </c>
-      <c r="Q86"/>
-      <c r="R86">
-        <v>1</v>
-      </c>
-      <c r="S86">
+      <c r="S86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86">
         <v>3</v>
       </c>
-      <c r="T86">
+      <c r="V86">
         <v>0.11</v>
       </c>
-      <c r="U86">
+      <c r="W86">
         <v>0.33</v>
       </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
-      <c r="W86">
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
         <v>0.33</v>
       </c>
     </row>
@@ -7543,7 +9360,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7553,51 +9370,72 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-PA2F1242X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japan</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M87"/>
-      <c r="N87">
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">667-ERJ-PA2F1242X</t>
+        </is>
+      </c>
+      <c r="P87">
         <v>0.28</v>
       </c>
-      <c r="O87">
+      <c r="Q87">
         <v>0.28</v>
       </c>
-      <c r="P87">
+      <c r="R87">
         <v>28035</v>
       </c>
-      <c r="Q87"/>
-      <c r="R87">
-        <v>1</v>
-      </c>
-      <c r="S87">
+      <c r="S87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87">
         <v>3</v>
       </c>
-      <c r="T87">
+      <c r="V87">
         <v>0.28</v>
       </c>
-      <c r="U87">
+      <c r="W87">
         <v>0.84</v>
       </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87">
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
         <v>0.84</v>
       </c>
     </row>
@@ -7642,48 +9480,69 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QSH-060-01-H-D-A</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
         </is>
       </c>
-      <c r="J88"/>
-      <c r="K88" t="inlineStr">
+      <c r="K88"/>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costa Rica</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M88"/>
-      <c r="N88">
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200-QSH06001HDA</t>
+        </is>
+      </c>
+      <c r="P88">
         <v>22.49</v>
       </c>
-      <c r="O88">
+      <c r="Q88">
         <v>22.49</v>
       </c>
-      <c r="P88">
+      <c r="R88">
         <v>202</v>
       </c>
-      <c r="Q88"/>
-      <c r="R88">
-        <v>1</v>
-      </c>
-      <c r="S88">
+      <c r="S88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="U88">
         <v>3</v>
       </c>
-      <c r="T88">
+      <c r="V88">
         <v>22.49</v>
-      </c>
-      <c r="U88">
-        <v>67.47</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
       </c>
       <c r="W88">
         <v>67.47</v>
+      </c>
+      <c r="X88">
+        <v>6.98</v>
+      </c>
+      <c r="Y88">
+        <v>4.7094</v>
+      </c>
+      <c r="Z88">
+        <v>72.1794</v>
       </c>
     </row>
     <row r="89">
@@ -7717,7 +9576,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7727,51 +9586,72 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A105KB8NNNC</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Multilayer Ceramic Capacitors MLCC - SMD/SMT</t>
         </is>
       </c>
-      <c r="J89"/>
-      <c r="K89" t="inlineStr">
+      <c r="K89"/>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philippines</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="M89"/>
-      <c r="N89">
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL10A105KB8NNNC</t>
+        </is>
+      </c>
+      <c r="P89">
         <v>0.11</v>
       </c>
-      <c r="O89">
+      <c r="Q89">
         <v>1.54</v>
       </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89"/>
       <c r="R89">
-        <v>1</v>
-      </c>
-      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89">
         <v>42</v>
       </c>
-      <c r="T89">
+      <c r="V89">
         <v>0.044</v>
-      </c>
-      <c r="U89">
-        <v>1.848</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
       </c>
       <c r="W89">
         <v>1.848</v>
       </c>
+      <c r="X89">
+        <v>8.18</v>
+      </c>
+      <c r="Y89">
+        <v>0.1512</v>
+      </c>
+      <c r="Z89">
+        <v>1.9992</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W89"/>
+  <autoFilter ref="A1:Z89"/>
 </worksheet>
 </file>
--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -17,6 +17,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -34,9 +40,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -45,7 +52,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Z89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -57,12 +64,12 @@
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="9" max="9" width="49" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="29" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
@@ -243,14 +250,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116009.pdf</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116009</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116009</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -353,14 +360,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B104KO5NNN</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B104KO5NNNC</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B104KO5NNNC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -459,14 +466,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-2102ELF</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-2102ELF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -569,14 +576,14 @@
           <t xml:space="preserve">0402</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04023R32FKED</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW04023R32FKED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -679,14 +686,14 @@
           <t xml:space="preserve">Tray</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qth.pdf</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QTH-060-01-L-D-A</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=QTH-060-01-L-D-A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -785,14 +792,14 @@
           <t xml:space="preserve">VSSOP-8</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/sn74lvc1g74</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G74DCUR</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1G74DCUR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -891,14 +898,14 @@
           <t xml:space="preserve">SOT23-6</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps22917</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22917LDBVR</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS22917LDBVR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -997,14 +1004,14 @@
           <t xml:space="preserve">SOT-23-3</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.onsemi.com/pub/Collateral/NDS7002A-D.PDF</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/2N7002</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=2N7002</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1103,14 +1110,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=1622877&amp;DocType=Customer+Drawing&amp;DocLang=English&amp;PartCntxt=1622877-2</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/TE-Connectivity-Holsworthy/CRG0603F1M0-10</t>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRG0603F1M0-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1213,14 +1220,14 @@
           <t xml:space="preserve">1206 (3216 metric)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL31A106KBHNNN</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A106KBHNNNE</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL31A106KBHNNNE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1319,14 +1326,14 @@
           <t xml:space="preserve">VQFN-16</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/bq24075</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/BQ24074RGTT</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=BQ24074RGTT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1425,14 +1432,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116004.pdf</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116004</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116004</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1535,14 +1542,14 @@
           <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A225KO8NNN</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A225KO8NNNC</t>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A225KO8NNNC</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1641,14 +1648,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1022V</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-H3EF1022V</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1751,14 +1758,14 @@
           <t xml:space="preserve">TSSOP-16</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/sn74lvc138a-ep</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC138AQPWREP</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC138AQPWREP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1857,14 +1864,14 @@
           <t xml:space="preserve">Bulk</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/61300811121.pdf</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300811121</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=61300811121</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1963,14 +1970,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B102KB5NNN</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B102KB5NNNC</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B102KB5NNNC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2069,14 +2076,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603249KFKEC</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW0603249KFKEC</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2179,14 +2186,14 @@
           <t xml:space="preserve">Reel</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/74438357010.pdf</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74438357010</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=74438357010</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2289,14 +2296,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/317/1/ASC_MR.pdf</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X4703FTL</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=MR06X4703FTL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2399,14 +2406,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDP0000/AOA0000C334.pdf</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-S03F1002V</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-S03F1002V</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2509,14 +2516,14 @@
           <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps22918-q1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22918TDBVRQ1</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2615,14 +2622,14 @@
           <t xml:space="preserve">SOT-353-5</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/diod-s-a0011233448-1.pdf</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Diodes-Incorporated/74AHC1G32QSE-7</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=74AHC1G32QSE-7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2721,14 +2728,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/AOA0000C331.pdf</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-P03F1101V</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-P03F1101V</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2831,14 +2838,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4422ELF</t>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4422ELF</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2941,14 +2948,14 @@
           <t xml:space="preserve">Reel</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/74439346068.pdf</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74439346068</t>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=74439346068</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3051,14 +3058,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/317/1/ASC_MR.pdf</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X47R0FTL</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=MR06X47R0FTL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3161,14 +3168,14 @@
           <t xml:space="preserve">SOT-563-6</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps61023</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS61023DRLT</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS61023DRLT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3267,14 +3274,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3162ELF</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-3162ELF</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3377,14 +3384,14 @@
           <t xml:space="preserve">3.2 mm x 2.5 mm</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/184/1/abm8.pdf</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ABRACON/ABM8-25.000MHZ-B2-T</t>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ABM8-25.000MHZ-B2-T</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3483,14 +3490,14 @@
           <t xml:space="preserve">Bulk</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/315/1/EG1218.pdf</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/E-Switch/EG1218</t>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=EG1218</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3585,12 +3592,12 @@
         </is>
       </c>
       <c r="G33"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/167/1/Scotch_300_Series_Barricade_Tapes_Data_Sheet_78_8125_9670_4_F.pdf</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.adafruit.com/product/358</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.adafruit.com/product/358</t>
         </is>
@@ -3606,14 +3613,10 @@
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">United States</t>
-        </is>
-      </c>
+      <c r="M33"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mouser</t>
+          <t xml:space="preserve">Adafruit</t>
         </is>
       </c>
       <c r="O33"/>
@@ -3641,9 +3644,7 @@
       <c r="W33">
         <v>59.85</v>
       </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
+      <c r="X33"/>
       <c r="Y33">
         <v>0</v>
       </c>
@@ -3685,14 +3686,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1872V</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-H3EF1872V</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3795,14 +3796,14 @@
           <t xml:space="preserve">0402</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04024K12FKED</t>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW04024K12FKED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3905,14 +3906,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4642ELF</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4642ELF</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4015,14 +4016,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-1181ELF</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-1181ELF</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4125,14 +4126,14 @@
           <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps3700</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS3700DDCR</t>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS3700DDCR</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4231,14 +4232,14 @@
           <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL21A106KOQNNN</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A106KOQNNNE</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL21A106KOQNNNE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4337,14 +4338,14 @@
           <t xml:space="preserve">SOT-23-5</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/ts5a3166</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TS5A3166DBVR</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TS5A3166DBVR</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4443,14 +4444,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116040.pdf</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116040</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116040</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4553,14 +4554,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4700ELF</t>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4700ELF</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4663,14 +4664,14 @@
           <t xml:space="preserve">Bulk</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/61300411121.pdf</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300411121</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=61300411121</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4769,14 +4770,14 @@
           <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.analog.com/MAX4995B/datasheet</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Analog-Devices-Maxim-Integrated/MAX4995BAUT%2bT</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=MAX4995BAUT_T</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4875,14 +4876,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20008/dcrcw.pdf</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603133KFKTA</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW0603133KFKTA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4985,14 +4986,14 @@
           <t xml:space="preserve">SOT-23-5</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/sn74lvc1g08</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G08DBVT</t>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1G08DBVT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5091,14 +5092,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-22R0ELF</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-22R0ELF</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5201,14 +5202,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3300ELF</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-3300ELF</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5311,14 +5312,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B222KB5NNN</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B222KB5NNNC</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B222KB5NNNC</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5417,14 +5418,14 @@
           <t xml:space="preserve">VQFN-HR-10</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps25947</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS259470LRPWR</t>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS259470LRPWR</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5523,14 +5524,14 @@
           <t xml:space="preserve">SOT-583-8</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps62933p</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS62933PDRLR</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS62933PDRLR</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5629,14 +5630,14 @@
           <t xml:space="preserve">0402</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0402FR-0710KL</t>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=RC0402FR-0710KL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5735,14 +5736,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-5101ELF</t>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-5101ELF</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5845,14 +5846,14 @@
           <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060RS75000.pdf</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060RS75000</t>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=150060RS75000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5951,14 +5952,14 @@
           <t xml:space="preserve">SOD-923-2</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.onsemi.com/pub/Collateral/ESD9X3.3ST5G-D.PDF</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/ESD9X5.0ST5G</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ESD9X5.0ST5G</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6057,14 +6058,14 @@
           <t xml:space="preserve">LQFP-144</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.st.com/resource/en/datasheet/stm32h753vi.pdf</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/STMicroelectronics/STM32H753ZIT6</t>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=STM32H753ZIT6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6163,14 +6164,14 @@
           <t xml:space="preserve">Tray</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/201/1/1043.pdf</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Keystone-Electronics/1043</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=1043</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6269,14 +6270,14 @@
           <t xml:space="preserve">Reel</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://ckswitches.com/media/1471/pts645.pdf</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/PTS645SM43SMTR92-LFS</t>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=PTS645SM43SMTR92LFS</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6371,14 +6372,14 @@
           <t xml:space="preserve">Reel</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/srp7028a.pdf</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/SRP7028A-4R7M</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SRP7028A-4R7M</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6477,14 +6478,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/72/1/PYU_RT_1_TO_0_01_ROHS_L.pdf</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RT0603BRD0794K2L</t>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=RT0603BRD0794K2L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6587,14 +6588,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C220JB5NNN</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C220JB5NNNC</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C220JB5NNNC</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6693,14 +6694,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C100JB5NNN</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C100JB5NNNC</t>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C100JB5NNNC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6799,14 +6800,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C750JB5NNN</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C750JB5NNNC</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C750JB5NNNC</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6901,14 +6902,14 @@
           <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://s3.us-west-2.amazonaws.com/catsy.557/Dialight_datasheet_599_Single-Color_0805_2_Taiwan.pdf</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Dialight/599-0160-137F</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=599-0160-137F</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7007,14 +7008,14 @@
           <t xml:space="preserve">1206 (3216 metric)</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL31A226KAHNNN</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A226KAHNNNE</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL31A226KAHNNNE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7113,14 +7114,14 @@
           <t xml:space="preserve">VQFN-12</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tps2121</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS2121RUXR</t>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS2121RUXR</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7219,14 +7220,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6652ELF</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-6652ELF</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7329,14 +7330,14 @@
           <t xml:space="preserve">Top-Mount</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Global_Connector_Technology_usb4105.pdf</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/GCT/USB4105-GF-A</t>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=USB4105-GF-A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7435,14 +7436,14 @@
           <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL21A475KAQNNN</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A475KAQNNNE</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL21A475KAQNNNE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7541,14 +7542,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0603FR-07220RL</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=RC0603FR-07220RL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7647,14 +7648,14 @@
           <t xml:space="preserve">SC-59-3 (SOT-23-3)</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/tpd2e009</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPD2E009DBZR</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TPD2E009DBZR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7753,14 +7754,14 @@
           <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060GS75000.pdf</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060GS75000</t>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=150060GS75000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7859,14 +7860,14 @@
           <t xml:space="preserve">0402 (1005 metric)</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B332KB5NNN</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B332KB5NNNC</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B332KB5NNNC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7965,14 +7966,14 @@
           <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/sn74ahc1g125</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74AHC1G125DRLR</t>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74AHC1G125DRLR</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8067,14 +8068,14 @@
         </is>
       </c>
       <c r="G75"/>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Yamaichi%20Electronics_08162018_IC51-0644-807_H.pdf</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Yamaichi-Electronics/IC51-0644-807</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=IC51-0644-807</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8173,14 +8174,14 @@
           <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/sn74lvc1gu04</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1GU04DRLR</t>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1GU04DRLR</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8279,14 +8280,14 @@
           <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A475KO8NNN</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A475KO8NNNC</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A475KO8NNNC</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8385,14 +8386,14 @@
           <t xml:space="preserve">VSSOP-8</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.ti.com/lit/gpn/txs0102</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TXS0102DCUR</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=TXS0102DCUR</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8491,14 +8492,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/PYu-AC_51_RoHS_L_11.pdf</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/AC0603FR-07255KL</t>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=AC0603FR-07255KL</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8601,14 +8602,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06035K05FKEA</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW06035K05FKEA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8711,14 +8712,14 @@
           <t xml:space="preserve">Reel</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://ckswitches.com/media/1422/js.pdf</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/JS102011SAQN</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=JS102011SAQN</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8817,14 +8818,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.rohm.com/datasheet?p=KTR03EZPF</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ROHM-Semiconductor/KTR03EZPF3403</t>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=KTR03EZPF3403</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8927,14 +8928,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.vishay.com/docs/20008/dcrcw.pdf</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06033R32FKTA</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW06033R32FKTA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9037,14 +9038,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6800ELF</t>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-6800ELF</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9147,14 +9148,14 @@
           <t xml:space="preserve">0805 (2012 metric)</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/742792022.pdf</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/742792022</t>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=742792022</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9253,14 +9254,14 @@
           <t xml:space="preserve">0603</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116151.pdf</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116151</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116151</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9363,14 +9364,14 @@
           <t xml:space="preserve">0402</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/AOA0000C331.pdf</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-PA2F1242X</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-PA2F1242X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9473,14 +9474,14 @@
           <t xml:space="preserve">Tray</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qsh.pdf</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QSH-060-01-H-D-A</t>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=QSH-060-01-H-D-A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9579,14 +9580,14 @@
           <t xml:space="preserve">0603 (1608 metric)</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A105KB8NNN</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A105KB8NNNC</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A105KB8NNNC</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9653,5 +9654,183 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Z89"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="I2" r:id="rId2"/>
+    <hyperlink ref="H3" r:id="rId3"/>
+    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink ref="H4" r:id="rId5"/>
+    <hyperlink ref="I4" r:id="rId6"/>
+    <hyperlink ref="H5" r:id="rId7"/>
+    <hyperlink ref="I5" r:id="rId8"/>
+    <hyperlink ref="H6" r:id="rId9"/>
+    <hyperlink ref="I6" r:id="rId10"/>
+    <hyperlink ref="H7" r:id="rId11"/>
+    <hyperlink ref="I7" r:id="rId12"/>
+    <hyperlink ref="H8" r:id="rId13"/>
+    <hyperlink ref="I8" r:id="rId14"/>
+    <hyperlink ref="H9" r:id="rId15"/>
+    <hyperlink ref="I9" r:id="rId16"/>
+    <hyperlink ref="H10" r:id="rId17"/>
+    <hyperlink ref="I10" r:id="rId18"/>
+    <hyperlink ref="H11" r:id="rId19"/>
+    <hyperlink ref="I11" r:id="rId20"/>
+    <hyperlink ref="H12" r:id="rId21"/>
+    <hyperlink ref="I12" r:id="rId22"/>
+    <hyperlink ref="H13" r:id="rId23"/>
+    <hyperlink ref="I13" r:id="rId24"/>
+    <hyperlink ref="H14" r:id="rId25"/>
+    <hyperlink ref="I14" r:id="rId26"/>
+    <hyperlink ref="H15" r:id="rId27"/>
+    <hyperlink ref="I15" r:id="rId28"/>
+    <hyperlink ref="H16" r:id="rId29"/>
+    <hyperlink ref="I16" r:id="rId30"/>
+    <hyperlink ref="H17" r:id="rId31"/>
+    <hyperlink ref="I17" r:id="rId32"/>
+    <hyperlink ref="H18" r:id="rId33"/>
+    <hyperlink ref="I18" r:id="rId34"/>
+    <hyperlink ref="H19" r:id="rId35"/>
+    <hyperlink ref="I19" r:id="rId36"/>
+    <hyperlink ref="H20" r:id="rId37"/>
+    <hyperlink ref="I20" r:id="rId38"/>
+    <hyperlink ref="H21" r:id="rId39"/>
+    <hyperlink ref="I21" r:id="rId40"/>
+    <hyperlink ref="H22" r:id="rId41"/>
+    <hyperlink ref="I22" r:id="rId42"/>
+    <hyperlink ref="H23" r:id="rId43"/>
+    <hyperlink ref="I23" r:id="rId44"/>
+    <hyperlink ref="H24" r:id="rId45"/>
+    <hyperlink ref="I24" r:id="rId46"/>
+    <hyperlink ref="H25" r:id="rId47"/>
+    <hyperlink ref="I25" r:id="rId48"/>
+    <hyperlink ref="H26" r:id="rId49"/>
+    <hyperlink ref="I26" r:id="rId50"/>
+    <hyperlink ref="H27" r:id="rId51"/>
+    <hyperlink ref="I27" r:id="rId52"/>
+    <hyperlink ref="H28" r:id="rId53"/>
+    <hyperlink ref="I28" r:id="rId54"/>
+    <hyperlink ref="H29" r:id="rId55"/>
+    <hyperlink ref="I29" r:id="rId56"/>
+    <hyperlink ref="H30" r:id="rId57"/>
+    <hyperlink ref="I30" r:id="rId58"/>
+    <hyperlink ref="H31" r:id="rId59"/>
+    <hyperlink ref="I31" r:id="rId60"/>
+    <hyperlink ref="H32" r:id="rId61"/>
+    <hyperlink ref="I32" r:id="rId62"/>
+    <hyperlink ref="H33" r:id="rId63"/>
+    <hyperlink ref="I33" r:id="rId64"/>
+    <hyperlink ref="H34" r:id="rId65"/>
+    <hyperlink ref="I34" r:id="rId66"/>
+    <hyperlink ref="H35" r:id="rId67"/>
+    <hyperlink ref="I35" r:id="rId68"/>
+    <hyperlink ref="H36" r:id="rId69"/>
+    <hyperlink ref="I36" r:id="rId70"/>
+    <hyperlink ref="H37" r:id="rId71"/>
+    <hyperlink ref="I37" r:id="rId72"/>
+    <hyperlink ref="H38" r:id="rId73"/>
+    <hyperlink ref="I38" r:id="rId74"/>
+    <hyperlink ref="H39" r:id="rId75"/>
+    <hyperlink ref="I39" r:id="rId76"/>
+    <hyperlink ref="H40" r:id="rId77"/>
+    <hyperlink ref="I40" r:id="rId78"/>
+    <hyperlink ref="H41" r:id="rId79"/>
+    <hyperlink ref="I41" r:id="rId80"/>
+    <hyperlink ref="H42" r:id="rId81"/>
+    <hyperlink ref="I42" r:id="rId82"/>
+    <hyperlink ref="H43" r:id="rId83"/>
+    <hyperlink ref="I43" r:id="rId84"/>
+    <hyperlink ref="H44" r:id="rId85"/>
+    <hyperlink ref="I44" r:id="rId86"/>
+    <hyperlink ref="H45" r:id="rId87"/>
+    <hyperlink ref="I45" r:id="rId88"/>
+    <hyperlink ref="H46" r:id="rId89"/>
+    <hyperlink ref="I46" r:id="rId90"/>
+    <hyperlink ref="H47" r:id="rId91"/>
+    <hyperlink ref="I47" r:id="rId92"/>
+    <hyperlink ref="H48" r:id="rId93"/>
+    <hyperlink ref="I48" r:id="rId94"/>
+    <hyperlink ref="H49" r:id="rId95"/>
+    <hyperlink ref="I49" r:id="rId96"/>
+    <hyperlink ref="H50" r:id="rId97"/>
+    <hyperlink ref="I50" r:id="rId98"/>
+    <hyperlink ref="H51" r:id="rId99"/>
+    <hyperlink ref="I51" r:id="rId100"/>
+    <hyperlink ref="H52" r:id="rId101"/>
+    <hyperlink ref="I52" r:id="rId102"/>
+    <hyperlink ref="H53" r:id="rId103"/>
+    <hyperlink ref="I53" r:id="rId104"/>
+    <hyperlink ref="H54" r:id="rId105"/>
+    <hyperlink ref="I54" r:id="rId106"/>
+    <hyperlink ref="H55" r:id="rId107"/>
+    <hyperlink ref="I55" r:id="rId108"/>
+    <hyperlink ref="H56" r:id="rId109"/>
+    <hyperlink ref="I56" r:id="rId110"/>
+    <hyperlink ref="H57" r:id="rId111"/>
+    <hyperlink ref="I57" r:id="rId112"/>
+    <hyperlink ref="H58" r:id="rId113"/>
+    <hyperlink ref="I58" r:id="rId114"/>
+    <hyperlink ref="H59" r:id="rId115"/>
+    <hyperlink ref="I59" r:id="rId116"/>
+    <hyperlink ref="H60" r:id="rId117"/>
+    <hyperlink ref="I60" r:id="rId118"/>
+    <hyperlink ref="H61" r:id="rId119"/>
+    <hyperlink ref="I61" r:id="rId120"/>
+    <hyperlink ref="H62" r:id="rId121"/>
+    <hyperlink ref="I62" r:id="rId122"/>
+    <hyperlink ref="H63" r:id="rId123"/>
+    <hyperlink ref="I63" r:id="rId124"/>
+    <hyperlink ref="H64" r:id="rId125"/>
+    <hyperlink ref="I64" r:id="rId126"/>
+    <hyperlink ref="H65" r:id="rId127"/>
+    <hyperlink ref="I65" r:id="rId128"/>
+    <hyperlink ref="H66" r:id="rId129"/>
+    <hyperlink ref="I66" r:id="rId130"/>
+    <hyperlink ref="H67" r:id="rId131"/>
+    <hyperlink ref="I67" r:id="rId132"/>
+    <hyperlink ref="H68" r:id="rId133"/>
+    <hyperlink ref="I68" r:id="rId134"/>
+    <hyperlink ref="H69" r:id="rId135"/>
+    <hyperlink ref="I69" r:id="rId136"/>
+    <hyperlink ref="H70" r:id="rId137"/>
+    <hyperlink ref="I70" r:id="rId138"/>
+    <hyperlink ref="H71" r:id="rId139"/>
+    <hyperlink ref="I71" r:id="rId140"/>
+    <hyperlink ref="H72" r:id="rId141"/>
+    <hyperlink ref="I72" r:id="rId142"/>
+    <hyperlink ref="H73" r:id="rId143"/>
+    <hyperlink ref="I73" r:id="rId144"/>
+    <hyperlink ref="H74" r:id="rId145"/>
+    <hyperlink ref="I74" r:id="rId146"/>
+    <hyperlink ref="H75" r:id="rId147"/>
+    <hyperlink ref="I75" r:id="rId148"/>
+    <hyperlink ref="H76" r:id="rId149"/>
+    <hyperlink ref="I76" r:id="rId150"/>
+    <hyperlink ref="H77" r:id="rId151"/>
+    <hyperlink ref="I77" r:id="rId152"/>
+    <hyperlink ref="H78" r:id="rId153"/>
+    <hyperlink ref="I78" r:id="rId154"/>
+    <hyperlink ref="H79" r:id="rId155"/>
+    <hyperlink ref="I79" r:id="rId156"/>
+    <hyperlink ref="H80" r:id="rId157"/>
+    <hyperlink ref="I80" r:id="rId158"/>
+    <hyperlink ref="H81" r:id="rId159"/>
+    <hyperlink ref="I81" r:id="rId160"/>
+    <hyperlink ref="H82" r:id="rId161"/>
+    <hyperlink ref="I82" r:id="rId162"/>
+    <hyperlink ref="H83" r:id="rId163"/>
+    <hyperlink ref="I83" r:id="rId164"/>
+    <hyperlink ref="H84" r:id="rId165"/>
+    <hyperlink ref="I84" r:id="rId166"/>
+    <hyperlink ref="H85" r:id="rId167"/>
+    <hyperlink ref="I85" r:id="rId168"/>
+    <hyperlink ref="H86" r:id="rId169"/>
+    <hyperlink ref="I86" r:id="rId170"/>
+    <hyperlink ref="H87" r:id="rId171"/>
+    <hyperlink ref="I87" r:id="rId172"/>
+    <hyperlink ref="H88" r:id="rId173"/>
+    <hyperlink ref="I88" r:id="rId174"/>
+    <hyperlink ref="H89" r:id="rId175"/>
+    <hyperlink ref="I89" r:id="rId176"/>
+  </hyperlinks>
 </worksheet>
 </file>
--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -64,13 +64,13 @@
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
-    <col min="9" max="9" width="49" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="29" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
@@ -257,7 +257,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116009</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116009</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -285,11 +285,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-560112116009</t>
-        </is>
-      </c>
+      <c r="O2"/>
       <c r="P2">
         <v>0.11</v>
       </c>
@@ -367,7 +363,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B104KO5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B104KO5NNNC</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -391,11 +387,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05B104KO5NNNC</t>
-        </is>
-      </c>
+      <c r="O3"/>
       <c r="P3">
         <v>0.1</v>
       </c>
@@ -473,7 +465,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-2102ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-2102ELF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -501,11 +493,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-2102ELF</t>
-        </is>
-      </c>
+      <c r="O4"/>
       <c r="P4">
         <v>0.1</v>
       </c>
@@ -583,7 +571,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW04023R32FKED</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04023R32FKED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -611,11 +599,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0402-3.32-E3</t>
-        </is>
-      </c>
+      <c r="O5"/>
       <c r="P5">
         <v>0.1</v>
       </c>
@@ -693,7 +677,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=QTH-060-01-L-D-A</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QTH-060-01-L-D-A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -717,11 +701,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200-QTH06001LDA</t>
-        </is>
-      </c>
+      <c r="O6"/>
       <c r="P6">
         <v>5.75</v>
       </c>
@@ -799,7 +779,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1G74DCUR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G74DCUR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,11 +803,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-SN74LVC1G74DCUR</t>
-        </is>
-      </c>
+      <c r="O7"/>
       <c r="P7">
         <v>0.6</v>
       </c>
@@ -905,7 +881,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS22917LDBVR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22917LDBVR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -929,11 +905,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS22917LDBVR</t>
-        </is>
-      </c>
+      <c r="O8"/>
       <c r="P8">
         <v>0.52</v>
       </c>
@@ -1011,7 +983,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=2N7002</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/2N7002</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1035,11 +1007,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">512-2N7002</t>
-        </is>
-      </c>
+      <c r="O9"/>
       <c r="P9">
         <v>1.09</v>
       </c>
@@ -1117,7 +1085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRG0603F1M0-10</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/TE-Connectivity-Holsworthy/CRG0603F1M0-10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1145,11 +1113,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279-CRG0603F1M0/10</t>
-        </is>
-      </c>
+      <c r="O10"/>
       <c r="P10">
         <v>0.24</v>
       </c>
@@ -1227,7 +1191,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL31A106KBHNNNE</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A106KBHNNNE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1251,11 +1215,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL31A106KBHNNNE</t>
-        </is>
-      </c>
+      <c r="O11"/>
       <c r="P11">
         <v>0.36</v>
       </c>
@@ -1333,7 +1293,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=BQ24074RGTT</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/BQ24074RGTT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1357,11 +1317,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-BQ24074RGTT</t>
-        </is>
-      </c>
+      <c r="O12"/>
       <c r="P12">
         <v>3.19</v>
       </c>
@@ -1439,7 +1395,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116004</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116004</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1467,11 +1423,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-560112116004</t>
-        </is>
-      </c>
+      <c r="O13"/>
       <c r="P13">
         <v>0.11</v>
       </c>
@@ -1549,7 +1501,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A225KO8NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A225KO8NNNC</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1573,11 +1525,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL10A225KO8NNNC</t>
-        </is>
-      </c>
+      <c r="O14"/>
       <c r="P14">
         <v>0.1</v>
       </c>
@@ -1655,7 +1603,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-H3EF1022V</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1022V</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1683,11 +1631,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">667-ERJ-H3EF1022V</t>
-        </is>
-      </c>
+      <c r="O15"/>
       <c r="P15">
         <v>0.28</v>
       </c>
@@ -1765,7 +1709,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC138AQPWREP</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC138AQPWREP</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1789,11 +1733,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-N74LVC138AQPWREP</t>
-        </is>
-      </c>
+      <c r="O16"/>
       <c r="P16">
         <v>2.73</v>
       </c>
@@ -1871,7 +1811,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=61300811121</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300811121</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1895,11 +1835,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-61300811121</t>
-        </is>
-      </c>
+      <c r="O17"/>
       <c r="P17">
         <v>0.39</v>
       </c>
@@ -1977,7 +1913,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B102KB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B102KB5NNNC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2001,11 +1937,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05B102KB5NNNC</t>
-        </is>
-      </c>
+      <c r="O18"/>
       <c r="P18">
         <v>0.1</v>
       </c>
@@ -2083,7 +2015,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW0603249KFKEC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603249KFKEC</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2111,11 +2043,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0603249KFKEC</t>
-        </is>
-      </c>
+      <c r="O19"/>
       <c r="P19">
         <v>0.25</v>
       </c>
@@ -2193,7 +2121,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=74438357010</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74438357010</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2221,11 +2149,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-74438357010</t>
-        </is>
-      </c>
+      <c r="O20"/>
       <c r="P20">
         <v>1.68</v>
       </c>
@@ -2303,7 +2227,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=MR06X4703FTL</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X4703FTL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2331,11 +2255,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791-MR06X4703FTL</t>
-        </is>
-      </c>
+      <c r="O21"/>
       <c r="P21">
         <v>0.13</v>
       </c>
@@ -2413,7 +2333,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-S03F1002V</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-S03F1002V</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2441,11 +2361,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">667-ERJ-S03F1002V</t>
-        </is>
-      </c>
+      <c r="O22"/>
       <c r="P22">
         <v>0.23</v>
       </c>
@@ -2523,7 +2439,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS22918TDBVRQ1</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2547,11 +2463,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS22918TDBVRQ1</t>
-        </is>
-      </c>
+      <c r="O23"/>
       <c r="P23">
         <v>0.76</v>
       </c>
@@ -2629,7 +2541,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=74AHC1G32QSE-7</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Diodes-Incorporated/74AHC1G32QSE-7</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2653,11 +2565,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">621-74AHC1G32QSE-7</t>
-        </is>
-      </c>
+      <c r="O24"/>
       <c r="P24">
         <v>0.14</v>
       </c>
@@ -2735,7 +2643,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-P03F1101V</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-P03F1101V</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2763,11 +2671,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">667-ERJ-P03F1101V</t>
-        </is>
-      </c>
+      <c r="O25"/>
       <c r="P25">
         <v>0.31</v>
       </c>
@@ -2845,7 +2749,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4422ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4422ELF</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2873,11 +2777,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-4422ELF</t>
-        </is>
-      </c>
+      <c r="O26"/>
       <c r="P26">
         <v>0.1</v>
       </c>
@@ -2955,7 +2855,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=74439346068</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74439346068</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2983,11 +2883,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-74439346068</t>
-        </is>
-      </c>
+      <c r="O27"/>
       <c r="P27">
         <v>4.05</v>
       </c>
@@ -3065,7 +2961,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=MR06X47R0FTL</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X47R0FTL</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3093,11 +2989,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791-MR06X47R0FTL</t>
-        </is>
-      </c>
+      <c r="O28"/>
       <c r="P28">
         <v>0.13</v>
       </c>
@@ -3175,7 +3067,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS61023DRLT</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS61023DRLT</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3199,11 +3091,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS61023DRLT</t>
-        </is>
-      </c>
+      <c r="O29"/>
       <c r="P29">
         <v>1.43</v>
       </c>
@@ -3281,7 +3169,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-3162ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3162ELF</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3309,11 +3197,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-3162ELF</t>
-        </is>
-      </c>
+      <c r="O30"/>
       <c r="P30">
         <v>0.1</v>
       </c>
@@ -3391,7 +3275,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ABM8-25.000MHZ-B2-T</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ABRACON/ABM8-25.000MHZ-B2-T</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3415,11 +3299,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815-ABM8-25-B2-T</t>
-        </is>
-      </c>
+      <c r="O31"/>
       <c r="P31">
         <v>0.5</v>
       </c>
@@ -3497,7 +3377,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=EG1218</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/E-Switch/EG1218</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3521,11 +3401,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">612-EG1218</t>
-        </is>
-      </c>
+      <c r="O32"/>
       <c r="P32">
         <v>0.71</v>
       </c>
@@ -3693,7 +3569,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-H3EF1872V</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1872V</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3721,11 +3597,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">667-ERJ-H3EF1872V</t>
-        </is>
-      </c>
+      <c r="O34"/>
       <c r="P34">
         <v>0.28</v>
       </c>
@@ -3803,7 +3675,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW04024K12FKED</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04024K12FKED</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3831,11 +3703,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0402-4.12K-E3</t>
-        </is>
-      </c>
+      <c r="O35"/>
       <c r="P35">
         <v>0.15</v>
       </c>
@@ -3913,7 +3781,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4642ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4642ELF</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3941,11 +3809,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-4642ELF</t>
-        </is>
-      </c>
+      <c r="O36"/>
       <c r="P36">
         <v>0.1</v>
       </c>
@@ -4023,7 +3887,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-1181ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-1181ELF</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4051,11 +3915,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-1181ELF</t>
-        </is>
-      </c>
+      <c r="O37"/>
       <c r="P37">
         <v>0.1</v>
       </c>
@@ -4133,7 +3993,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS3700DDCR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS3700DDCR</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4157,11 +4017,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS3700DDCR</t>
-        </is>
-      </c>
+      <c r="O38"/>
       <c r="P38">
         <v>2.52</v>
       </c>
@@ -4239,7 +4095,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL21A106KOQNNNE</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A106KOQNNNE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4263,11 +4119,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL21A106KOQNNNE</t>
-        </is>
-      </c>
+      <c r="O39"/>
       <c r="P39">
         <v>0.11</v>
       </c>
@@ -4345,7 +4197,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TS5A3166DBVR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TS5A3166DBVR</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4369,11 +4221,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TS5A3166DBVR</t>
-        </is>
-      </c>
+      <c r="O40"/>
       <c r="P40">
         <v>0.43</v>
       </c>
@@ -4451,7 +4299,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116040</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116040</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4479,11 +4327,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-560112116040</t>
-        </is>
-      </c>
+      <c r="O41"/>
       <c r="P41">
         <v>0.11</v>
       </c>
@@ -4561,7 +4405,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-4700ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4700ELF</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4589,11 +4433,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-4700ELF</t>
-        </is>
-      </c>
+      <c r="O42"/>
       <c r="P42">
         <v>0.1</v>
       </c>
@@ -4671,7 +4511,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=61300411121</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/61300411121</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4695,11 +4535,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-61300411121</t>
-        </is>
-      </c>
+      <c r="O43"/>
       <c r="P43">
         <v>0.19</v>
       </c>
@@ -4777,7 +4613,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=MAX4995BAUT_T</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Analog-Devices-Maxim-Integrated/MAX4995BAUT%2bT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4801,11 +4637,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700-MAX4995BAUTT</t>
-        </is>
-      </c>
+      <c r="O44"/>
       <c r="P44">
         <v>6.99</v>
       </c>
@@ -4883,7 +4715,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW0603133KFKTA</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW0603133KFKTA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4911,11 +4743,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0603-133K</t>
-        </is>
-      </c>
+      <c r="O45"/>
       <c r="P45">
         <v>0.16</v>
       </c>
@@ -4993,7 +4821,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1G08DBVT</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1G08DBVT</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5017,11 +4845,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-SN74LVC1G08DBVT</t>
-        </is>
-      </c>
+      <c r="O46"/>
       <c r="P46">
         <v>0.9</v>
       </c>
@@ -5099,7 +4923,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-22R0ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-22R0ELF</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5127,11 +4951,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-22R0ELF</t>
-        </is>
-      </c>
+      <c r="O47"/>
       <c r="P47">
         <v>0.1</v>
       </c>
@@ -5209,7 +5029,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-3300ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3300ELF</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5237,11 +5057,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-3300ELF</t>
-        </is>
-      </c>
+      <c r="O48"/>
       <c r="P48">
         <v>0.1</v>
       </c>
@@ -5319,7 +5135,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B222KB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B222KB5NNNC</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5343,11 +5159,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05B222KB5NNNC</t>
-        </is>
-      </c>
+      <c r="O49"/>
       <c r="P49">
         <v>0.1</v>
       </c>
@@ -5425,7 +5237,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS259470LRPWR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS259470LRPWR</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5449,11 +5261,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS259470LRPWR</t>
-        </is>
-      </c>
+      <c r="O50"/>
       <c r="P50">
         <v>1.71</v>
       </c>
@@ -5531,7 +5339,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS62933PDRLR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS62933PDRLR</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5555,11 +5363,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS62933PDRLR</t>
-        </is>
-      </c>
+      <c r="O51"/>
       <c r="P51">
         <v>1.38</v>
       </c>
@@ -5637,7 +5441,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=RC0402FR-0710KL</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0402FR-0710KL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5661,11 +5465,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">603-RC0402FR-0710KL</t>
-        </is>
-      </c>
+      <c r="O52"/>
       <c r="P52">
         <v>0.1</v>
       </c>
@@ -5743,7 +5543,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-5101ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-5101ELF</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5771,11 +5571,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-5101ELF</t>
-        </is>
-      </c>
+      <c r="O53"/>
       <c r="P53">
         <v>0.1</v>
       </c>
@@ -5853,7 +5649,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=150060RS75000</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060RS75000</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5877,11 +5673,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-150060RS75000</t>
-        </is>
-      </c>
+      <c r="O54"/>
       <c r="P54">
         <v>0.16</v>
       </c>
@@ -5959,7 +5751,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ESD9X5.0ST5G</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/ESD9X5.0ST5G</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5983,11 +5775,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">863-ESD9X5.0ST5G</t>
-        </is>
-      </c>
+      <c r="O55"/>
       <c r="P55">
         <v>0.16</v>
       </c>
@@ -6065,7 +5853,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=STM32H753ZIT6</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/STMicroelectronics/STM32H753ZIT6</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6089,11 +5877,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">511-STM32H753ZIT6</t>
-        </is>
-      </c>
+      <c r="O56"/>
       <c r="P56">
         <v>17.13</v>
       </c>
@@ -6171,7 +5955,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=1043</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Keystone-Electronics/1043</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6195,11 +5979,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">534-1043</t>
-        </is>
-      </c>
+      <c r="O57"/>
       <c r="P57">
         <v>2.99</v>
       </c>
@@ -6277,7 +6057,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=PTS645SM43SMTR92LFS</t>
+          <t xml:space="preserve">https://www.mouser.com/ProductDetail/CK/PTS645SM43SMTR92LFS</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6301,11 +6081,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">611-PTS645SM43SMTR92</t>
-        </is>
-      </c>
+      <c r="O58"/>
       <c r="P58">
         <v>0.36</v>
       </c>
@@ -6379,7 +6155,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SRP7028A-4R7M</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/SRP7028A-4R7M</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6403,11 +6179,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-SRP7028A-4R7M</t>
-        </is>
-      </c>
+      <c r="O59"/>
       <c r="P59">
         <v>1.1</v>
       </c>
@@ -6485,7 +6257,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=RT0603BRD0794K2L</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RT0603BRD0794K2L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6513,11 +6285,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">603-RT0603BRD0794K2L</t>
-        </is>
-      </c>
+      <c r="O60"/>
       <c r="P60">
         <v>0.1</v>
       </c>
@@ -6595,7 +6363,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C220JB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C220JB5NNNC</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6619,11 +6387,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05C220JB5NNNC</t>
-        </is>
-      </c>
+      <c r="O61"/>
       <c r="P61">
         <v>0.1</v>
       </c>
@@ -6701,7 +6465,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C100JB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C100JB5NNNC</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6725,11 +6489,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05C100JB5NNNC</t>
-        </is>
-      </c>
+      <c r="O62"/>
       <c r="P62">
         <v>0.1</v>
       </c>
@@ -6807,7 +6567,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05C750JB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C750JB5NNNC</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6831,11 +6591,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05C750JB5NNNC</t>
-        </is>
-      </c>
+      <c r="O63"/>
       <c r="P63">
         <v>0.1</v>
       </c>
@@ -6909,7 +6665,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=599-0160-137F</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Dialight/599-0160-137F</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6933,11 +6689,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">645-599-0160-137F</t>
-        </is>
-      </c>
+      <c r="O64"/>
       <c r="P64">
         <v>0.29</v>
       </c>
@@ -7015,7 +6767,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL31A226KAHNNNE</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A226KAHNNNE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7039,11 +6791,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL31A226KAHNNNE</t>
-        </is>
-      </c>
+      <c r="O65"/>
       <c r="P65">
         <v>0.38</v>
       </c>
@@ -7121,7 +6869,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPS2121RUXR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS2121RUXR</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7145,11 +6893,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPS2121RUXR</t>
-        </is>
-      </c>
+      <c r="O66"/>
       <c r="P66">
         <v>2.44</v>
       </c>
@@ -7227,7 +6971,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-6652ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6652ELF</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7255,11 +6999,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603-FX6652ELF</t>
-        </is>
-      </c>
+      <c r="O67"/>
       <c r="P67">
         <v>0.1</v>
       </c>
@@ -7337,7 +7077,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=USB4105-GF-A</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/GCT/USB4105-GF-A?qs=KUoIvG%2F9IlY%2FMLlBMpStpA%3D%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7361,11 +7101,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">640-USB4105-GF-A</t>
-        </is>
-      </c>
+      <c r="O68"/>
       <c r="P68">
         <v>0.93</v>
       </c>
@@ -7443,7 +7179,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL21A475KAQNNNE</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A475KAQNNNE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7467,11 +7203,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL21A475KAQNNNE</t>
-        </is>
-      </c>
+      <c r="O69"/>
       <c r="P69">
         <v>0.11</v>
       </c>
@@ -7549,7 +7281,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=RC0603FR-07220RL</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0603FR-07220RL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7573,11 +7305,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">603-RC0603FR-07220RL</t>
-        </is>
-      </c>
+      <c r="O70"/>
       <c r="P70">
         <v>0.1</v>
       </c>
@@ -7655,7 +7383,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TPD2E009DBZR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPD2E009DBZR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7679,11 +7407,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TPD2E009DBZR</t>
-        </is>
-      </c>
+      <c r="O71"/>
       <c r="P71">
         <v>0.79</v>
       </c>
@@ -7761,7 +7485,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=150060GS75000</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060GS75000</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7785,11 +7509,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-150060GS75000</t>
-        </is>
-      </c>
+      <c r="O72"/>
       <c r="P72">
         <v>0.16</v>
       </c>
@@ -7867,7 +7587,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL05B332KB5NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B332KB5NNNC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7891,11 +7611,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL05B332KB5NNNC</t>
-        </is>
-      </c>
+      <c r="O73"/>
       <c r="P73">
         <v>0.1</v>
       </c>
@@ -7973,7 +7689,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74AHC1G125DRLR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74AHC1G125DRLR</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7997,11 +7713,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-SN74AHC1G125DRLR</t>
-        </is>
-      </c>
+      <c r="O74"/>
       <c r="P74">
         <v>0.22</v>
       </c>
@@ -8075,7 +7787,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=IC51-0644-807</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Yamaichi-Electronics/IC51-0644-807</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8099,11 +7811,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">945-IC51-0644-807</t>
-        </is>
-      </c>
+      <c r="O75"/>
       <c r="P75">
         <v>126.53</v>
       </c>
@@ -8181,7 +7889,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=SN74LVC1GU04DRLR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1GU04DRLR</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8205,11 +7913,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-SN74LVC1GU04DRLR</t>
-        </is>
-      </c>
+      <c r="O76"/>
       <c r="P76">
         <v>0.36</v>
       </c>
@@ -8287,7 +7991,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A475KO8NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A475KO8NNNC</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8311,11 +8015,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL10A475KO8NNNC</t>
-        </is>
-      </c>
+      <c r="O77"/>
       <c r="P77">
         <v>0.12</v>
       </c>
@@ -8393,7 +8093,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=TXS0102DCUR</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TXS0102DCUR</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8417,11 +8117,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595-TXS0102DCUR</t>
-        </is>
-      </c>
+      <c r="O78"/>
       <c r="P78">
         <v>0.63</v>
       </c>
@@ -8499,7 +8195,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=AC0603FR-07255KL</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/AC0603FR-07255KL</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8527,11 +8223,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">603-AC0603FR-07255KL</t>
-        </is>
-      </c>
+      <c r="O79"/>
       <c r="P79">
         <v>0.1</v>
       </c>
@@ -8609,7 +8301,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW06035K05FKEA</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06035K05FKEA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8637,11 +8329,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0603-5.05K-E3</t>
-        </is>
-      </c>
+      <c r="O80"/>
       <c r="P80">
         <v>0.1</v>
       </c>
@@ -8719,7 +8407,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=JS102011SAQN</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/JS102011SAQN</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8743,11 +8431,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">611-JS102011SAQN</t>
-        </is>
-      </c>
+      <c r="O81"/>
       <c r="P81">
         <v>0.84</v>
       </c>
@@ -8825,7 +8509,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=KTR03EZPF3403</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ROHM-Semiconductor/KTR03EZPF3403</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8853,11 +8537,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">755-KTR03EZPF3403</t>
-        </is>
-      </c>
+      <c r="O82"/>
       <c r="P82">
         <v>0.19</v>
       </c>
@@ -8935,7 +8615,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CRCW06033R32FKTA</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06033R32FKTA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8963,11 +8643,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71-CRCW0603-3.32</t>
-        </is>
-      </c>
+      <c r="O83"/>
       <c r="P83">
         <v>0.29</v>
       </c>
@@ -9045,7 +8721,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CR0603-FX-6800ELF</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6800ELF</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9073,11 +8749,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">652-CR0603FX-6800ELF</t>
-        </is>
-      </c>
+      <c r="O84"/>
       <c r="P84">
         <v>0.1</v>
       </c>
@@ -9155,7 +8827,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=742792022</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/742792022</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -9179,11 +8851,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-742792022</t>
-        </is>
-      </c>
+      <c r="O85"/>
       <c r="P85">
         <v>0.16</v>
       </c>
@@ -9261,7 +8929,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=560112116151</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116151</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9289,11 +8957,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710-560112116151</t>
-        </is>
-      </c>
+      <c r="O86"/>
       <c r="P86">
         <v>0.11</v>
       </c>
@@ -9371,7 +9035,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=ERJ-PA2F1242X</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-PA2F1242X</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9399,11 +9063,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">667-ERJ-PA2F1242X</t>
-        </is>
-      </c>
+      <c r="O87"/>
       <c r="P87">
         <v>0.28</v>
       </c>
@@ -9481,7 +9141,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=QSH-060-01-H-D-A</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QSH-060-01-H-D-A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9505,11 +9165,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200-QSH06001HDA</t>
-        </is>
-      </c>
+      <c r="O88"/>
       <c r="P88">
         <v>22.49</v>
       </c>
@@ -9587,7 +9243,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/c/?q=CL10A105KB8NNNC</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A105KB8NNNC</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9611,11 +9267,7 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187-CL10A105KB8NNNC</t>
-        </is>
-      </c>
+      <c r="O89"/>
       <c r="P89">
         <v>0.11</v>
       </c>

--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -74,7 +74,7 @@
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="9" customWidth="1"/>
     <col min="21" max="21" width="11" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
@@ -839,7 +839,7 @@
         <v>0.6</v>
       </c>
       <c r="R7">
-        <v>52599</v>
+        <v>52594</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>0.2</v>
       </c>
       <c r="R8">
-        <v>1496328</v>
+        <v>1496308</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>1.09</v>
       </c>
       <c r="R10">
-        <v>526042</v>
+        <v>525994</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Japan</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1475,14 +1475,20 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O13"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81-GCM1555C1HR75CA6J</t>
+        </is>
+      </c>
       <c r="P13">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="Q13">
-        <v>0.1</v>
-      </c>
-      <c r="R13"/>
+        <v>0.15</v>
+      </c>
+      <c r="R13">
+        <v>35585</v>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t xml:space="preserve">Active</t>
@@ -1492,20 +1498,22 @@
         <v>1</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V13">
-        <v>0.021</v>
+        <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.21</v>
-      </c>
-      <c r="X13"/>
+        <v>0.45</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
       <c r="Y13">
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14">
@@ -1809,7 +1817,7 @@
         <v>0.1</v>
       </c>
       <c r="R16">
-        <v>874450</v>
+        <v>874350</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2021,7 +2029,7 @@
         <v>3.12</v>
       </c>
       <c r="R18">
-        <v>21510</v>
+        <v>21500</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2783,7 +2791,7 @@
         <v>0.93</v>
       </c>
       <c r="R25">
-        <v>481287</v>
+        <v>481266</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2881,15 +2889,19 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O26"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL31A226MAHNNNE</t>
+        </is>
+      </c>
       <c r="P26">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="Q26">
-        <v>3.04</v>
+        <v>5.2</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>12611</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2903,19 +2915,19 @@
         <v>24</v>
       </c>
       <c r="V26">
-        <v>0.166</v>
+        <v>0.431</v>
       </c>
       <c r="W26">
-        <v>3.984</v>
+        <v>10.344</v>
       </c>
       <c r="X26">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>0.3143</v>
+        <v>0.8275</v>
       </c>
       <c r="Z26">
-        <v>4.2983</v>
+        <v>11.1715</v>
       </c>
     </row>
     <row r="27">
@@ -2999,7 +3011,7 @@
         <v>7.82</v>
       </c>
       <c r="R27">
-        <v>58284</v>
+        <v>58274</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3325,7 +3337,7 @@
         <v>1.43</v>
       </c>
       <c r="R30">
-        <v>47115</v>
+        <v>47090</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3533,7 +3545,7 @@
         <v>0.8</v>
       </c>
       <c r="R32">
-        <v>64742</v>
+        <v>64322</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -4165,7 +4177,7 @@
         <v>0.22</v>
       </c>
       <c r="R38">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -5143,7 +5155,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Active</t>
+          <t xml:space="preserve">New Product</t>
         </is>
       </c>
       <c r="T47">
@@ -5567,7 +5579,7 @@
         <v>0.16</v>
       </c>
       <c r="R51">
-        <v>368610</v>
+        <v>368302</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5779,7 +5791,7 @@
         <v>2.99</v>
       </c>
       <c r="R53">
-        <v>9773</v>
+        <v>9743</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5987,15 +5999,19 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O55"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05C100JB5NNWC</t>
+        </is>
+      </c>
       <c r="P55">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="Q55">
-        <v>0.3</v>
+        <v>0.69</v>
       </c>
       <c r="R55">
-        <v>118171</v>
+        <v>99958</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -6009,19 +6025,19 @@
         <v>10</v>
       </c>
       <c r="V55">
-        <v>0.019</v>
+        <v>0.081</v>
       </c>
       <c r="W55">
-        <v>0.19</v>
+        <v>0.81</v>
       </c>
       <c r="X55">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="Y55">
-        <v>0.0152</v>
+        <v>0.0634</v>
       </c>
       <c r="Z55">
-        <v>0.2052</v>
+        <v>0.8734</v>
       </c>
     </row>
     <row r="56">
@@ -6321,7 +6337,7 @@
         <v>11.5</v>
       </c>
       <c r="R58">
-        <v>5176</v>
+        <v>4882</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6643,7 +6659,7 @@
         <v>2.44</v>
       </c>
       <c r="R61">
-        <v>16194</v>
+        <v>14155</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6753,7 +6769,7 @@
         <v>0.1</v>
       </c>
       <c r="R62">
-        <v>331735</v>
+        <v>331725</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6843,7 +6859,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6851,7 +6867,11 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O63"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187-CL05B332KB5NNWC</t>
+        </is>
+      </c>
       <c r="P63">
         <v>0.1</v>
       </c>
@@ -6859,7 +6879,7 @@
         <v>0.1</v>
       </c>
       <c r="R63">
-        <v>125342</v>
+        <v>80721</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6873,19 +6893,19 @@
         <v>10</v>
       </c>
       <c r="V63">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="W63">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="X63">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y63">
-        <v>0.0096</v>
+        <v>0.013</v>
       </c>
       <c r="Z63">
-        <v>0.1296</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="64">
@@ -6969,7 +6989,7 @@
         <v>0.1</v>
       </c>
       <c r="R64">
-        <v>6976557</v>
+        <v>6731048</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -7185,7 +7205,7 @@
         <v>0.79</v>
       </c>
       <c r="R66">
-        <v>10330</v>
+        <v>4367</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -7291,7 +7311,7 @@
         <v>6.99</v>
       </c>
       <c r="R67">
-        <v>3754</v>
+        <v>3744</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -7617,7 +7637,7 @@
         <v>0.16</v>
       </c>
       <c r="R70">
-        <v>146494</v>
+        <v>146444</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -8269,7 +8289,7 @@
         <v>0.12</v>
       </c>
       <c r="R76">
-        <v>389441</v>
+        <v>385121</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -8481,7 +8501,7 @@
         <v>1.26</v>
       </c>
       <c r="R78">
-        <v>111487</v>
+        <v>111475</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -9121,14 +9141,20 @@
           <t xml:space="preserve">Mouser</t>
         </is>
       </c>
-      <c r="O84"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">611-PTS645SK43SMTR92</t>
+        </is>
+      </c>
       <c r="P84">
         <v>0.36</v>
       </c>
       <c r="Q84">
         <v>0.72</v>
       </c>
-      <c r="R84"/>
+      <c r="R84">
+        <v>87087</v>
+      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t xml:space="preserve">Active</t>
@@ -9146,12 +9172,14 @@
       <c r="W84">
         <v>2.16</v>
       </c>
-      <c r="X84"/>
+      <c r="X84">
+        <v>8.06</v>
+      </c>
       <c r="Y84">
-        <v>0</v>
+        <v>0.1741</v>
       </c>
       <c r="Z84">
-        <v>2.16</v>
+        <v>2.3341</v>
       </c>
     </row>
     <row r="85">
@@ -9345,7 +9373,7 @@
         <v>0.48</v>
       </c>
       <c r="R86">
-        <v>18238</v>
+        <v>18188</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>

--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -9,6 +9,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -40,10 +43,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -53,7 +58,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z89"/>
+  <dimension ref="A1:Z90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -62,7 +67,7 @@
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="60" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
@@ -290,10 +295,10 @@
           <t xml:space="preserve">652-CR0603FX-1181ELF</t>
         </is>
       </c>
-      <c r="P2">
+      <c r="P2" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="3">
         <v>0.1</v>
       </c>
       <c r="R2">
@@ -310,19 +315,19 @@
       <c r="U2">
         <v>10</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="3">
         <v>0.016</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="3">
         <v>0.16</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="3">
         <v>0</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="3">
         <v>0.16</v>
       </c>
     </row>
@@ -400,10 +405,10 @@
           <t xml:space="preserve">710-560112116009</t>
         </is>
       </c>
-      <c r="P3">
+      <c r="P3" s="3">
         <v>0.11</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="3">
         <v>0.44</v>
       </c>
       <c r="R3">
@@ -420,19 +425,19 @@
       <c r="U3">
         <v>12</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="3">
         <v>0.102</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="3">
         <v>1.224</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="3">
         <v>0</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="3">
         <v>1.224</v>
       </c>
     </row>
@@ -467,7 +472,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -510,10 +515,10 @@
           <t xml:space="preserve">187-CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="P4">
+      <c r="P4" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="3">
         <v>6</v>
       </c>
       <c r="R4">
@@ -530,19 +535,19 @@
       <c r="U4">
         <v>180</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="3">
         <v>0.01</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="3">
         <v>1.8</v>
       </c>
       <c r="X4">
         <v>8</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="3">
         <v>0.144</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="3">
         <v>1.944</v>
       </c>
     </row>
@@ -620,10 +625,10 @@
           <t xml:space="preserve">71-CRCW0402-3.32-E3</t>
         </is>
       </c>
-      <c r="P5">
+      <c r="P5" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="3">
         <v>0.1</v>
       </c>
       <c r="R5">
@@ -640,19 +645,19 @@
       <c r="U5">
         <v>10</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="3">
         <v>0.025</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="3">
         <v>0.25</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="3">
         <v>0.025</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="3">
         <v>0.275</v>
       </c>
     </row>
@@ -726,10 +731,10 @@
           <t xml:space="preserve">621-74AHC1G32QSE-7</t>
         </is>
       </c>
-      <c r="P6">
+      <c r="P6" s="3">
         <v>0.14</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="3">
         <v>0.56</v>
       </c>
       <c r="R6">
@@ -746,19 +751,19 @@
       <c r="U6">
         <v>12</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="3">
         <v>0.092</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="3">
         <v>1.104</v>
       </c>
       <c r="X6">
         <v>37.86</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="3">
         <v>0.418</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="3">
         <v>1.522</v>
       </c>
     </row>
@@ -832,10 +837,10 @@
           <t xml:space="preserve">595-SN74LVC1G74DCUR</t>
         </is>
       </c>
-      <c r="P7">
+      <c r="P7" s="3">
         <v>0.6</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="3">
         <v>0.6</v>
       </c>
       <c r="R7">
@@ -852,19 +857,19 @@
       <c r="U7">
         <v>3</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="3">
         <v>0.6</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="3">
         <v>1.8</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="3">
         <v>0.144</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="3">
         <v>1.944</v>
       </c>
     </row>
@@ -942,10 +947,10 @@
           <t xml:space="preserve">652-CR0603FX-5101ELF</t>
         </is>
       </c>
-      <c r="P8">
+      <c r="P8" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="3">
         <v>0.2</v>
       </c>
       <c r="R8">
@@ -962,19 +967,19 @@
       <c r="U8">
         <v>10</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="3">
         <v>0.012</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="3">
         <v>0.12</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="3">
         <v>0</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="3">
         <v>0.12</v>
       </c>
     </row>
@@ -1048,10 +1053,10 @@
           <t xml:space="preserve">595-TPS22917LDBVR</t>
         </is>
       </c>
-      <c r="P9">
+      <c r="P9" s="3">
         <v>0.52</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="3">
         <v>3.64</v>
       </c>
       <c r="R9">
@@ -1068,19 +1073,19 @@
       <c r="U9">
         <v>21</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="3">
         <v>0.367</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="3">
         <v>7.707</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="3">
         <v>0</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="3">
         <v>7.707</v>
       </c>
     </row>
@@ -1154,10 +1159,10 @@
           <t xml:space="preserve">512-2N7002</t>
         </is>
       </c>
-      <c r="P10">
+      <c r="P10" s="3">
         <v>1.09</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="3">
         <v>1.09</v>
       </c>
       <c r="R10">
@@ -1174,19 +1179,19 @@
       <c r="U10">
         <v>3</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="3">
         <v>1.09</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="3">
         <v>3.27</v>
       </c>
       <c r="X10">
         <v>7.98</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="3">
         <v>0.2609</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="3">
         <v>3.5309</v>
       </c>
     </row>
@@ -1206,12 +1211,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL31A106KBHNNNE</t>
+          <t xml:space="preserve">CC1206MKX5R9BB106</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1221,17 +1226,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206 (3216 metric)</t>
+          <t xml:space="preserve">1206</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL31A106KBHNNN</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/upy-gphc_x5r_4v-to-50v.pdf</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A106KBHNNNE?qs=X6jEic%2FHinBsSMnC%2FFnmbg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/CC1206MKX5R9BB106?qs=W0yvOO0ixfEGA7Mg821gyg%3D%3D</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1251,7 +1256,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1261,17 +1266,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL31A106KBHNNNE</t>
-        </is>
-      </c>
-      <c r="P11">
-        <v>0.36</v>
-      </c>
-      <c r="Q11">
-        <v>1.8</v>
+          <t xml:space="preserve">603-CC1206MKX5R9BB10</t>
+        </is>
+      </c>
+      <c r="P11" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2431</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1284,20 +1289,20 @@
       <c r="U11">
         <v>15</v>
       </c>
-      <c r="V11">
-        <v>0.155</v>
-      </c>
-      <c r="W11">
-        <v>2.325</v>
+      <c r="V11" s="3">
+        <v>0.306</v>
+      </c>
+      <c r="W11" s="3">
+        <v>4.59</v>
       </c>
       <c r="X11">
-        <v>8.06</v>
-      </c>
-      <c r="Y11">
-        <v>0.1874</v>
-      </c>
-      <c r="Z11">
-        <v>2.5124</v>
+        <v>8.04</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.369</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>4.959</v>
       </c>
     </row>
     <row r="12">
@@ -1370,10 +1375,10 @@
           <t xml:space="preserve">595-BQ24074RGTT</t>
         </is>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <v>3.19</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="3">
         <v>3.19</v>
       </c>
       <c r="R12">
@@ -1390,19 +1395,19 @@
       <c r="U12">
         <v>3</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="3">
         <v>3.19</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="3">
         <v>9.57</v>
       </c>
       <c r="X12">
         <v>37.93</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="3">
         <v>3.6299</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="3">
         <v>13.1999</v>
       </c>
     </row>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1480,10 +1485,10 @@
           <t xml:space="preserve">81-GCM1555C1HR75CA6J</t>
         </is>
       </c>
-      <c r="P13">
+      <c r="P13" s="3">
         <v>0.15</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="3">
         <v>0.15</v>
       </c>
       <c r="R13">
@@ -1500,19 +1505,19 @@
       <c r="U13">
         <v>3</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="3">
         <v>0.15</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="3">
         <v>0.45</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="3">
         <v>0</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="3">
         <v>0.45</v>
       </c>
     </row>
@@ -1590,10 +1595,10 @@
           <t xml:space="preserve">710-560112116004</t>
         </is>
       </c>
-      <c r="P14">
+      <c r="P14" s="3">
         <v>0.11</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="3">
         <v>0.88</v>
       </c>
       <c r="R14">
@@ -1610,19 +1615,19 @@
       <c r="U14">
         <v>24</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="3">
         <v>0.102</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="3">
         <v>2.448</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="3">
         <v>2.448</v>
       </c>
     </row>
@@ -1657,7 +1662,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603 (1608 metric)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1700,10 +1705,10 @@
           <t xml:space="preserve">187-CL10A225KO8NNNC</t>
         </is>
       </c>
-      <c r="P15">
+      <c r="P15" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="3">
         <v>0.4</v>
       </c>
       <c r="R15">
@@ -1720,19 +1725,19 @@
       <c r="U15">
         <v>12</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="3">
         <v>0.033</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="3">
         <v>0.396</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="3">
         <v>0.0317</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="3">
         <v>0.4277</v>
       </c>
     </row>
@@ -1810,10 +1815,10 @@
           <t xml:space="preserve">652-CR0603FX-4700ELF</t>
         </is>
       </c>
-      <c r="P16">
+      <c r="P16" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="3">
         <v>0.1</v>
       </c>
       <c r="R16">
@@ -1830,19 +1835,19 @@
       <c r="U16">
         <v>10</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="3">
         <v>0.012</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="3">
         <v>0.12</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="3">
         <v>0</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="3">
         <v>0.12</v>
       </c>
     </row>
@@ -1916,10 +1921,10 @@
           <t xml:space="preserve">595-N74LVC138AQPWREP</t>
         </is>
       </c>
-      <c r="P17">
+      <c r="P17" s="3">
         <v>2.73</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="3">
         <v>2.73</v>
       </c>
       <c r="R17">
@@ -1936,19 +1941,19 @@
       <c r="U17">
         <v>3</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="3">
         <v>2.73</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="3">
         <v>8.19</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="3">
         <v>0</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="3">
         <v>8.19</v>
       </c>
     </row>
@@ -1981,11 +1986,7 @@
           <t xml:space="preserve">Connector_PinHeader_2.54mm:PinHeader_1x08_P2.54mm_Vertical</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulk</t>
-        </is>
-      </c>
+      <c r="G18"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/61300811121.pdf</t>
@@ -2022,10 +2023,10 @@
           <t xml:space="preserve">710-61300811121</t>
         </is>
       </c>
-      <c r="P18">
+      <c r="P18" s="3">
         <v>0.39</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="3">
         <v>3.12</v>
       </c>
       <c r="R18">
@@ -2042,19 +2043,19 @@
       <c r="U18">
         <v>25</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="3">
         <v>0.28</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="3">
         <v>7</v>
       </c>
       <c r="X18">
         <v>0</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="3">
         <v>0</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="3">
         <v>7</v>
       </c>
     </row>
@@ -2089,7 +2090,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2132,10 +2133,10 @@
           <t xml:space="preserve">187-CL05B102KB5NNNC</t>
         </is>
       </c>
-      <c r="P19">
+      <c r="P19" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="3">
         <v>0.2</v>
       </c>
       <c r="R19">
@@ -2152,19 +2153,19 @@
       <c r="U19">
         <v>10</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="3">
         <v>0.015</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="3">
         <v>0.15</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="3">
         <v>0.012</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="3">
         <v>0.162</v>
       </c>
     </row>
@@ -2242,10 +2243,10 @@
           <t xml:space="preserve">667-ERJ-P03F1101V</t>
         </is>
       </c>
-      <c r="P20">
+      <c r="P20" s="3">
         <v>0.31</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="3">
         <v>0.31</v>
       </c>
       <c r="R20">
@@ -2262,19 +2263,19 @@
       <c r="U20">
         <v>3</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="3">
         <v>0.31</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="3">
         <v>0.93</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="3">
         <v>0.93</v>
       </c>
     </row>
@@ -2352,10 +2353,10 @@
           <t xml:space="preserve">71-CRCW0603249KFKEC</t>
         </is>
       </c>
-      <c r="P21">
+      <c r="P21" s="3">
         <v>0.25</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="3">
         <v>0.25</v>
       </c>
       <c r="R21">
@@ -2372,19 +2373,19 @@
       <c r="U21">
         <v>10</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="3">
         <v>0.063</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="3">
         <v>0.63</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="3">
         <v>0</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="3">
         <v>0.63</v>
       </c>
     </row>
@@ -2417,11 +2418,7 @@
           <t xml:space="preserve">Inductor_SMD:L_Wuerth_MAPI-4030</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reel</t>
-        </is>
-      </c>
+      <c r="G22"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/74438357010.pdf</t>
@@ -2462,10 +2459,10 @@
           <t xml:space="preserve">710-74438357010</t>
         </is>
       </c>
-      <c r="P22">
+      <c r="P22" s="3">
         <v>1.68</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="3">
         <v>1.68</v>
       </c>
       <c r="R22">
@@ -2482,19 +2479,19 @@
       <c r="U22">
         <v>3</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="3">
         <v>1.68</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="3">
         <v>5.04</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="3">
         <v>5.04</v>
       </c>
     </row>
@@ -2572,10 +2569,10 @@
           <t xml:space="preserve">791-MR06X4703FTL</t>
         </is>
       </c>
-      <c r="P23">
+      <c r="P23" s="3">
         <v>0.13</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="3">
         <v>0.13</v>
       </c>
       <c r="R23">
@@ -2592,26 +2589,26 @@
       <c r="U23">
         <v>10</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="3">
         <v>0.033</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="3">
         <v>0.33</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="3">
         <v>0</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="3">
         <v>0.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">VTGT_1V1,VTGT_3V1</t>
+          <t xml:space="preserve">C11,C23</t>
         </is>
       </c>
       <c r="B24">
@@ -2619,45 +2616,49 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS22918DBVR</t>
+          <t xml:space="preserve">10u</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS22918TDBVRQ1</t>
+          <t xml:space="preserve">CC0805MKX5R7BB106</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SOT95P280X145-6N</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23-6</t>
+          <t xml:space="preserve">0805</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps22918-q1</t>
+          <t xml:space="preserve">https://www.yageogroup.com/content/datasheet/asset/file/UPY-GPHC_X5R_4V-TO-50V</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22918TDBVRQ1?qs=sGAEpiMZZMv0DJfhVcWlK1Yz3z1OExkkjE2ZiqKPcyuhsbfKfPdS3Q%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/CC0805MKX5R7BB106?qs=sGAEpiMZZMsh%252B1woXyUXjzfuHVctiE89c1qCe%2FicWOU%3D</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
-        </is>
-      </c>
-      <c r="K24"/>
+          <t xml:space="preserve">capacitor, small US symbol</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -2665,7 +2666,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2675,17 +2676,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TPS22918TDBVRQ1</t>
-        </is>
-      </c>
-      <c r="P24">
-        <v>0.76</v>
-      </c>
-      <c r="Q24">
-        <v>1.52</v>
+          <t xml:space="preserve">603-CC805MKX5R7BB106</t>
+        </is>
+      </c>
+      <c r="P24" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0.62</v>
       </c>
       <c r="R24">
-        <v>10139</v>
+        <v>1990</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,71 +2697,71 @@
         <v>1</v>
       </c>
       <c r="U24">
-        <v>6</v>
-      </c>
-      <c r="V24">
-        <v>0.76</v>
-      </c>
-      <c r="W24">
-        <v>4.56</v>
+        <v>10</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0.135</v>
+      </c>
+      <c r="W24" s="3">
+        <v>1.35</v>
       </c>
       <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>4.56</v>
+        <v>10</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0.135</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>1.485</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">USB-C1</t>
+          <t xml:space="preserve">VTGT_1V1,VTGT_3V1</t>
         </is>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">USB4105-GF-A</t>
+          <t xml:space="preserve">TPS22918DBVR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">USB4105-GF-A</t>
+          <t xml:space="preserve">TPS22918TDBVRQ1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">GCT</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:GCT_USB4105-GF-A</t>
+          <t xml:space="preserve">MyFootprints:SOT95P280X145-6N</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top-Mount</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Global_Connector_Technology_usb4105.pdf</t>
+          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps22918-q1</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/GCT/USB4105-GF-A?qs=KUoIvG%2F9IlY%2FMLlBMpStpA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS22918TDBVRQ1?qs=sGAEpiMZZMv0DJfhVcWlK1Yz3z1OExkkjE2ZiqKPcyuhsbfKfPdS3Q%3D%3D</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">USB4105-GF-A GCT USB Connectors USB Type C,2.0, Rec,SMT, 0.95mmTH Shell Stakes,G/F,RA,Top Mnt,T&amp;R datasheet, inventory, &amp; pricing.</t>
+          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
         </is>
       </c>
       <c r="K25"/>
@@ -2781,17 +2782,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">640-USB4105-GF-A</t>
-        </is>
-      </c>
-      <c r="P25">
-        <v>0.93</v>
-      </c>
-      <c r="Q25">
-        <v>0.93</v>
+          <t xml:space="preserve">595-TPS22918TDBVRQ1</t>
+        </is>
+      </c>
+      <c r="P25" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1.52</v>
       </c>
       <c r="R25">
-        <v>481266</v>
+        <v>10139</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2802,78 +2803,74 @@
         <v>1</v>
       </c>
       <c r="U25">
-        <v>3</v>
-      </c>
-      <c r="V25">
-        <v>0.93</v>
-      </c>
-      <c r="W25">
-        <v>2.79</v>
+        <v>6</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="W25" s="3">
+        <v>4.56</v>
       </c>
       <c r="X25">
-        <v>30</v>
-      </c>
-      <c r="Y25">
-        <v>0.837</v>
-      </c>
-      <c r="Z25">
-        <v>3.627</v>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>4.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4,C6,C14,C16,C45,C46,C47,C48</t>
+          <t xml:space="preserve">USB-C1</t>
         </is>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">22uF</t>
+          <t xml:space="preserve">USB4105-GF-A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL31A226MAHNNNE</t>
+          <t xml:space="preserve">USB4105-GF-A</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">GCT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_1206_3216Metric</t>
+          <t xml:space="preserve">MyFootprints:GCT_USB4105-GF-A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206 (3216 metric)</t>
+          <t xml:space="preserve">Top-Mount</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL31A226KAHNNN</t>
+          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Global_Connector_Technology_usb4105.pdf</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A226MAHNNNE?qs=xZ%2FP%252Ba9zWqY8YGNZEyQ08w%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/GCT/USB4105-GF-A?qs=KUoIvG%2F9IlY%2FMLlBMpStpA%3D%3D</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">USB4105-GF-A GCT USB Connectors USB Type C,2.0, Rec,SMT, 0.95mmTH Shell Stakes,G/F,RA,Top Mnt,T&amp;R datasheet, inventory, &amp; pricing.</t>
+        </is>
+      </c>
+      <c r="K26"/>
       <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -2881,7 +2878,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2891,17 +2888,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL31A226MAHNNNE</t>
-        </is>
-      </c>
-      <c r="P26">
-        <v>0.65</v>
-      </c>
-      <c r="Q26">
-        <v>5.2</v>
+          <t xml:space="preserve">640-USB4105-GF-A</t>
+        </is>
+      </c>
+      <c r="P26" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0.93</v>
       </c>
       <c r="R26">
-        <v>12611</v>
+        <v>481266</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2912,71 +2909,71 @@
         <v>1</v>
       </c>
       <c r="U26">
-        <v>24</v>
-      </c>
-      <c r="V26">
-        <v>0.431</v>
-      </c>
-      <c r="W26">
-        <v>10.344</v>
+        <v>3</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="W26" s="3">
+        <v>2.79</v>
       </c>
       <c r="X26">
-        <v>8</v>
-      </c>
-      <c r="Y26">
-        <v>0.8275</v>
-      </c>
-      <c r="Z26">
-        <v>11.1715</v>
+        <v>30</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0.837</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>3.627</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">R3,R8,R9,R14,R19,R38,R39,R40,R41,R42,R46,R50,R51,R52,R53,R54,R64,R66,R67,R68,R70,R71,R72,R73,R74,R75,R76,R79,R80,R81,R83,R84,R86,R90</t>
+          <t xml:space="preserve">C4,C6,C14,C16,C45,C46,C47,C48</t>
         </is>
       </c>
       <c r="B27">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">10k</t>
+          <t xml:space="preserve">22uF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERJ-S03F1002V</t>
+          <t xml:space="preserve">CL31A226MAHNNNE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panasonic</t>
+          <t xml:space="preserve">Samsung</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">1206</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDP0000/AOA0000C334.pdf</t>
+          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL31A226KAHNNN</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-S03F1002V?qs=Zyl8A9hlmJoZiGA1sKtMzw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL31A226MAHNNNE?qs=xZ%2FP%252Ba9zWqY8YGNZEyQ08w%3D%3D</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
+          <t xml:space="preserve">capacitor, small US symbol</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2991,7 +2988,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3001,17 +2998,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">667-ERJ-S03F1002V</t>
-        </is>
-      </c>
-      <c r="P27">
-        <v>0.23</v>
-      </c>
-      <c r="Q27">
-        <v>7.82</v>
+          <t xml:space="preserve">187-CL31A226MAHNNNE</t>
+        </is>
+      </c>
+      <c r="P27" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>5.2</v>
       </c>
       <c r="R27">
-        <v>58274</v>
+        <v>12611</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3022,71 +3019,71 @@
         <v>1</v>
       </c>
       <c r="U27">
-        <v>102</v>
-      </c>
-      <c r="V27">
-        <v>0.072</v>
-      </c>
-      <c r="W27">
-        <v>7.344</v>
+        <v>24</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0.431</v>
+      </c>
+      <c r="W27" s="3">
+        <v>10.344</v>
       </c>
       <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>7.344</v>
+        <v>8</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>0.8275</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>11.1715</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">L_BK1</t>
+          <t xml:space="preserve">R3,R8,R9,R14,R19,R38,R39,R40,R41,R42,R46,R50,R51,R52,R53,R54,R64,R66,R67,R68,R70,R71,R72,R73,R74,R75,R76,R79,R80,R81,R83,R84,R86,R90</t>
         </is>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.8u WE-XHMI_6060</t>
+          <t xml:space="preserve">10k</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">74439346068</t>
+          <t xml:space="preserve">ERJ-S03F1002V</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wurth Elektronik</t>
+          <t xml:space="preserve">Panasonic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inductor_SMD:L_Wuerth_XHMI-6060</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/74439346068.pdf</t>
+          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDP0000/AOA0000C334.pdf</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74439346068?qs=NSAOzM2zc%2FVj5BeHYKNgfQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-S03F1002V?qs=Zyl8A9hlmJoZiGA1sKtMzw%3D%3D</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Inductors - SMD</t>
+          <t xml:space="preserve">Resistor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3101,7 +3098,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Japan</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3111,17 +3108,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-74439346068</t>
-        </is>
-      </c>
-      <c r="P28">
-        <v>4.05</v>
-      </c>
-      <c r="Q28">
-        <v>4.05</v>
+          <t xml:space="preserve">667-ERJ-S03F1002V</t>
+        </is>
+      </c>
+      <c r="P28" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>7.82</v>
       </c>
       <c r="R28">
-        <v>6579</v>
+        <v>58274</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3132,28 +3129,28 @@
         <v>1</v>
       </c>
       <c r="U28">
-        <v>3</v>
-      </c>
-      <c r="V28">
-        <v>4.05</v>
-      </c>
-      <c r="W28">
-        <v>12.15</v>
+        <v>102</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0.072</v>
+      </c>
+      <c r="W28" s="3">
+        <v>7.344</v>
       </c>
       <c r="X28">
-        <v>35.06</v>
-      </c>
-      <c r="Y28">
-        <v>4.2598</v>
-      </c>
-      <c r="Z28">
-        <v>16.4098</v>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>7.344</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">R55</t>
+          <t xml:space="preserve">L_BK1</t>
         </is>
       </c>
       <c r="B29">
@@ -3161,42 +3158,38 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">6.8u WE-XHMI_6060</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR06X47R0FTL</t>
+          <t xml:space="preserve">74439346068</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walsin</t>
+          <t xml:space="preserve">Wurth Elektronik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Inductor_SMD:L_Wuerth_XHMI-6060</t>
+        </is>
+      </c>
+      <c r="G29"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/317/1/ASC_MR.pdf</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/74439346068.pdf</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X47R0FTL?qs=GedFDFLaBXGoJo8MM4e47Q%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/74439346068?qs=NSAOzM2zc%2FVj5BeHYKNgfQ%3D%3D</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
+          <t xml:space="preserve">Power Inductors - SMD</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3211,7 +3204,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3221,17 +3214,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">791-MR06X47R0FTL</t>
-        </is>
-      </c>
-      <c r="P29">
-        <v>0.13</v>
-      </c>
-      <c r="Q29">
-        <v>0.13</v>
+          <t xml:space="preserve">710-74439346068</t>
+        </is>
+      </c>
+      <c r="P29" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>4.05</v>
       </c>
       <c r="R29">
-        <v>49137</v>
+        <v>6579</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3242,28 +3235,28 @@
         <v>1</v>
       </c>
       <c r="U29">
-        <v>10</v>
-      </c>
-      <c r="V29">
-        <v>0.033</v>
-      </c>
-      <c r="W29">
-        <v>0.33</v>
+        <v>3</v>
+      </c>
+      <c r="V29" s="3">
+        <v>4.05</v>
+      </c>
+      <c r="W29" s="3">
+        <v>12.15</v>
       </c>
       <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0.33</v>
+        <v>35.06</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>4.2598</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>16.4098</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOOST1</t>
+          <t xml:space="preserve">R55</t>
         </is>
       </c>
       <c r="B30">
@@ -3271,45 +3264,49 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS61023</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS61023DRLT</t>
+          <t xml:space="preserve">MR06X47R0FTL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Walsin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-563</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-563-6</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.ti.com/general/docs/suppproductinfo.tsp?distId=10&amp;gotoUrl=http%3A%2F%2Fwww.ti.com%2Flit%2Fgpn%2Ftps61023</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/317/1/ASC_MR.pdf</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS61023DRLT?qs=BJlw7L4Cy78Zr3IJIU3gNw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Walsin/MR06X47R0FTL?qs=GedFDFLaBXGoJo8MM4e47Q%3D%3D</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Switching Voltage Regulators 3-A boost converter with 0.5-V ultra-low input voltage 6-SOT-5X3 -40 to 125</t>
-        </is>
-      </c>
-      <c r="K30"/>
+          <t xml:space="preserve">Resistor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -3317,7 +3314,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3327,17 +3324,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TPS61023DRLT</t>
-        </is>
-      </c>
-      <c r="P30">
-        <v>1.43</v>
-      </c>
-      <c r="Q30">
-        <v>1.43</v>
+          <t xml:space="preserve">791-MR06X47R0FTL</t>
+        </is>
+      </c>
+      <c r="P30" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0.13</v>
       </c>
       <c r="R30">
-        <v>47090</v>
+        <v>49137</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3348,28 +3345,28 @@
         <v>1</v>
       </c>
       <c r="U30">
-        <v>3</v>
-      </c>
-      <c r="V30">
-        <v>1.43</v>
-      </c>
-      <c r="W30">
-        <v>4.29</v>
+        <v>10</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0.033</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0.33</v>
       </c>
       <c r="X30">
         <v>0</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="3">
         <v>0</v>
       </c>
-      <c r="Z30">
-        <v>4.29</v>
+      <c r="Z30" s="3">
+        <v>0.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">J_SOCKET_64_1</t>
+          <t xml:space="preserve">BOOST1</t>
         </is>
       </c>
       <c r="B31">
@@ -3377,38 +3374,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IC51-0644-807</t>
+          <t xml:space="preserve">TPS61023</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IC51-0644-807</t>
+          <t xml:space="preserve">TPS61023DRLT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yamaichi Electronics</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:YAMAICHI_IC51-0644-807</t>
-        </is>
-      </c>
-      <c r="G31"/>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-563</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOT-563-6</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Yamaichi%20Electronics_08162018_IC51-0644-807_H.pdf</t>
+          <t xml:space="preserve">http://www.ti.com/general/docs/suppproductinfo.tsp?distId=10&amp;gotoUrl=http%3A%2F%2Fwww.ti.com%2Flit%2Fgpn%2Ftps61023</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Yamaichi-Electronics/IC51-0644-807?qs=nO3wRANIIvmhhPuENfC7rw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS61023DRLT?qs=BJlw7L4Cy78Zr3IJIU3gNw%3D%3D</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">IC &amp; Component Sockets</t>
+          <t xml:space="preserve">Switching Voltage Regulators 3-A boost converter with 0.5-V ultra-low input voltage 6-SOT-5X3 -40 to 125</t>
         </is>
       </c>
       <c r="K31"/>
@@ -3429,17 +3430,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">945-IC51-0644-807</t>
-        </is>
-      </c>
-      <c r="P31">
-        <v>126.53</v>
-      </c>
-      <c r="Q31">
-        <v>126.53</v>
+          <t xml:space="preserve">595-TPS61023DRLT</t>
+        </is>
+      </c>
+      <c r="P31" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>1.43</v>
       </c>
       <c r="R31">
-        <v>9</v>
+        <v>47090</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3452,69 +3453,65 @@
       <c r="U31">
         <v>3</v>
       </c>
-      <c r="V31">
-        <v>126.53</v>
-      </c>
-      <c r="W31">
-        <v>379.59</v>
+      <c r="V31" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="W31" s="3">
+        <v>4.29</v>
       </c>
       <c r="X31">
-        <v>8</v>
-      </c>
-      <c r="Y31">
-        <v>30.3672</v>
-      </c>
-      <c r="Z31">
-        <v>409.9572</v>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>4.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1,D2,D3,D4,D5</t>
+          <t xml:space="preserve">J_SOCKET_64_1</t>
         </is>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESD9X5.0ST5G</t>
+          <t xml:space="preserve">IC51-0644-807</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESD9X5.0ST5G</t>
+          <t xml:space="preserve">IC51-0644-807</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">onsemi</t>
+          <t xml:space="preserve">Yamaichi Electronics</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diode_SMD:D_SOD-923</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SOD-923-2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MyFootprints:YAMAICHI_IC51-0644-807</t>
+        </is>
+      </c>
+      <c r="G32"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://assets.nexperia.com/documents/data-sheet/PTVS5V0Z1USK.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/Yamaichi%20Electronics_08162018_IC51-0644-807_H.pdf</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/ESD9X5.0ST5G?qs=OSf9jACorvbLo4%2Fn72DVLA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Yamaichi-Electronics/IC51-0644-807?qs=nO3wRANIIvmhhPuENfC7rw%3D%3D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5V, 1200W TVS unidirectional diode, DSN1608-2</t>
+          <t xml:space="preserve">IC &amp; Component Sockets</t>
         </is>
       </c>
       <c r="K32"/>
@@ -3525,7 +3522,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3535,17 +3532,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">863-ESD9X5.0ST5G</t>
-        </is>
-      </c>
-      <c r="P32">
-        <v>0.16</v>
-      </c>
-      <c r="Q32">
-        <v>0.8</v>
+          <t xml:space="preserve">945-IC51-0644-807</t>
+        </is>
+      </c>
+      <c r="P32" s="3">
+        <v>126.53</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>126.53</v>
       </c>
       <c r="R32">
-        <v>64322</v>
+        <v>9</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3556,71 +3553,71 @@
         <v>1</v>
       </c>
       <c r="U32">
-        <v>15</v>
-      </c>
-      <c r="V32">
-        <v>0.101</v>
-      </c>
-      <c r="W32">
-        <v>1.515</v>
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
+        <v>126.53</v>
+      </c>
+      <c r="W32" s="3">
+        <v>379.59</v>
       </c>
       <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>1.515</v>
+        <v>8</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>30.3672</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>409.9572</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW_BOOT1</t>
+          <t xml:space="preserve">D1,D2,D3,D4,D5</t>
         </is>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EG1218</t>
+          <t xml:space="preserve">ESD9X5.0ST5G</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EG1218</t>
+          <t xml:space="preserve">ESD9X5.0ST5G</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-Switch</t>
+          <t xml:space="preserve">onsemi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SW_EG1218</t>
+          <t xml:space="preserve">Diode_SMD:D_SOD-923</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulk</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EG1218</t>
+          <t xml:space="preserve">SOD-923-2</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://assets.nexperia.com/documents/data-sheet/PTVS5V0Z1USK.pdf</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/E-Switch/EG1218?qs=xDsBkp9LkocT0c8K%252B5e%2FgA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/onsemi/ESD9X5.0ST5G?qs=OSf9jACorvbLo4%2Fn72DVLA%3D%3D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slide Switches</t>
+          <t xml:space="preserve">5V, 1200W TVS unidirectional diode, DSN1608-2</t>
         </is>
       </c>
       <c r="K33"/>
@@ -3641,17 +3638,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">612-EG1218</t>
-        </is>
-      </c>
-      <c r="P33">
-        <v>0.71</v>
-      </c>
-      <c r="Q33">
-        <v>0.71</v>
+          <t xml:space="preserve">863-ESD9X5.0ST5G</t>
+        </is>
+      </c>
+      <c r="P33" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>0.8</v>
       </c>
       <c r="R33">
-        <v>12328</v>
+        <v>64322</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3662,28 +3659,28 @@
         <v>1</v>
       </c>
       <c r="U33">
-        <v>3</v>
-      </c>
-      <c r="V33">
-        <v>0.71</v>
-      </c>
-      <c r="W33">
-        <v>2.13</v>
+        <v>15</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0.101</v>
+      </c>
+      <c r="W33" s="3">
+        <v>1.515</v>
       </c>
       <c r="X33">
-        <v>30</v>
-      </c>
-      <c r="Y33">
-        <v>0.639</v>
-      </c>
-      <c r="Z33">
-        <v>2.769</v>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>1.515</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCD1</t>
+          <t xml:space="preserve">SW_BOOT1</t>
         </is>
       </c>
       <c r="B34">
@@ -3691,38 +3688,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">358</t>
+          <t xml:space="preserve">EG1218</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">358</t>
+          <t xml:space="preserve">EG1218</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adafruit Industries</t>
+          <t xml:space="preserve">E-Switch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connector_PinSocket_2.54mm:PinSocket_1x10_P2.54mm_Vertical</t>
+          <t xml:space="preserve">MyFootprints:SW_EG1218</t>
         </is>
       </c>
       <c r="G34"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://cdn-shop.adafruit.com/datasheets/ST7735R_V0.2.pdf</t>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EG1218</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.digikey.com/en/products/detail/adafruit-industries-llc/358/5801368</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/E-Switch/EG1218?qs=xDsBkp9LkocT0c8K%252B5e%2FgA%3D%3D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">358</t>
+          <t xml:space="preserve">Slide Switches</t>
         </is>
       </c>
       <c r="K34"/>
@@ -3731,24 +3728,30 @@
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="M34"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DigiKey</t>
+          <t xml:space="preserve">Mouser</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">517-358</t>
-        </is>
-      </c>
-      <c r="P34">
-        <v>19.95</v>
-      </c>
-      <c r="Q34">
-        <v>19.95</v>
-      </c>
-      <c r="R34"/>
+          <t xml:space="preserve">612-EG1218</t>
+        </is>
+      </c>
+      <c r="P34" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="R34">
+        <v>12328</v>
+      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t xml:space="preserve">Active</t>
@@ -3760,67 +3763,65 @@
       <c r="U34">
         <v>3</v>
       </c>
-      <c r="V34">
-        <v>19.95</v>
-      </c>
-      <c r="W34">
-        <v>59.85</v>
-      </c>
-      <c r="X34"/>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>59.85</v>
+      <c r="V34" s="3">
+        <v>0.71</v>
+      </c>
+      <c r="W34" s="3">
+        <v>2.13</v>
+      </c>
+      <c r="X34">
+        <v>30</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0.639</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>2.769</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">J_CARDX_L_1</t>
+          <t xml:space="preserve">LCD1</t>
         </is>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">QSH-060-01-X-D-A</t>
+          <t xml:space="preserve">358</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">QSH-060-01-H-D-A</t>
+          <t xml:space="preserve">358</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samtec</t>
+          <t xml:space="preserve">Adafruit Industries</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SAMTEC_QSH-060-01-X-D-A</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tray</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Connector_PinSocket_2.54mm:PinSocket_1x10_P2.54mm_Vertical</t>
+        </is>
+      </c>
+      <c r="G35"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qsh.pdf</t>
+          <t xml:space="preserve">https://cdn-shop.adafruit.com/datasheets/ST7735R_V0.2.pdf</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QSH-060-01-H-D-A?qs=rU5fayqh%252BE34oibMPSfe5w%3D%3D</t>
+          <t xml:space="preserve">https://www.digikey.com/en/products/detail/adafruit-industries-llc/358/5801368</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
+          <t xml:space="preserve">358</t>
         </is>
       </c>
       <c r="K35"/>
@@ -3829,30 +3830,24 @@
           <t xml:space="preserve">Details</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Costa Rica</t>
-        </is>
-      </c>
+      <c r="M35"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mouser</t>
+          <t xml:space="preserve">DigiKey</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200-QSH06001HDA</t>
-        </is>
-      </c>
-      <c r="P35">
-        <v>22.49</v>
-      </c>
-      <c r="Q35">
-        <v>44.98</v>
-      </c>
-      <c r="R35">
-        <v>202</v>
-      </c>
+          <t xml:space="preserve">517-358</t>
+        </is>
+      </c>
+      <c r="P35" s="3">
+        <v>19.95</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>19.95</v>
+      </c>
+      <c r="R35"/>
       <c r="S35" t="inlineStr">
         <is>
           <t xml:space="preserve">Active</t>
@@ -3862,78 +3857,68 @@
         <v>1</v>
       </c>
       <c r="U35">
-        <v>6</v>
-      </c>
-      <c r="V35">
-        <v>22.49</v>
-      </c>
-      <c r="W35">
-        <v>134.94</v>
-      </c>
-      <c r="X35">
-        <v>6.98</v>
-      </c>
-      <c r="Y35">
-        <v>9.4188</v>
-      </c>
-      <c r="Z35">
-        <v>144.3588</v>
+        <v>3</v>
+      </c>
+      <c r="V35" s="3">
+        <v>19.95</v>
+      </c>
+      <c r="W35" s="3">
+        <v>59.85</v>
+      </c>
+      <c r="X35"/>
+      <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>59.85</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">R10</t>
+          <t xml:space="preserve">J_CARDX_L_1</t>
         </is>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.12k</t>
+          <t xml:space="preserve">QSH-060-01-X-D-A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRCW04024K12FKED</t>
+          <t xml:space="preserve">QSH-060-01-H-D-A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vishay</t>
+          <t xml:space="preserve">Samtec</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0402</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MyFootprints:SAMTEC_QSH-060-01-X-D-A</t>
+        </is>
+      </c>
+      <c r="G36"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qsh.pdf</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04024K12FKED?qs=hAuyw6LW%252BLh45zlhMS0oKQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QSH-060-01-H-D-A?qs=rU5fayqh%252BE34oibMPSfe5w%3D%3D</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
+        </is>
+      </c>
+      <c r="K36"/>
       <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -3941,7 +3926,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Costa Rica</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3951,17 +3936,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">71-CRCW0402-4.12K-E3</t>
-        </is>
-      </c>
-      <c r="P36">
-        <v>0.15</v>
-      </c>
-      <c r="Q36">
-        <v>0.15</v>
+          <t xml:space="preserve">200-QSH06001HDA</t>
+        </is>
+      </c>
+      <c r="P36" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>44.98</v>
       </c>
       <c r="R36">
-        <v>10238</v>
+        <v>202</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3972,28 +3957,28 @@
         <v>1</v>
       </c>
       <c r="U36">
-        <v>3</v>
-      </c>
-      <c r="V36">
-        <v>0.15</v>
-      </c>
-      <c r="W36">
-        <v>0.45</v>
+        <v>6</v>
+      </c>
+      <c r="V36" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="W36" s="3">
+        <v>134.94</v>
       </c>
       <c r="X36">
-        <v>10</v>
-      </c>
-      <c r="Y36">
-        <v>0.045</v>
-      </c>
-      <c r="Z36">
-        <v>0.495</v>
+        <v>6.98</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>9.4188</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>144.3588</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVP1</t>
+          <t xml:space="preserve">R10</t>
         </is>
       </c>
       <c r="B37">
@@ -4001,45 +3986,49 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS3700DDCR</t>
+          <t xml:space="preserve">4.12k</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS3700DDCR</t>
+          <t xml:space="preserve">CRCW04024K12FKED</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Vishay</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-6</t>
+          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23-6</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps3700</t>
+          <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS3700DDCR?qs=mNuCSSXMdBz5rDLbdTsfrQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW04024K12FKED?qs=hAuyw6LW%252BLh45zlhMS0oKQ%3D%3D</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analog Comparators</t>
-        </is>
-      </c>
-      <c r="K37"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -4047,7 +4036,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4057,17 +4046,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TPS3700DDCR</t>
-        </is>
-      </c>
-      <c r="P37">
-        <v>2.52</v>
-      </c>
-      <c r="Q37">
-        <v>2.52</v>
+          <t xml:space="preserve">71-CRCW0402-4.12K-E3</t>
+        </is>
+      </c>
+      <c r="P37" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>0.15</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>10238</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4080,76 +4069,72 @@
       <c r="U37">
         <v>3</v>
       </c>
-      <c r="V37">
-        <v>2.52</v>
-      </c>
-      <c r="W37">
-        <v>7.56</v>
+      <c r="V37" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="W37" s="3">
+        <v>0.45</v>
       </c>
       <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>7.56</v>
+        <v>10</v>
+      </c>
+      <c r="Y37" s="3">
+        <v>0.045</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>0.495</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">C11,C23</t>
+          <t xml:space="preserve">SPST1,SPST2,SPST3,SPST4</t>
         </is>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">10u</t>
+          <t xml:space="preserve">TS5A3166DBVR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL21A106KOQNNNE</t>
+          <t xml:space="preserve">TS5A3166DBVR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0805_2012Metric</t>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805 (2012 metric)</t>
+          <t xml:space="preserve">SOT-23-5</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL21A106KOQNNN</t>
+          <t xml:space="preserve">http://www.ti.com/lit/ds/symlink/ts5a3166.pdf</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A106KOQNNNE?qs=349EhDEZ59qKIX0T0PKtPw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TS5A3166DBVR?qs=0O%2FZFlpUpJWfi7hoK1hGig%3D%3D</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Single SPST Analog Switch, 5-V/3.3-V, normally OFF, 0.9Ohm Ron, SOT-23-5</t>
+        </is>
+      </c>
+      <c r="K38"/>
       <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -4157,7 +4142,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4167,17 +4152,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL21A106KOQNNNE</t>
-        </is>
-      </c>
-      <c r="P38">
-        <v>0.11</v>
-      </c>
-      <c r="Q38">
-        <v>0.22</v>
+          <t xml:space="preserve">595-TS5A3166DBVR</t>
+        </is>
+      </c>
+      <c r="P38" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1.72</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>6188</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4188,74 +4173,78 @@
         <v>1</v>
       </c>
       <c r="U38">
-        <v>10</v>
-      </c>
-      <c r="V38">
-        <v>0.042</v>
-      </c>
-      <c r="W38">
-        <v>0.42</v>
+        <v>12</v>
+      </c>
+      <c r="V38" s="3">
+        <v>0.302</v>
+      </c>
+      <c r="W38" s="3">
+        <v>3.624</v>
       </c>
       <c r="X38">
-        <v>8.18</v>
-      </c>
-      <c r="Y38">
-        <v>0.0344</v>
-      </c>
-      <c r="Z38">
-        <v>0.4544</v>
+        <v>7.91</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>0.2867</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>3.9107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPST1,SPST2,SPST3,SPST4</t>
+          <t xml:space="preserve">R65,R69,R77,R78,R82,R85</t>
         </is>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TS5A3166DBVR</t>
+          <t xml:space="preserve">12k</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TS5A3166DBVR</t>
+          <t xml:space="preserve">560112116040</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Wurth Elektronik</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-5</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23-5</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.ti.com/lit/ds/symlink/ts5a3166.pdf</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116040.pdf</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TS5A3166DBVR?qs=0O%2FZFlpUpJWfi7hoK1hGig%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116040?qs=mELouGlnn3eCk9Q8a0lJSQ%3D%3D</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single SPST Analog Switch, 5-V/3.3-V, normally OFF, 0.9Ohm Ron, SOT-23-5</t>
-        </is>
-      </c>
-      <c r="K39"/>
+          <t xml:space="preserve">Resistor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -4263,7 +4252,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4273,17 +4262,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TS5A3166DBVR</t>
-        </is>
-      </c>
-      <c r="P39">
-        <v>0.43</v>
-      </c>
-      <c r="Q39">
-        <v>1.72</v>
+          <t xml:space="preserve">710-560112116040</t>
+        </is>
+      </c>
+      <c r="P39" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0.66</v>
       </c>
       <c r="R39">
-        <v>6188</v>
+        <v>13073</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4294,51 +4283,51 @@
         <v>1</v>
       </c>
       <c r="U39">
-        <v>12</v>
-      </c>
-      <c r="V39">
-        <v>0.302</v>
-      </c>
-      <c r="W39">
-        <v>3.624</v>
+        <v>18</v>
+      </c>
+      <c r="V39" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="W39" s="3">
+        <v>1.836</v>
       </c>
       <c r="X39">
-        <v>7.91</v>
-      </c>
-      <c r="Y39">
-        <v>0.2867</v>
-      </c>
-      <c r="Z39">
-        <v>3.9107</v>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="3">
+        <v>1.836</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">R65,R69,R77,R78,R82,R85</t>
+          <t xml:space="preserve">C7,C9,C18,C30,C31,C70,C72,C75,C76,C77,C78,C80,C81,C82</t>
         </is>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">12k</t>
+          <t xml:space="preserve">1uF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">560112116040</t>
+          <t xml:space="preserve">CC0603KRX5R9BB105</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wurth Elektronik</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4348,17 +4337,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116040.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/upy-gphc_x5r_4v-to-50v.pdf</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116040?qs=mELouGlnn3eCk9Q8a0lJSQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/CC0603KRX5R9BB105?qs=zEY9bCHj09dqHVk4sHIcjA%3D%3D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
+          <t xml:space="preserve">capacitor, small US symbol</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4383,17 +4372,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-560112116040</t>
-        </is>
-      </c>
-      <c r="P40">
-        <v>0.11</v>
-      </c>
-      <c r="Q40">
-        <v>0.66</v>
+          <t xml:space="preserve">603-CC603KRX5R9BB105</t>
+        </is>
+      </c>
+      <c r="P40" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>3.22</v>
       </c>
       <c r="R40">
-        <v>13073</v>
+        <v>60700</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4404,22 +4393,22 @@
         <v>1</v>
       </c>
       <c r="U40">
-        <v>18</v>
-      </c>
-      <c r="V40">
-        <v>0.102</v>
-      </c>
-      <c r="W40">
-        <v>1.836</v>
+        <v>42</v>
+      </c>
+      <c r="V40" s="3">
+        <v>0.096</v>
+      </c>
+      <c r="W40" s="3">
+        <v>4.032</v>
       </c>
       <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>1.836</v>
+        <v>7.83</v>
+      </c>
+      <c r="Y40" s="3">
+        <v>0.3157</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>4.3477</v>
       </c>
     </row>
     <row r="41">
@@ -4451,11 +4440,7 @@
           <t xml:space="preserve">Connector_PinHeader_2.54mm:PinHeader_1x04_P2.54mm_Vertical</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulk</t>
-        </is>
-      </c>
+      <c r="G41"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/61300411121.pdf</t>
@@ -4492,10 +4477,10 @@
           <t xml:space="preserve">710-61300411121</t>
         </is>
       </c>
-      <c r="P41">
+      <c r="P41" s="3">
         <v>0.19</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="3">
         <v>0.57</v>
       </c>
       <c r="R41">
@@ -4512,19 +4497,19 @@
       <c r="U41">
         <v>10</v>
       </c>
-      <c r="V41">
+      <c r="V41" s="3">
         <v>0.163</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="3">
         <v>1.63</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" s="3">
         <v>0</v>
       </c>
-      <c r="Z41">
+      <c r="Z41" s="3">
         <v>1.63</v>
       </c>
     </row>
@@ -4602,10 +4587,10 @@
           <t xml:space="preserve">652-CR0603-FX6652ELF</t>
         </is>
       </c>
-      <c r="P42">
+      <c r="P42" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="3">
         <v>0.1</v>
       </c>
       <c r="R42">
@@ -4622,19 +4607,19 @@
       <c r="U42">
         <v>10</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="3">
         <v>0.016</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="3">
         <v>0.16</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="3">
         <v>0</v>
       </c>
-      <c r="Z42">
+      <c r="Z42" s="3">
         <v>0.16</v>
       </c>
     </row>
@@ -4712,10 +4697,10 @@
           <t xml:space="preserve">667-ERJ-H3EF1022V</t>
         </is>
       </c>
-      <c r="P43">
+      <c r="P43" s="3">
         <v>0.28</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="3">
         <v>0.28</v>
       </c>
       <c r="R43">
@@ -4732,19 +4717,19 @@
       <c r="U43">
         <v>3</v>
       </c>
-      <c r="V43">
+      <c r="V43" s="3">
         <v>0.28</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="3">
         <v>0.84</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43">
+      <c r="Z43" s="3">
         <v>0.84</v>
       </c>
     </row>
@@ -4822,10 +4807,10 @@
           <t xml:space="preserve">71-CRCW0603-133K</t>
         </is>
       </c>
-      <c r="P44">
+      <c r="P44" s="3">
         <v>0.16</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="3">
         <v>0.16</v>
       </c>
       <c r="R44">
@@ -4842,19 +4827,19 @@
       <c r="U44">
         <v>3</v>
       </c>
-      <c r="V44">
+      <c r="V44" s="3">
         <v>0.16</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="3">
         <v>0.48</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" s="3">
         <v>0</v>
       </c>
-      <c r="Z44">
+      <c r="Z44" s="3">
         <v>0.48</v>
       </c>
     </row>
@@ -4928,10 +4913,10 @@
           <t xml:space="preserve">595-SN74LVC1G08DBVT</t>
         </is>
       </c>
-      <c r="P45">
+      <c r="P45" s="3">
         <v>0.9</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="3">
         <v>4.5</v>
       </c>
       <c r="R45">
@@ -4948,19 +4933,19 @@
       <c r="U45">
         <v>15</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="3">
         <v>0.643</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="3">
         <v>9.645</v>
       </c>
       <c r="X45">
         <v>8</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="3">
         <v>0.7716</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="3">
         <v>10.4166</v>
       </c>
     </row>
@@ -4995,7 +4980,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5038,10 +5023,10 @@
           <t xml:space="preserve">187-CL05B222KB5NNNC</t>
         </is>
       </c>
-      <c r="P46">
+      <c r="P46" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="3">
         <v>0.1</v>
       </c>
       <c r="R46">
@@ -5058,19 +5043,19 @@
       <c r="U46">
         <v>10</v>
       </c>
-      <c r="V46">
+      <c r="V46" s="3">
         <v>0.016</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="3">
         <v>0.16</v>
       </c>
       <c r="X46">
         <v>8</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" s="3">
         <v>0.0128</v>
       </c>
-      <c r="Z46">
+      <c r="Z46" s="3">
         <v>0.1728</v>
       </c>
     </row>
@@ -5105,7 +5090,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805 (2012 metric)</t>
+          <t xml:space="preserve">0805</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5144,10 +5129,10 @@
           <t xml:space="preserve">645-599-0160-137F</t>
         </is>
       </c>
-      <c r="P47">
+      <c r="P47" s="3">
         <v>0.29</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="3">
         <v>0.87</v>
       </c>
       <c r="R47">
@@ -5164,19 +5149,19 @@
       <c r="U47">
         <v>10</v>
       </c>
-      <c r="V47">
+      <c r="V47" s="3">
         <v>0.195</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="3">
         <v>1.95</v>
       </c>
       <c r="X47">
         <v>7.93</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" s="3">
         <v>0.1546</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="3">
         <v>2.1046</v>
       </c>
     </row>
@@ -5250,10 +5235,10 @@
           <t xml:space="preserve">595-TPS259470LRPWR</t>
         </is>
       </c>
-      <c r="P48">
+      <c r="P48" s="3">
         <v>1.71</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="3">
         <v>1.71</v>
       </c>
       <c r="R48">
@@ -5270,19 +5255,19 @@
       <c r="U48">
         <v>3</v>
       </c>
-      <c r="V48">
+      <c r="V48" s="3">
         <v>1.71</v>
       </c>
-      <c r="W48">
+      <c r="W48" s="3">
         <v>5.13</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
-      <c r="Y48">
+      <c r="Y48" s="3">
         <v>0</v>
       </c>
-      <c r="Z48">
+      <c r="Z48" s="3">
         <v>5.13</v>
       </c>
     </row>
@@ -5356,10 +5341,10 @@
           <t xml:space="preserve">595-TPS62933PDRLR</t>
         </is>
       </c>
-      <c r="P49">
+      <c r="P49" s="3">
         <v>1.38</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="3">
         <v>2.76</v>
       </c>
       <c r="R49">
@@ -5376,19 +5361,19 @@
       <c r="U49">
         <v>6</v>
       </c>
-      <c r="V49">
+      <c r="V49" s="3">
         <v>1.38</v>
       </c>
-      <c r="W49">
+      <c r="W49" s="3">
         <v>8.28</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
-      <c r="Y49">
+      <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49">
+      <c r="Z49" s="3">
         <v>8.28</v>
       </c>
     </row>
@@ -5466,10 +5451,10 @@
           <t xml:space="preserve">652-CR0603FX-22R0ELF</t>
         </is>
       </c>
-      <c r="P50">
+      <c r="P50" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="3">
         <v>0.4</v>
       </c>
       <c r="R50">
@@ -5486,72 +5471,76 @@
       <c r="U50">
         <v>12</v>
       </c>
-      <c r="V50">
+      <c r="V50" s="3">
         <v>0.012</v>
       </c>
-      <c r="W50">
+      <c r="W50" s="3">
         <v>0.144</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
-      <c r="Y50">
+      <c r="Y50" s="3">
         <v>0</v>
       </c>
-      <c r="Z50">
+      <c r="Z50" s="3">
         <v>0.144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLT1</t>
+          <t xml:space="preserve">C27,C53</t>
         </is>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Red LED, V_f ~ 2.0 V typ, 0603</t>
+          <t xml:space="preserve">4.7uF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">150060RS75000</t>
+          <t xml:space="preserve">CC0805KFX5R8BB475</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wurth Elektronik</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED_SMD:LED_0603_1608Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603 (1608 metric)</t>
+          <t xml:space="preserve">0805</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060RS75000.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/upy-gphc_x5r_4v-to-50v.pdf</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060RS75000?qs=LlUlMxKIyB3QnmZ3fw%2FVCA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/CC0805KFX5R8BB475?qs=mzRxyRlhVdvf7w1%2FCVNeQQ%3D%3D</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Light emitting diode</t>
-        </is>
-      </c>
-      <c r="K51"/>
+          <t xml:space="preserve">capacitor, small US symbol</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -5559,7 +5548,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5569,17 +5558,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-150060RS75000</t>
-        </is>
-      </c>
-      <c r="P51">
-        <v>0.16</v>
-      </c>
-      <c r="Q51">
-        <v>0.16</v>
+          <t xml:space="preserve">603-CC0805KFX5R8BB47</t>
+        </is>
+      </c>
+      <c r="P51" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0.78</v>
       </c>
       <c r="R51">
-        <v>368302</v>
+        <v>19998</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5590,28 +5579,28 @@
         <v>1</v>
       </c>
       <c r="U51">
-        <v>3</v>
-      </c>
-      <c r="V51">
-        <v>0.16</v>
-      </c>
-      <c r="W51">
-        <v>0.48</v>
+        <v>10</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="W51" s="3">
+        <v>1.7</v>
       </c>
       <c r="X51">
-        <v>35</v>
-      </c>
-      <c r="Y51">
-        <v>0.168</v>
-      </c>
-      <c r="Z51">
-        <v>0.648</v>
+        <v>7.95</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0.1351</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>1.8351</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">STM32H1</t>
+          <t xml:space="preserve">FLT1</t>
         </is>
       </c>
       <c r="B52">
@@ -5619,42 +5608,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">STM32H753ZIT6</t>
+          <t xml:space="preserve">Red LED, V_f ~ 2.0 V typ, 0603</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">STM32H753ZIT6</t>
+          <t xml:space="preserve">150060RS75000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">STMicroelectronics</t>
+          <t xml:space="preserve">Wurth Elektronik</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_QFP:LQFP-144_20x20mm_P0.5mm</t>
+          <t xml:space="preserve">LED_SMD:LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">LQFP-144</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.st.com/resource/en/datasheet/stm32h753zi.pdf</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060RS75000.pdf</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/STMicroelectronics/STM32H753ZIT6?qs=u4fy%2FsgLU9PzR9vtNNw%2FMw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060RS75000?qs=LlUlMxKIyB3QnmZ3fw%2FVCA%3D%3D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">STMicroelectronics Arm Cortex-M7 MCU, 2048KB flash, 1024KB RAM, 480 MHz, 1.62-3.6V, 114 GPIO, LQFP144</t>
+          <t xml:space="preserve">Light emitting diode</t>
         </is>
       </c>
       <c r="K52"/>
@@ -5665,7 +5654,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">France</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5675,17 +5664,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">511-STM32H753ZIT6</t>
-        </is>
-      </c>
-      <c r="P52">
-        <v>17.13</v>
-      </c>
-      <c r="Q52">
-        <v>17.13</v>
+          <t xml:space="preserve">710-150060RS75000</t>
+        </is>
+      </c>
+      <c r="P52" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0.16</v>
       </c>
       <c r="R52">
-        <v>14</v>
+        <v>368302</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5698,26 +5687,26 @@
       <c r="U52">
         <v>3</v>
       </c>
-      <c r="V52">
-        <v>17.13</v>
-      </c>
-      <c r="W52">
-        <v>51.39</v>
+      <c r="V52" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0.48</v>
       </c>
       <c r="X52">
-        <v>0</v>
-      </c>
-      <c r="Y52">
-        <v>0</v>
-      </c>
-      <c r="Z52">
-        <v>51.39</v>
+        <v>35</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0.168</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0.648</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAT1</t>
+          <t xml:space="preserve">STM32H1</t>
         </is>
       </c>
       <c r="B53">
@@ -5725,42 +5714,42 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043 Holder for 18650</t>
+          <t xml:space="preserve">STM32H753ZIT6</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1043</t>
+          <t xml:space="preserve">STM32H753ZIT6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keystone</t>
+          <t xml:space="preserve">STMicroelectronics</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:BAT_1043</t>
+          <t xml:space="preserve">Package_QFP:LQFP-144_20x20mm_P0.5mm</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tray</t>
+          <t xml:space="preserve">LQFP-144</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/201/1/1043.pdf</t>
+          <t xml:space="preserve">https://www.st.com/resource/en/datasheet/stm32h753zi.pdf</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Keystone-Electronics/1043?qs=%2F7TOpeL5Mz6j%2FnxeOA1rsg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/STMicroelectronics/STM32H753ZIT6?qs=u4fy%2FsgLU9PzR9vtNNw%2FMw%3D%3D</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylindrical Battery Contacts, Clips, Holders &amp; Springs</t>
+          <t xml:space="preserve">STMicroelectronics Arm Cortex-M7 MCU, 2048KB flash, 1024KB RAM, 480 MHz, 1.62-3.6V, 114 GPIO, LQFP144</t>
         </is>
       </c>
       <c r="K53"/>
@@ -5771,7 +5760,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">France</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5781,17 +5770,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve">534-1043</t>
-        </is>
-      </c>
-      <c r="P53">
-        <v>2.99</v>
-      </c>
-      <c r="Q53">
-        <v>2.99</v>
+          <t xml:space="preserve">511-STM32H753ZIT6</t>
+        </is>
+      </c>
+      <c r="P53" s="3">
+        <v>17.13</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>17.13</v>
       </c>
       <c r="R53">
-        <v>9743</v>
+        <v>14</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5804,26 +5793,26 @@
       <c r="U53">
         <v>3</v>
       </c>
-      <c r="V53">
-        <v>2.99</v>
-      </c>
-      <c r="W53">
-        <v>8.97</v>
+      <c r="V53" s="3">
+        <v>17.13</v>
+      </c>
+      <c r="W53" s="3">
+        <v>51.39</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
-      <c r="Y53">
+      <c r="Y53" s="3">
         <v>0</v>
       </c>
-      <c r="Z53">
-        <v>8.97</v>
+      <c r="Z53" s="3">
+        <v>51.39</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">R25</t>
+          <t xml:space="preserve">BAT1</t>
         </is>
       </c>
       <c r="B54">
@@ -5831,49 +5820,41 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">258k</t>
+          <t xml:space="preserve">1043 Holder for 18650</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AC0603FR-07255KL</t>
+          <t xml:space="preserve">1043</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAGEO</t>
+          <t xml:space="preserve">Keystone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MyFootprints:BAT_1043</t>
+        </is>
+      </c>
+      <c r="G54"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/PYu-AC_51_RoHS_L_11.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/201/1/1043.pdf</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/AC0603FR-07255KL?qs=ygRr%2FtkhteuHHB%2Fp4hR9tQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Keystone-Electronics/1043?qs=%2F7TOpeL5Mz6j%2FnxeOA1rsg%3D%3D</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cylindrical Battery Contacts, Clips, Holders &amp; Springs</t>
+        </is>
+      </c>
+      <c r="K54"/>
       <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -5881,7 +5862,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5891,17 +5872,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">603-AC0603FR-07255KL</t>
-        </is>
-      </c>
-      <c r="P54">
-        <v>0.1</v>
-      </c>
-      <c r="Q54">
-        <v>0.1</v>
+          <t xml:space="preserve">534-1043</t>
+        </is>
+      </c>
+      <c r="P54" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>2.99</v>
       </c>
       <c r="R54">
-        <v>27471</v>
+        <v>9743</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5912,71 +5893,71 @@
         <v>1</v>
       </c>
       <c r="U54">
-        <v>10</v>
-      </c>
-      <c r="V54">
-        <v>0.017</v>
-      </c>
-      <c r="W54">
-        <v>0.17</v>
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
+        <v>2.99</v>
+      </c>
+      <c r="W54" s="3">
+        <v>8.97</v>
       </c>
       <c r="X54">
-        <v>30</v>
-      </c>
-      <c r="Y54">
-        <v>0.051</v>
-      </c>
-      <c r="Z54">
-        <v>0.221</v>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>8.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">C43,C52,C55</t>
+          <t xml:space="preserve">R25</t>
         </is>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10pF</t>
+          <t xml:space="preserve">258k</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL05C100JB5NNWC</t>
+          <t xml:space="preserve">AC0603FR-07255KL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C100JB5NNN</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/508/1/PYu-AC_51_RoHS_L_11.pdf</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C100JB5NNWC?qs=CveC9HkIcgk8xP%252BMUb%252BQXw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/AC0603FR-07255KL?qs=ygRr%2FtkhteuHHB%2Fp4hR9tQ%3D%3D</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
+          <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5991,7 +5972,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6001,17 +5982,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL05C100JB5NNWC</t>
-        </is>
-      </c>
-      <c r="P55">
-        <v>0.23</v>
-      </c>
-      <c r="Q55">
-        <v>0.69</v>
+          <t xml:space="preserve">603-AC0603FR-07255KL</t>
+        </is>
+      </c>
+      <c r="P55" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>0.1</v>
       </c>
       <c r="R55">
-        <v>99958</v>
+        <v>27471</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -6024,69 +6005,69 @@
       <c r="U55">
         <v>10</v>
       </c>
-      <c r="V55">
-        <v>0.081</v>
-      </c>
-      <c r="W55">
-        <v>0.81</v>
+      <c r="V55" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="W55" s="3">
+        <v>0.17</v>
       </c>
       <c r="X55">
-        <v>7.83</v>
-      </c>
-      <c r="Y55">
-        <v>0.0634</v>
-      </c>
-      <c r="Z55">
-        <v>0.8734</v>
+        <v>30</v>
+      </c>
+      <c r="Y55" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="Z55" s="3">
+        <v>0.221</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">R12</t>
+          <t xml:space="preserve">C43,C52,C55</t>
         </is>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">94.2k</t>
+          <t xml:space="preserve">10pF</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">RT0603BRD0794K2L</t>
+          <t xml:space="preserve">CL05C100JB5NNWC</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAGEO</t>
+          <t xml:space="preserve">Samsung</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/72/1/PYU_RT_1_TO_0_01_ROHS_L.pdf</t>
+          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C100JB5NNN</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RT0603BRD0794K2L?qs=bQfrgN9vNvwe21O8BIcT9A%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C100JB5NNWC?qs=CveC9HkIcgk8xP%252BMUb%252BQXw%3D%3D</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
+          <t xml:space="preserve">capacitor, small US symbol</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6101,7 +6082,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6111,17 +6092,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">603-RT0603BRD0794K2L</t>
-        </is>
-      </c>
-      <c r="P56">
-        <v>0.1</v>
-      </c>
-      <c r="Q56">
-        <v>0.1</v>
+          <t xml:space="preserve">187-CL05C100JB5NNWC</t>
+        </is>
+      </c>
+      <c r="P56" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>0.69</v>
       </c>
       <c r="R56">
-        <v>8529</v>
+        <v>99958</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -6132,28 +6113,28 @@
         <v>1</v>
       </c>
       <c r="U56">
-        <v>3</v>
-      </c>
-      <c r="V56">
-        <v>0.1</v>
-      </c>
-      <c r="W56">
-        <v>0.3</v>
+        <v>10</v>
+      </c>
+      <c r="V56" s="3">
+        <v>0.081</v>
+      </c>
+      <c r="W56" s="3">
+        <v>0.81</v>
       </c>
       <c r="X56">
-        <v>8</v>
-      </c>
-      <c r="Y56">
-        <v>0.024</v>
-      </c>
-      <c r="Z56">
-        <v>0.324</v>
+        <v>7.83</v>
+      </c>
+      <c r="Y56" s="3">
+        <v>0.0634</v>
+      </c>
+      <c r="Z56" s="3">
+        <v>0.8734</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">C12</t>
+          <t xml:space="preserve">OVP1</t>
         </is>
       </c>
       <c r="B57">
@@ -6161,49 +6142,45 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">22p</t>
+          <t xml:space="preserve">TPS3700DDCR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL05C220JB5NNNC</t>
+          <t xml:space="preserve">TPS3700DDCR2G4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C220JB5NNN</t>
+          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps3700</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C220JB5NNNC?qs=349EhDEZ59rwk5AXsooX1g%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS3700DDCR2G4?qs=7%2F6SraaimPQ2iIfCXLqUgg%3D%3D</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Analog Comparators</t>
+        </is>
+      </c>
+      <c r="K57"/>
       <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -6211,7 +6188,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6221,17 +6198,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL05C220JB5NNNC</t>
-        </is>
-      </c>
-      <c r="P57">
-        <v>0.1</v>
-      </c>
-      <c r="Q57">
-        <v>0.1</v>
+          <t xml:space="preserve">595-TPS3700DDCR2G4</t>
+        </is>
+      </c>
+      <c r="P57" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2.75</v>
       </c>
       <c r="R57">
-        <v>101965</v>
+        <v>2919</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -6242,74 +6219,78 @@
         <v>1</v>
       </c>
       <c r="U57">
-        <v>10</v>
-      </c>
-      <c r="V57">
-        <v>0.021</v>
-      </c>
-      <c r="W57">
-        <v>0.21</v>
+        <v>3</v>
+      </c>
+      <c r="V57" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="W57" s="3">
+        <v>8.25</v>
       </c>
       <c r="X57">
-        <v>8</v>
-      </c>
-      <c r="Y57">
-        <v>0.0168</v>
-      </c>
-      <c r="Z57">
-        <v>0.2268</v>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>8.25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LQFP64_DATA_1</t>
+          <t xml:space="preserve">R12</t>
         </is>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">QTH-060-01-X-D-A</t>
+          <t xml:space="preserve">94.2k</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">QTH-060-01-L-D-A</t>
+          <t xml:space="preserve">RT0603BRD0794K2L</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samtec</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SAMTEC_QTH-060-01-X-D-A</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tray</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qth.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/72/1/PYU_RT_1_TO_0_01_ROHS_L.pdf</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QTH-060-01-L-D-A?qs=4hHQsd36k317SgTiURd9mA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RT0603BRD0794K2L?qs=bQfrgN9vNvwe21O8BIcT9A%3D%3D</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
-        </is>
-      </c>
-      <c r="K58"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -6317,7 +6298,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Malaysia</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6327,17 +6308,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200-QTH06001LDA</t>
-        </is>
-      </c>
-      <c r="P58">
-        <v>5.75</v>
-      </c>
-      <c r="Q58">
-        <v>11.5</v>
+          <t xml:space="preserve">603-RT0603BRD0794K2L</t>
+        </is>
+      </c>
+      <c r="P58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0.1</v>
       </c>
       <c r="R58">
-        <v>4882</v>
+        <v>8529</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6348,28 +6329,28 @@
         <v>1</v>
       </c>
       <c r="U58">
-        <v>6</v>
-      </c>
-      <c r="V58">
-        <v>5.75</v>
-      </c>
-      <c r="W58">
-        <v>34.5</v>
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0.3</v>
       </c>
       <c r="X58">
         <v>8</v>
       </c>
-      <c r="Y58">
-        <v>2.76</v>
-      </c>
-      <c r="Z58">
-        <v>37.26</v>
+      <c r="Y58" s="3">
+        <v>0.024</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0.324</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">R45</t>
+          <t xml:space="preserve">C12</t>
         </is>
       </c>
       <c r="B59">
@@ -6377,42 +6358,42 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.25k</t>
+          <t xml:space="preserve">22p</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-3162ELF</t>
+          <t xml:space="preserve">CL05C220JB5NNNC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">Samsung</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05C220JB5NNN</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3162ELF?qs=I4suiNu8FYA4%252BNO%252BV%2FGfgA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05C220JB5NNNC?qs=349EhDEZ59rwk5AXsooX1g%3D%3D</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
+          <t xml:space="preserve">capacitor, small US symbol</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6427,7 +6408,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6437,17 +6418,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-3162ELF</t>
-        </is>
-      </c>
-      <c r="P59">
+          <t xml:space="preserve">187-CL05C220JB5NNNC</t>
+        </is>
+      </c>
+      <c r="P59" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="3">
         <v>0.1</v>
       </c>
       <c r="R59">
-        <v>828379</v>
+        <v>101965</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6460,69 +6441,65 @@
       <c r="U59">
         <v>10</v>
       </c>
-      <c r="V59">
-        <v>0.012</v>
-      </c>
-      <c r="W59">
-        <v>0.12</v>
+      <c r="V59" s="3">
+        <v>0.021</v>
+      </c>
+      <c r="W59" s="3">
+        <v>0.21</v>
       </c>
       <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0.12</v>
+        <v>8</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0.0168</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0.2268</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBK-1</t>
+          <t xml:space="preserve">LQFP64_DATA_1</t>
         </is>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7u</t>
+          <t xml:space="preserve">QTH-060-01-X-D-A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SRP7028A-4R7M</t>
+          <t xml:space="preserve">QTH-060-01-L-D-A</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">Samtec</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inductor_SMD:L_Bourns_SRP7028A_7.3x6.6mm</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reel</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MyFootprints:SAMTEC_QTH-060-01-X-D-A</t>
+        </is>
+      </c>
+      <c r="G60"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/srp7028a.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/85/1/qth.pdf</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/SRP7028A-4R7M?qs=7z%252BmIopC6%2FJgdLFz63lL4Q%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samtec/QTH-060-01-L-D-A?qs=4hHQsd36k317SgTiURd9mA%3D%3D</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inductor</t>
+          <t xml:space="preserve">Board to Board &amp; Mezzanine Connectors</t>
         </is>
       </c>
       <c r="K60"/>
@@ -6533,7 +6510,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Malaysia</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6543,17 +6520,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-SRP7028A-4R7M</t>
-        </is>
-      </c>
-      <c r="P60">
-        <v>1.1</v>
-      </c>
-      <c r="Q60">
-        <v>1.1</v>
+          <t xml:space="preserve">200-QTH06001LDA</t>
+        </is>
+      </c>
+      <c r="P60" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>11.5</v>
       </c>
       <c r="R60">
-        <v>16159</v>
+        <v>4882</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6564,28 +6541,28 @@
         <v>1</v>
       </c>
       <c r="U60">
-        <v>3</v>
-      </c>
-      <c r="V60">
-        <v>1.1</v>
-      </c>
-      <c r="W60">
-        <v>3.3</v>
+        <v>6</v>
+      </c>
+      <c r="V60" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="W60" s="3">
+        <v>34.5</v>
       </c>
       <c r="X60">
         <v>8</v>
       </c>
-      <c r="Y60">
-        <v>0.264</v>
-      </c>
-      <c r="Z60">
-        <v>3.564</v>
+      <c r="Y60" s="3">
+        <v>2.76</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>37.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWR_MUX1</t>
+          <t xml:space="preserve">R45</t>
         </is>
       </c>
       <c r="B61">
@@ -6593,45 +6570,49 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS2121RUXR</t>
+          <t xml:space="preserve">31.25k</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPS2121RUXR</t>
+          <t xml:space="preserve">CR0603-FX-3162ELF</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TEXAS INSTRUMENTS</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:IC_TPS2121RUXR</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">VQFN-12</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps2121</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS2121RUXR?qs=qSfuJ%252Bfl%2Fd7dCYiVnUfngQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3162ELF?qs=I4suiNu8FYA4%252BNO%252BV%2FGfgA%3D%3D</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
-        </is>
-      </c>
-      <c r="K61"/>
+          <t xml:space="preserve">Resistor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -6639,7 +6620,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6649,17 +6630,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TPS2121RUXR</t>
-        </is>
-      </c>
-      <c r="P61">
-        <v>2.44</v>
-      </c>
-      <c r="Q61">
-        <v>2.44</v>
+          <t xml:space="preserve">652-CR0603FX-3162ELF</t>
+        </is>
+      </c>
+      <c r="P61" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0.1</v>
       </c>
       <c r="R61">
-        <v>14155</v>
+        <v>828379</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6670,28 +6651,28 @@
         <v>1</v>
       </c>
       <c r="U61">
-        <v>3</v>
-      </c>
-      <c r="V61">
-        <v>2.44</v>
-      </c>
-      <c r="W61">
-        <v>7.32</v>
+        <v>10</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0.12</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
-      <c r="Y61">
+      <c r="Y61" s="3">
         <v>0</v>
       </c>
-      <c r="Z61">
-        <v>7.32</v>
+      <c r="Z61" s="3">
+        <v>0.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">R32</t>
+          <t xml:space="preserve">LBK-1</t>
         </is>
       </c>
       <c r="B62">
@@ -6699,12 +6680,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.2k</t>
+          <t xml:space="preserve">4.7u</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-4422ELF</t>
+          <t xml:space="preserve">SRP7028A-4R7M</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6714,34 +6695,26 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Inductor_SMD:L_Bourns_SRP7028A_7.3x6.6mm</t>
+        </is>
+      </c>
+      <c r="G62"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/srp7028a.pdf</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4422ELF?qs=CCIlxZRRv7iL770YaT7glg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/SRP7028A-4R7M?qs=7z%252BmIopC6%2FJgdLFz63lL4Q%3D%3D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Inductor</t>
+        </is>
+      </c>
+      <c r="K62"/>
       <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -6749,7 +6722,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6759,17 +6732,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-4422ELF</t>
-        </is>
-      </c>
-      <c r="P62">
-        <v>0.1</v>
-      </c>
-      <c r="Q62">
-        <v>0.1</v>
+          <t xml:space="preserve">652-SRP7028A-4R7M</t>
+        </is>
+      </c>
+      <c r="P62" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1.1</v>
       </c>
       <c r="R62">
-        <v>331725</v>
+        <v>16159</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6780,28 +6753,28 @@
         <v>1</v>
       </c>
       <c r="U62">
-        <v>10</v>
-      </c>
-      <c r="V62">
-        <v>0.016</v>
-      </c>
-      <c r="W62">
-        <v>0.16</v>
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="W62" s="3">
+        <v>3.3</v>
       </c>
       <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0.16</v>
+        <v>8</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0.264</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>3.564</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">C25</t>
+          <t xml:space="preserve">PWR_MUX1</t>
         </is>
       </c>
       <c r="B63">
@@ -6809,49 +6782,45 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3n</t>
+          <t xml:space="preserve">TPS2121RUXR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL05B332KB5NNWC</t>
+          <t xml:space="preserve">TPS2121RUXR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">TEXAS INSTRUMENTS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
+          <t xml:space="preserve">MyFootprints:IC_TPS2121RUXR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402 (1005 metric)</t>
+          <t xml:space="preserve">VQFN-12</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B332KB5NNN</t>
+          <t xml:space="preserve">https://www.ti.com/lit/gpn/tps2121</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B332KB5NNWC?qs=xZ%2FP%252Ba9zWqZqGlb3MDMYXQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPS2121RUXR?qs=qSfuJ%252Bfl%2Fd7dCYiVnUfngQ%3D%3D</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
+        </is>
+      </c>
+      <c r="K63"/>
       <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -6859,7 +6828,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6869,17 +6838,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL05B332KB5NNWC</t>
-        </is>
-      </c>
-      <c r="P63">
-        <v>0.1</v>
-      </c>
-      <c r="Q63">
-        <v>0.1</v>
+          <t xml:space="preserve">595-TPS2121RUXR</t>
+        </is>
+      </c>
+      <c r="P63" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>2.44</v>
       </c>
       <c r="R63">
-        <v>80721</v>
+        <v>14155</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6890,28 +6859,28 @@
         <v>1</v>
       </c>
       <c r="U63">
-        <v>10</v>
-      </c>
-      <c r="V63">
-        <v>0.013</v>
-      </c>
-      <c r="W63">
-        <v>0.13</v>
+        <v>3</v>
+      </c>
+      <c r="V63" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="W63" s="3">
+        <v>7.32</v>
       </c>
       <c r="X63">
-        <v>10</v>
-      </c>
-      <c r="Y63">
-        <v>0.013</v>
-      </c>
-      <c r="Z63">
-        <v>0.143</v>
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>7.32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">R48</t>
+          <t xml:space="preserve">R32</t>
         </is>
       </c>
       <c r="B64">
@@ -6919,37 +6888,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">10k</t>
+          <t xml:space="preserve">44.2k</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0402FR-0710KL</t>
+          <t xml:space="preserve">CR0603-FX-4422ELF</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAGEO</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0402FR-0710KL?qs=I1mnnYJTTsxUoNwrUsQExA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4422ELF?qs=CCIlxZRRv7iL770YaT7glg%3D%3D</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6979,17 +6948,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">603-RC0402FR-0710KL</t>
-        </is>
-      </c>
-      <c r="P64">
+          <t xml:space="preserve">652-CR0603FX-4422ELF</t>
+        </is>
+      </c>
+      <c r="P64" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="3">
         <v>0.1</v>
       </c>
       <c r="R64">
-        <v>6731048</v>
+        <v>331725</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -7002,39 +6971,39 @@
       <c r="U64">
         <v>10</v>
       </c>
-      <c r="V64">
-        <v>0.009</v>
-      </c>
-      <c r="W64">
-        <v>0.09</v>
+      <c r="V64" s="3">
+        <v>0.016</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0.16</v>
       </c>
       <c r="X64">
-        <v>8</v>
-      </c>
-      <c r="Y64">
-        <v>0.0072</v>
-      </c>
-      <c r="Z64">
-        <v>0.0972</v>
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">C27,C53</t>
+          <t xml:space="preserve">C25</t>
         </is>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7uF</t>
+          <t xml:space="preserve">3.3n</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL21A475KAQNNNE</t>
+          <t xml:space="preserve">CL05B332KB5NNWC</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7044,22 +7013,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0805_2012Metric</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805 (2012 metric)</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL21A475KAQNNN</t>
+          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL05B332KB5NNN</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL21A475KAQNNNE?qs=yOVawPpwOwkWIBpK%2Fbg0Aw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL05B332KB5NNWC?qs=xZ%2FP%252Ba9zWqZqGlb3MDMYXQ%3D%3D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7079,7 +7048,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7089,17 +7058,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL21A475KAQNNNE</t>
-        </is>
-      </c>
-      <c r="P65">
-        <v>0.11</v>
-      </c>
-      <c r="Q65">
-        <v>0.22</v>
+          <t xml:space="preserve">187-CL05B332KB5NNWC</t>
+        </is>
+      </c>
+      <c r="P65" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0.1</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>80721</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -7112,26 +7081,26 @@
       <c r="U65">
         <v>10</v>
       </c>
-      <c r="V65">
-        <v>0.042</v>
-      </c>
-      <c r="W65">
-        <v>0.42</v>
+      <c r="V65" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0.13</v>
       </c>
       <c r="X65">
-        <v>8.18</v>
-      </c>
-      <c r="Y65">
-        <v>0.0344</v>
-      </c>
-      <c r="Z65">
-        <v>0.4544</v>
+        <v>10</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0.143</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">U-ESD1</t>
+          <t xml:space="preserve">R49</t>
         </is>
       </c>
       <c r="B66">
@@ -7139,45 +7108,49 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPD2E009DRTR</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TPD2E009DBZR</t>
+          <t xml:space="preserve">ERJ-3GEYJ221V</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Panasonic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-3</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">SC-59-3 (SOT-23-3)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.ti.com/lit/gpn/tpd2e009</t>
+          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPD2E009DBZR?qs=XGzIaZb%2FFYIsL3UFh35JpQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-3GEYJ221V?qs=4WZYzuGhm5qHCFSN9go8VQ%3D%3D</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESD Protection Diodes / TVS Diodes</t>
-        </is>
-      </c>
-      <c r="K66"/>
+          <t xml:space="preserve">Resistor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7185,7 +7158,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7195,17 +7168,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TPD2E009DBZR</t>
-        </is>
-      </c>
-      <c r="P66">
-        <v>0.79</v>
-      </c>
-      <c r="Q66">
-        <v>0.79</v>
+          <t xml:space="preserve">667-ERJ-3GEYJ221V</t>
+        </is>
+      </c>
+      <c r="P66" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>0.1</v>
       </c>
       <c r="R66">
-        <v>4367</v>
+        <v>41255</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -7216,28 +7189,28 @@
         <v>1</v>
       </c>
       <c r="U66">
-        <v>3</v>
-      </c>
-      <c r="V66">
-        <v>0.79</v>
-      </c>
-      <c r="W66">
-        <v>2.37</v>
+        <v>10</v>
+      </c>
+      <c r="V66" s="3">
+        <v>0.023</v>
+      </c>
+      <c r="W66" s="3">
+        <v>0.23</v>
       </c>
       <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>2.37</v>
+        <v>8</v>
+      </c>
+      <c r="Y66" s="3">
+        <v>0.0184</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>0.2484</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCP1</t>
+          <t xml:space="preserve">R48</t>
         </is>
       </c>
       <c r="B67">
@@ -7245,45 +7218,49 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAX4995BAUT_T</t>
+          <t xml:space="preserve">10k</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAX4995BAUT+T</t>
+          <t xml:space="preserve">RC0402FR-0710KL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analog Devices Inc.</t>
+          <t xml:space="preserve">YAGEO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SOT95P280X145-6N</t>
+          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-23-6</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.analog.com/MAX4995B/datasheet</t>
+          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Analog-Devices-Maxim-Integrated/MAX4995BAUT%2bT?qs=7H2Jq%252ByxpJLB5kcRV%252By2dw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/YAGEO/RC0402FR-0710KL?qs=I1mnnYJTTsxUoNwrUsQExA%3D%3D</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
-        </is>
-      </c>
-      <c r="K67"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7291,7 +7268,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7301,17 +7278,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">700-MAX4995BAUTT</t>
-        </is>
-      </c>
-      <c r="P67">
-        <v>6.99</v>
-      </c>
-      <c r="Q67">
-        <v>6.99</v>
+          <t xml:space="preserve">603-RC0402FR-0710KL</t>
+        </is>
+      </c>
+      <c r="P67" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>0.1</v>
       </c>
       <c r="R67">
-        <v>3744</v>
+        <v>6731048</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -7322,28 +7299,28 @@
         <v>1</v>
       </c>
       <c r="U67">
-        <v>3</v>
-      </c>
-      <c r="V67">
-        <v>6.99</v>
-      </c>
-      <c r="W67">
-        <v>20.97</v>
+        <v>10</v>
+      </c>
+      <c r="V67" s="3">
+        <v>0.009</v>
+      </c>
+      <c r="W67" s="3">
+        <v>0.09</v>
       </c>
       <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>20.97</v>
+        <v>8</v>
+      </c>
+      <c r="Y67" s="3">
+        <v>0.0072</v>
+      </c>
+      <c r="Z67" s="3">
+        <v>0.0972</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">R49</t>
+          <t xml:space="preserve">U-ESD1</t>
         </is>
       </c>
       <c r="B68">
@@ -7351,49 +7328,45 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">TPD2E009DRTR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RC0603FR-07220RL</t>
+          <t xml:space="preserve">TPD2E009DBZR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAGEO</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-23-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">SC-59-3</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/catalog/specsheets/YAGEO_PYu_RC_Group_51_RoHS_L_12.pdf</t>
+          <t xml:space="preserve">https://www.ti.com/lit/gpn/tpd2e009</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.in/en/ProductDetail/YAGEO/RC0603FR-07220RL?qs=VU8sRB4EgwA1IyQ0vhXEEw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TPD2E009DBZR?qs=XGzIaZb%2FFYIsL3UFh35JpQ%3D%3D</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ESD Protection Diodes / TVS Diodes</t>
+        </is>
+      </c>
+      <c r="K68"/>
       <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7401,7 +7374,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7411,99 +7384,95 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">603-RC0603FR-07220RL</t>
-        </is>
-      </c>
-      <c r="P68">
-        <v>0.1</v>
-      </c>
-      <c r="Q68">
-        <v>0.1</v>
+          <t xml:space="preserve">595-TPD2E009DBZR</t>
+        </is>
+      </c>
+      <c r="P68" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0.79</v>
       </c>
       <c r="R68">
+        <v>4367</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68">
+        <v>3</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="W68" s="3">
+        <v>2.37</v>
+      </c>
+      <c r="X68">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Active</t>
-        </is>
-      </c>
-      <c r="T68">
-        <v>1</v>
-      </c>
-      <c r="U68">
-        <v>10</v>
-      </c>
-      <c r="V68">
-        <v>0.014</v>
-      </c>
-      <c r="W68">
-        <v>0.14</v>
-      </c>
-      <c r="X68">
-        <v>8</v>
-      </c>
-      <c r="Y68">
-        <v>0.0112</v>
-      </c>
-      <c r="Z68">
-        <v>0.1512</v>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>2.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">R11,R13</t>
+          <t xml:space="preserve">OCP1</t>
         </is>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">330</t>
+          <t xml:space="preserve">MAX4995BAUT_T</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-3300ELF</t>
+          <t xml:space="preserve">MAX4995BAUT+T</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">Analog Devices Inc.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">MyFootprints:SOT95P280X145-6N</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">SOT-23-6</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://www.analog.com/MAX4995B/datasheet</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3300ELF?qs=I4suiNu8FYB0EfszDEV%252BGw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Analog-Devices-Maxim-Integrated/MAX4995BAUT%2bT?qs=7H2Jq%252ByxpJLB5kcRV%252By2dw%3D%3D</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Power Switch ICs - Power Distribution</t>
+        </is>
+      </c>
+      <c r="K69"/>
       <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7511,7 +7480,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7521,17 +7490,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-3300ELF</t>
-        </is>
-      </c>
-      <c r="P69">
-        <v>0.1</v>
-      </c>
-      <c r="Q69">
-        <v>0.2</v>
+          <t xml:space="preserve">700-MAX4995BAUTT</t>
+        </is>
+      </c>
+      <c r="P69" s="3">
+        <v>6.99</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>6.99</v>
       </c>
       <c r="R69">
-        <v>1487770</v>
+        <v>3744</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7542,74 +7511,78 @@
         <v>1</v>
       </c>
       <c r="U69">
-        <v>10</v>
-      </c>
-      <c r="V69">
-        <v>0.012</v>
-      </c>
-      <c r="W69">
-        <v>0.12</v>
+        <v>3</v>
+      </c>
+      <c r="V69" s="3">
+        <v>6.99</v>
+      </c>
+      <c r="W69" s="3">
+        <v>20.97</v>
       </c>
       <c r="X69">
         <v>0</v>
       </c>
-      <c r="Y69">
+      <c r="Y69" s="3">
         <v>0</v>
       </c>
-      <c r="Z69">
-        <v>0.12</v>
+      <c r="Z69" s="3">
+        <v>20.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOOT0_LED1</t>
+          <t xml:space="preserve">R11,R13</t>
         </is>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED</t>
+          <t xml:space="preserve">330</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">150060GS75000</t>
+          <t xml:space="preserve">CR0603-FX-3300ELF</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wurth Elektronik</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">LED_SMD:LED_0603_1608Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603 (1608 metric)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060GS75000.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060GS75000?qs=LlUlMxKIyB0UYkq5lDO8nA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-3300ELF?qs=I4suiNu8FYB0EfszDEV%252BGw%3D%3D</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Light emitting diode</t>
-        </is>
-      </c>
-      <c r="K70"/>
+          <t xml:space="preserve">Resistor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7617,7 +7590,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7627,17 +7600,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-150060GS75000</t>
-        </is>
-      </c>
-      <c r="P70">
-        <v>0.16</v>
-      </c>
-      <c r="Q70">
-        <v>0.16</v>
+          <t xml:space="preserve">652-CR0603FX-3300ELF</t>
+        </is>
+      </c>
+      <c r="P70" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0.2</v>
       </c>
       <c r="R70">
-        <v>146444</v>
+        <v>1487770</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7648,28 +7621,28 @@
         <v>1</v>
       </c>
       <c r="U70">
-        <v>3</v>
-      </c>
-      <c r="V70">
-        <v>0.16</v>
-      </c>
-      <c r="W70">
-        <v>0.48</v>
+        <v>10</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0.12</v>
       </c>
       <c r="X70">
-        <v>35</v>
-      </c>
-      <c r="Y70">
-        <v>0.168</v>
-      </c>
-      <c r="Z70">
-        <v>0.648</v>
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0.12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">R30</t>
+          <t xml:space="preserve">BOOT0_LED1</t>
         </is>
       </c>
       <c r="B71">
@@ -7677,22 +7650,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">680</t>
+          <t xml:space="preserve">LED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-6800ELF</t>
+          <t xml:space="preserve">150060GS75000</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">Wurth Elektronik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">LED_SMD:LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7702,24 +7675,20 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/150060GS75000.pdf</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6800ELF?qs=0nF2VnfAjXlQv%252B4gY05i1Q%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/150060GS75000?qs=LlUlMxKIyB0UYkq5lDO8nA%3D%3D</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Light emitting diode</t>
+        </is>
+      </c>
+      <c r="K71"/>
       <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7727,7 +7696,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7737,17 +7706,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-6800ELF</t>
-        </is>
-      </c>
-      <c r="P71">
-        <v>0.1</v>
-      </c>
-      <c r="Q71">
-        <v>0.1</v>
+          <t xml:space="preserve">710-150060GS75000</t>
+        </is>
+      </c>
+      <c r="P71" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0.16</v>
       </c>
       <c r="R71">
-        <v>971001</v>
+        <v>146444</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7758,74 +7727,78 @@
         <v>1</v>
       </c>
       <c r="U71">
-        <v>10</v>
-      </c>
-      <c r="V71">
-        <v>0.011</v>
-      </c>
-      <c r="W71">
-        <v>0.11</v>
+        <v>3</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0.48</v>
       </c>
       <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0.11</v>
+        <v>35</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0.168</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0.648</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUF1,BUF2,BUF3,BUF4,BUF5,BUF6,BUF7,BUF8,BUF9,BUF10,BUF11,BUF12</t>
+          <t xml:space="preserve">R30</t>
         </is>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">74AHC1G125</t>
+          <t xml:space="preserve">680</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SN74AHC1G125DRLR</t>
+          <t xml:space="preserve">CR0603-FX-6800ELF</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-553</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-5X3-5</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.ti.com/lit/sg/scyt129e/scyt129e.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74AHC1G125DRLR?qs=NvrC5vRk3q5L7MSRMAsCMg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-6800ELF?qs=0nF2VnfAjXlQv%252B4gY05i1Q%3D%3D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single Buffer Gate Tri-State, Low-Voltage CMOS</t>
-        </is>
-      </c>
-      <c r="K72"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7833,7 +7806,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -7843,17 +7816,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-SN74AHC1G125DRLR</t>
-        </is>
-      </c>
-      <c r="P72">
-        <v>0.22</v>
-      </c>
-      <c r="Q72">
-        <v>2.64</v>
+          <t xml:space="preserve">652-CR0603FX-6800ELF</t>
+        </is>
+      </c>
+      <c r="P72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0.1</v>
       </c>
       <c r="R72">
-        <v>6492</v>
+        <v>971001</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7864,78 +7837,74 @@
         <v>1</v>
       </c>
       <c r="U72">
-        <v>36</v>
-      </c>
-      <c r="V72">
-        <v>0.131</v>
-      </c>
-      <c r="W72">
-        <v>4.716</v>
+        <v>10</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="W72" s="3">
+        <v>0.11</v>
       </c>
       <c r="X72">
         <v>0</v>
       </c>
-      <c r="Y72">
+      <c r="Y72" s="3">
         <v>0</v>
       </c>
-      <c r="Z72">
-        <v>4.716</v>
+      <c r="Z72" s="3">
+        <v>0.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">R47</t>
+          <t xml:space="preserve">BUF1,BUF2,BUF3,BUF4,BUF5,BUF6,BUF7,BUF8,BUF9,BUF10,BUF11,BUF12</t>
         </is>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.5k</t>
+          <t xml:space="preserve">74AHC1G125</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERJ-PA2F1242X</t>
+          <t xml:space="preserve">SN74AHC1G125DRLR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panasonic</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-553</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0402</t>
+          <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/AOA0000C331.pdf</t>
+          <t xml:space="preserve">http://www.ti.com/lit/sg/scyt129e/scyt129e.pdf</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-PA2F1242X?qs=V%252BBODeGd91LZ4cJzK1GGng%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74AHC1G125DRLR?qs=NvrC5vRk3q5L7MSRMAsCMg%3D%3D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Single Buffer Gate Tri-State, Low-Voltage CMOS</t>
+        </is>
+      </c>
+      <c r="K73"/>
       <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -7943,7 +7912,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7953,17 +7922,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">667-ERJ-PA2F1242X</t>
-        </is>
-      </c>
-      <c r="P73">
-        <v>0.28</v>
-      </c>
-      <c r="Q73">
-        <v>0.28</v>
+          <t xml:space="preserve">595-SN74AHC1G125DRLR</t>
+        </is>
+      </c>
+      <c r="P73" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>2.64</v>
       </c>
       <c r="R73">
-        <v>28035</v>
+        <v>6492</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7974,28 +7943,28 @@
         <v>1</v>
       </c>
       <c r="U73">
-        <v>3</v>
-      </c>
-      <c r="V73">
-        <v>0.28</v>
-      </c>
-      <c r="W73">
-        <v>0.84</v>
+        <v>36</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0.131</v>
+      </c>
+      <c r="W73" s="3">
+        <v>4.716</v>
       </c>
       <c r="X73">
         <v>0</v>
       </c>
-      <c r="Y73">
+      <c r="Y73" s="3">
         <v>0</v>
       </c>
-      <c r="Z73">
-        <v>0.84</v>
+      <c r="Z73" s="3">
+        <v>4.716</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">R28</t>
+          <t xml:space="preserve">R47</t>
         </is>
       </c>
       <c r="B74">
@@ -8003,12 +7972,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.6k</t>
+          <t xml:space="preserve">12.5k</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERJ-H3EF1872V</t>
+          <t xml:space="preserve">ERJ-PA2F1242X</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8018,22 +7987,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">0402</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
+          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/AOA0000C331.pdf</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1872V?qs=eP2BKZSCXI5l01WTRmuzHg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-PA2F1242X?qs=V%252BBODeGd91LZ4cJzK1GGng%3D%3D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8063,17 +8032,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">667-ERJ-H3EF1872V</t>
-        </is>
-      </c>
-      <c r="P74">
+          <t xml:space="preserve">667-ERJ-PA2F1242X</t>
+        </is>
+      </c>
+      <c r="P74" s="3">
         <v>0.28</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="3">
         <v>0.28</v>
       </c>
       <c r="R74">
-        <v>9748</v>
+        <v>28035</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -8086,72 +8055,76 @@
       <c r="U74">
         <v>3</v>
       </c>
-      <c r="V74">
+      <c r="V74" s="3">
         <v>0.28</v>
       </c>
-      <c r="W74">
+      <c r="W74" s="3">
         <v>0.84</v>
       </c>
       <c r="X74">
         <v>0</v>
       </c>
-      <c r="Y74">
+      <c r="Y74" s="3">
         <v>0</v>
       </c>
-      <c r="Z74">
+      <c r="Z74" s="3">
         <v>0.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">INV1,INV2,INV3,INV4,INV5,INV6,INV7</t>
+          <t xml:space="preserve">R28</t>
         </is>
       </c>
       <c r="B75">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">74LVC1GU04DRLR</t>
+          <t xml:space="preserve">18.6k</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SN74LVC1GU04DRLR</t>
+          <t xml:space="preserve">ERJ-H3EF1872V</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Panasonic</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-553</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT-5X3-5</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.ti.com/lit/ds/symlink/sn74lvc1gu04.pdf</t>
+          <t xml:space="preserve">https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/RDO0000C334.pdf</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1GU04DRLR?qs=dT9u2OTAaVWQWKRtkB6JZw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Panasonic/ERJ-H3EF1872V?qs=eP2BKZSCXI5l01WTRmuzHg%3D%3D</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single Inverter Gate, SOT-553</t>
-        </is>
-      </c>
-      <c r="K75"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8159,7 +8132,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">Japan</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8169,17 +8142,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-SN74LVC1GU04DRLR</t>
-        </is>
-      </c>
-      <c r="P75">
-        <v>0.36</v>
-      </c>
-      <c r="Q75">
-        <v>2.52</v>
+          <t xml:space="preserve">667-ERJ-H3EF1872V</t>
+        </is>
+      </c>
+      <c r="P75" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0.28</v>
       </c>
       <c r="R75">
-        <v>6693</v>
+        <v>9748</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -8190,78 +8163,74 @@
         <v>1</v>
       </c>
       <c r="U75">
-        <v>21</v>
-      </c>
-      <c r="V75">
-        <v>0.246</v>
-      </c>
-      <c r="W75">
-        <v>5.166</v>
+        <v>3</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0.84</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
-      <c r="Y75">
+      <c r="Y75" s="3">
         <v>0</v>
       </c>
-      <c r="Z75">
-        <v>5.166</v>
+      <c r="Z75" s="3">
+        <v>0.84</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">INV1,INV2,INV3,INV4,INV5,INV6,INV7</t>
         </is>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.7u</t>
+          <t xml:space="preserve">74LVC1GU04DRLR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL10A475KO8NNNC</t>
+          <t xml:space="preserve">SN74LVC1GU04DRLR</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0603_1608Metric</t>
+          <t xml:space="preserve">Package_TO_SOT_SMD:SOT-553</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603 (1608 metric)</t>
+          <t xml:space="preserve">SOT-5X3-5</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A475KO8NNN</t>
+          <t xml:space="preserve">http://www.ti.com/lit/ds/symlink/sn74lvc1gu04.pdf</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A475KO8NNNC?qs=X6jEic%2FHinAbIjmLnFfqqQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/SN74LVC1GU04DRLR?qs=dT9u2OTAaVWQWKRtkB6JZw%3D%3D</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Single Inverter Gate, SOT-553</t>
+        </is>
+      </c>
+      <c r="K76"/>
       <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8269,7 +8238,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8279,17 +8248,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL10A475KO8NNNC</t>
-        </is>
-      </c>
-      <c r="P76">
-        <v>0.12</v>
-      </c>
-      <c r="Q76">
-        <v>0.12</v>
+          <t xml:space="preserve">595-SN74LVC1GU04DRLR</t>
+        </is>
+      </c>
+      <c r="P76" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="Q76" s="3">
+        <v>2.52</v>
       </c>
       <c r="R76">
-        <v>385121</v>
+        <v>6693</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -8300,28 +8269,28 @@
         <v>1</v>
       </c>
       <c r="U76">
-        <v>3</v>
-      </c>
-      <c r="V76">
-        <v>0.12</v>
-      </c>
-      <c r="W76">
-        <v>0.36</v>
+        <v>21</v>
+      </c>
+      <c r="V76" s="3">
+        <v>0.246</v>
+      </c>
+      <c r="W76" s="3">
+        <v>5.166</v>
       </c>
       <c r="X76">
-        <v>8.33</v>
-      </c>
-      <c r="Y76">
-        <v>0.03</v>
-      </c>
-      <c r="Z76">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>5.166</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B77">
@@ -8329,45 +8298,49 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crystal_GND24</t>
+          <t xml:space="preserve">4.7u</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABM8-25.000MHZ-B2-T</t>
+          <t xml:space="preserve">CL10A475KO8NNNC</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abracon</t>
+          <t xml:space="preserve">Samsung</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crystal:Crystal_SMD_0603-4Pin_6.0x3.5mm</t>
+          <t xml:space="preserve">Capacitor_SMD:C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2 mm x 2.5 mm</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/184/1/abm8.pdf</t>
+          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A475KO8NNN</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ABRACON/ABM8-25.000MHZ-B2-T?qs=D0XpjEo%2FJ5CyDikUKoGKpw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A475KO8NNNC?qs=X6jEic%2FHinAbIjmLnFfqqQ%3D%3D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four pin crystal, GND on pins 2 and 4</t>
-        </is>
-      </c>
-      <c r="K77"/>
+          <t xml:space="preserve">capacitor, small US symbol</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8375,7 +8348,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8385,17 +8358,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">815-ABM8-25-B2-T</t>
-        </is>
-      </c>
-      <c r="P77">
-        <v>0.5</v>
-      </c>
-      <c r="Q77">
-        <v>0.5</v>
+          <t xml:space="preserve">187-CL10A475KO8NNNC</t>
+        </is>
+      </c>
+      <c r="P77" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0.12</v>
       </c>
       <c r="R77">
-        <v>14291</v>
+        <v>385121</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -8408,69 +8381,69 @@
       <c r="U77">
         <v>3</v>
       </c>
-      <c r="V77">
-        <v>0.5</v>
-      </c>
-      <c r="W77">
-        <v>1.5</v>
+      <c r="V77" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0.36</v>
       </c>
       <c r="X77">
-        <v>30</v>
-      </c>
-      <c r="Y77">
-        <v>0.45</v>
-      </c>
-      <c r="Z77">
-        <v>1.95</v>
+        <v>8.33</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0.39</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">LS1,LS2</t>
+          <t xml:space="preserve">Y1</t>
         </is>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXS0102DCUR</t>
+          <t xml:space="preserve">Crystal_GND24</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXS0102DCUR</t>
+          <t xml:space="preserve">ABM8-25.000MHZ-B2-T</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Texas Instruments</t>
+          <t xml:space="preserve">Abracon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package_SO:VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t xml:space="preserve">Crystal:Crystal_SMD_0603-4Pin_6.0x3.5mm</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">VSSOP-8</t>
+          <t xml:space="preserve">3.2 mm x 2.5 mm</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">http://www.ti.com/lit/gpn/txs0102</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/184/1/abm8.pdf</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TXS0102DCUR?qs=dB0LedT%252BmmBcQ3I%2Fs9XEDA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ABRACON/ABM8-25.000MHZ-B2-T?qs=D0XpjEo%2FJ5CyDikUKoGKpw%3D%3D</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2-Bit Bidirectional Voltage-Level Shifter for Open-Drain and Push-Pull Application, VSSOP-8</t>
+          <t xml:space="preserve">Four pin crystal, GND on pins 2 and 4</t>
         </is>
       </c>
       <c r="K78"/>
@@ -8481,7 +8454,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8491,17 +8464,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">595-TXS0102DCUR</t>
-        </is>
-      </c>
-      <c r="P78">
-        <v>0.63</v>
-      </c>
-      <c r="Q78">
-        <v>1.26</v>
+          <t xml:space="preserve">815-ABM8-25-B2-T</t>
+        </is>
+      </c>
+      <c r="P78" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>0.5</v>
       </c>
       <c r="R78">
-        <v>111475</v>
+        <v>14291</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -8512,78 +8485,74 @@
         <v>1</v>
       </c>
       <c r="U78">
-        <v>6</v>
-      </c>
-      <c r="V78">
-        <v>0.63</v>
-      </c>
-      <c r="W78">
-        <v>3.78</v>
+        <v>3</v>
+      </c>
+      <c r="V78" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="W78" s="3">
+        <v>1.5</v>
       </c>
       <c r="X78">
-        <v>0</v>
-      </c>
-      <c r="Y78">
-        <v>0</v>
-      </c>
-      <c r="Z78">
-        <v>3.78</v>
+        <v>30</v>
+      </c>
+      <c r="Y78" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="Z78" s="3">
+        <v>1.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">R24,R27,R29</t>
+          <t xml:space="preserve">LS1,LS2</t>
         </is>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5k</t>
+          <t xml:space="preserve">TXS0102DCUR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRCW06035K05FKEA</t>
+          <t xml:space="preserve">TXS0102DCUR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vishay</t>
+          <t xml:space="preserve">Texas Instruments</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Package_SO:VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">VSSOP-8</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
+          <t xml:space="preserve">http://www.ti.com/lit/gpn/txs0102</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06035K05FKEA?qs=p2bJuJLPpvR%2F884G9E6gpw%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Texas-Instruments/TXS0102DCUR?qs=dB0LedT%252BmmBcQ3I%2Fs9XEDA%3D%3D</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2-Bit Bidirectional Voltage-Level Shifter for Open-Drain and Push-Pull Application, VSSOP-8</t>
+        </is>
+      </c>
+      <c r="K79"/>
       <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8591,7 +8560,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israel</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8601,17 +8570,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">71-CRCW0603-5.05K-E3</t>
-        </is>
-      </c>
-      <c r="P79">
-        <v>0.1</v>
-      </c>
-      <c r="Q79">
-        <v>0.3</v>
+          <t xml:space="preserve">595-TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="P79" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="Q79" s="3">
+        <v>1.26</v>
       </c>
       <c r="R79">
-        <v>7092</v>
+        <v>111475</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -8622,46 +8591,46 @@
         <v>1</v>
       </c>
       <c r="U79">
-        <v>10</v>
-      </c>
-      <c r="V79">
-        <v>0.029</v>
-      </c>
-      <c r="W79">
-        <v>0.29</v>
+        <v>6</v>
+      </c>
+      <c r="V79" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="W79" s="3">
+        <v>3.78</v>
       </c>
       <c r="X79">
         <v>0</v>
       </c>
-      <c r="Y79">
+      <c r="Y79" s="3">
         <v>0</v>
       </c>
-      <c r="Z79">
-        <v>0.29</v>
+      <c r="Z79" s="3">
+        <v>3.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">R26</t>
+          <t xml:space="preserve">R24,R27,R29</t>
         </is>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">21k</t>
+          <t xml:space="preserve">5k</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-2102ELF</t>
+          <t xml:space="preserve">CRCW06035K05FKEA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">Vishay</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8676,12 +8645,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-2102ELF?qs=zx2075yZkZKAHyCDerhqYg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06035K05FKEA?qs=p2bJuJLPpvR%2F884G9E6gpw%3D%3D</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8701,7 +8670,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Israel</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8711,17 +8680,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-2102ELF</t>
-        </is>
-      </c>
-      <c r="P80">
+          <t xml:space="preserve">71-CRCW0603-5.05K-E3</t>
+        </is>
+      </c>
+      <c r="P80" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q80">
-        <v>0.1</v>
+      <c r="Q80" s="3">
+        <v>0.3</v>
       </c>
       <c r="R80">
-        <v>137114</v>
+        <v>7092</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8734,72 +8703,76 @@
       <c r="U80">
         <v>10</v>
       </c>
-      <c r="V80">
-        <v>0.012</v>
-      </c>
-      <c r="W80">
-        <v>0.12</v>
+      <c r="V80" s="3">
+        <v>0.029</v>
+      </c>
+      <c r="W80" s="3">
+        <v>0.29</v>
       </c>
       <c r="X80">
         <v>0</v>
       </c>
-      <c r="Y80">
+      <c r="Y80" s="3">
         <v>0</v>
       </c>
-      <c r="Z80">
-        <v>0.12</v>
+      <c r="Z80" s="3">
+        <v>0.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1V8_EN1,3.3V_EN1</t>
+          <t xml:space="preserve">R26</t>
         </is>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">JS102011SAQN</t>
+          <t xml:space="preserve">21k</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">JS102011SAQN</t>
+          <t xml:space="preserve">CR0603-FX-2102ELF</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">C&amp;K</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Button_Switch_SMD:SW_SPDT_CK_JS102011SAQN</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://ckswitches.com/media/1422/js.pdf</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/JS102011SAQN?qs=LgMIjt8LuD%252B69bNM9a%2FozQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-2102ELF?qs=zx2075yZkZKAHyCDerhqYg%3D%3D</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slide Switches</t>
-        </is>
-      </c>
-      <c r="K81"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8807,7 +8780,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -8817,17 +8790,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">611-JS102011SAQN</t>
-        </is>
-      </c>
-      <c r="P81">
-        <v>0.84</v>
-      </c>
-      <c r="Q81">
-        <v>1.68</v>
+          <t xml:space="preserve">652-CR0603FX-2102ELF</t>
+        </is>
+      </c>
+      <c r="P81" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0.1</v>
       </c>
       <c r="R81">
-        <v>6938</v>
+        <v>137114</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8838,78 +8811,70 @@
         <v>1</v>
       </c>
       <c r="U81">
-        <v>6</v>
-      </c>
-      <c r="V81">
-        <v>0.84</v>
-      </c>
-      <c r="W81">
-        <v>5.04</v>
+        <v>10</v>
+      </c>
+      <c r="V81" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="W81" s="3">
+        <v>0.12</v>
       </c>
       <c r="X81">
-        <v>7.98</v>
-      </c>
-      <c r="Y81">
-        <v>0.4022</v>
-      </c>
-      <c r="Z81">
-        <v>5.4422</v>
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>0.12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">R4</t>
+          <t xml:space="preserve">1V8_EN1,3.3V_EN1</t>
         </is>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">46.4k</t>
+          <t xml:space="preserve">JS102011SAQN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR0603-FX-4642ELF</t>
+          <t xml:space="preserve">JS102011SAQN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourns</t>
+          <t xml:space="preserve">C&amp;K</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Button_Switch_SMD:SW_SPDT_CK_JS102011SAQN</t>
+        </is>
+      </c>
+      <c r="G82"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
+          <t xml:space="preserve">https://ckswitches.com/media/1422/js.pdf</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4642ELF?qs=CCIlxZRRv7h4Dp7z3u08Ag%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/JS102011SAQN?qs=LgMIjt8LuD%252B69bNM9a%2FozQ%3D%3D</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Slide Switches</t>
+        </is>
+      </c>
+      <c r="K82"/>
       <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -8917,7 +8882,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8927,17 +8892,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">652-CR0603FX-4642ELF</t>
-        </is>
-      </c>
-      <c r="P82">
-        <v>0.1</v>
-      </c>
-      <c r="Q82">
-        <v>0.1</v>
+          <t xml:space="preserve">611-JS102011SAQN</t>
+        </is>
+      </c>
+      <c r="P82" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>1.68</v>
       </c>
       <c r="R82">
-        <v>85609</v>
+        <v>6938</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8948,28 +8913,28 @@
         <v>1</v>
       </c>
       <c r="U82">
-        <v>10</v>
-      </c>
-      <c r="V82">
-        <v>0.016</v>
-      </c>
-      <c r="W82">
-        <v>0.16</v>
+        <v>6</v>
+      </c>
+      <c r="V82" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="W82" s="3">
+        <v>5.04</v>
       </c>
       <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>0</v>
-      </c>
-      <c r="Z82">
-        <v>0.16</v>
+        <v>7.98</v>
+      </c>
+      <c r="Y82" s="3">
+        <v>0.4022</v>
+      </c>
+      <c r="Z82" s="3">
+        <v>5.4422</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">R16</t>
+          <t xml:space="preserve">R4</t>
         </is>
       </c>
       <c r="B83">
@@ -8977,17 +8942,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">732k</t>
+          <t xml:space="preserve">46.4k</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">KTR03EZPF3403</t>
+          <t xml:space="preserve">CR0603-FX-4642ELF</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROHM Semiconductor</t>
+          <t xml:space="preserve">Bourns</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9002,12 +8967,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.rohm.com/datasheet?p=KTR03EZPF</t>
+          <t xml:space="preserve">https://www.mouser.com/datasheet/3/40/1/cr.pdf</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ROHM-Semiconductor/KTR03EZPF3403?qs=17ckDYBRdekVwQV2ubwDJA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Bourns/CR0603-FX-4642ELF?qs=CCIlxZRRv7h4Dp7z3u08Ag%3D%3D</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9027,7 +8992,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9037,17 +9002,17 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">755-KTR03EZPF3403</t>
-        </is>
-      </c>
-      <c r="P83">
-        <v>0.19</v>
-      </c>
-      <c r="Q83">
-        <v>0.19</v>
+          <t xml:space="preserve">652-CR0603FX-4642ELF</t>
+        </is>
+      </c>
+      <c r="P83" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0.1</v>
       </c>
       <c r="R83">
-        <v>13778</v>
+        <v>85609</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -9058,74 +9023,78 @@
         <v>1</v>
       </c>
       <c r="U83">
-        <v>3</v>
-      </c>
-      <c r="V83">
-        <v>0.19</v>
-      </c>
-      <c r="W83">
-        <v>0.57</v>
+        <v>10</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0.016</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0.16</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
-      <c r="Y83">
+      <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83">
-        <v>0.57</v>
+      <c r="Z83" s="3">
+        <v>0.16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESET1,TRGT_PWR_ON1</t>
+          <t xml:space="preserve">R16</t>
         </is>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTS645</t>
+          <t xml:space="preserve">732k</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTS645SK43SMTR92-LFS</t>
+          <t xml:space="preserve">KTR03EZPF3403</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">C&amp;K Switches</t>
+          <t xml:space="preserve">ROHM Semiconductor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">MyFootprints:SWITCH_43SMTR92LFS</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reel</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PTS645SM43SMTR92LFS</t>
+          <t xml:space="preserve">0603</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.rohm.com/datasheet?p=KTR03EZPF</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/PTS645SK43SMTR92-LFS?qs=Imq1NPwxi76wjUe7hzmA%252BA%3D%3D&amp;mgh=1</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/ROHM-Semiconductor/KTR03EZPF3403?qs=17ckDYBRdekVwQV2ubwDJA%3D%3D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTS645</t>
-        </is>
-      </c>
-      <c r="K84"/>
+          <t xml:space="preserve">Resistor, small symbol</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Details</t>
@@ -9133,7 +9102,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">China</t>
+          <t xml:space="preserve">Philippines</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9143,17 +9112,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">611-PTS645SK43SMTR92</t>
-        </is>
-      </c>
-      <c r="P84">
-        <v>0.36</v>
-      </c>
-      <c r="Q84">
-        <v>0.72</v>
+          <t xml:space="preserve">755-KTR03EZPF3403</t>
+        </is>
+      </c>
+      <c r="P84" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0.19</v>
       </c>
       <c r="R84">
-        <v>87087</v>
+        <v>13778</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -9164,86 +9133,78 @@
         <v>1</v>
       </c>
       <c r="U84">
-        <v>6</v>
-      </c>
-      <c r="V84">
-        <v>0.36</v>
-      </c>
-      <c r="W84">
-        <v>2.16</v>
+        <v>3</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0.57</v>
       </c>
       <c r="X84">
-        <v>8.06</v>
-      </c>
-      <c r="Y84">
-        <v>0.1741</v>
-      </c>
-      <c r="Z84">
-        <v>2.3341</v>
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">R43</t>
+          <t xml:space="preserve">RESET1,TRGT_PWR_ON1</t>
         </is>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3</t>
+          <t xml:space="preserve">PTS645</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRCW06033R32FKTA</t>
+          <t xml:space="preserve">PTS645SK43SMTR92-LFS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vishay</t>
+          <t xml:space="preserve">C&amp;K Switches</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0603</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.vishay.com/docs/20008/dcrcw.pdf</t>
+          <t xml:space="preserve">MyFootprints:SWITCH_43SMTR92LFS</t>
+        </is>
+      </c>
+      <c r="G85"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PTS645SM43SMTR92LFS</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06033R32FKTA?qs=oycmPmJ%2FEmljaarH4ntLEQ%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/CK/PTS645SK43SMTR92-LFS?qs=Imq1NPwxi76wjUe7hzmA%252BA%3D%3D&amp;mgh=1</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
+          <t xml:space="preserve">PTS645</t>
+        </is>
+      </c>
+      <c r="K85"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">No - RoHS Version Available</t>
+          <t xml:space="preserve">Details</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">United States</t>
+          <t xml:space="preserve">China</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9253,17 +9214,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">71-CRCW0603-3.32</t>
-        </is>
-      </c>
-      <c r="P85">
-        <v>0.29</v>
-      </c>
-      <c r="Q85">
-        <v>0.29</v>
+          <t xml:space="preserve">611-PTS645SK43SMTR92</t>
+        </is>
+      </c>
+      <c r="P85" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0.72</v>
       </c>
       <c r="R85">
-        <v>2600</v>
+        <v>87087</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -9274,46 +9235,46 @@
         <v>1</v>
       </c>
       <c r="U85">
-        <v>3</v>
-      </c>
-      <c r="V85">
-        <v>0.29</v>
-      </c>
-      <c r="W85">
-        <v>0.87</v>
+        <v>6</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="W85" s="3">
+        <v>2.16</v>
       </c>
       <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>0</v>
-      </c>
-      <c r="Z85">
-        <v>0.87</v>
+        <v>8.06</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0.1741</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>2.3341</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">R6,R21</t>
+          <t xml:space="preserve">R43</t>
         </is>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1M</t>
+          <t xml:space="preserve">3.3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRG0603F1M0-10</t>
+          <t xml:space="preserve">CRCW06033R32FKTA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">TE Connectivity Holsworthy</t>
+          <t xml:space="preserve">Vishay</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9328,17 +9289,17 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=1622877&amp;DocType=Customer+Drawing&amp;DocLang=English&amp;PartCntxt=1622877-2</t>
+          <t xml:space="preserve">https://www.vishay.com/docs/20008/dcrcw.pdf</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/TE-Connectivity-Holsworthy/CRG0603F1M0-10?qs=s1WWODT2SXVmMRw54xD%2FMg%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Vishay/CRCW06033R32FKTA?qs=oycmPmJ%2FEmljaarH4ntLEQ%3D%3D</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
+          <t xml:space="preserve">Resistor</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -9348,12 +9309,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Details</t>
+          <t xml:space="preserve">No - RoHS Version Available</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thailand</t>
+          <t xml:space="preserve">United States</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9363,17 +9324,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">279-CRG0603F1M0/10</t>
-        </is>
-      </c>
-      <c r="P86">
-        <v>0.24</v>
-      </c>
-      <c r="Q86">
-        <v>0.48</v>
+          <t xml:space="preserve">71-CRCW0603-3.32</t>
+        </is>
+      </c>
+      <c r="P86" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0.29</v>
       </c>
       <c r="R86">
-        <v>18188</v>
+        <v>2600</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -9384,71 +9345,71 @@
         <v>1</v>
       </c>
       <c r="U86">
-        <v>10</v>
-      </c>
-      <c r="V86">
-        <v>0.06</v>
-      </c>
-      <c r="W86">
-        <v>0.6</v>
+        <v>3</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0.87</v>
       </c>
       <c r="X86">
         <v>0</v>
       </c>
-      <c r="Y86">
+      <c r="Y86" s="3">
         <v>0</v>
       </c>
-      <c r="Z86">
-        <v>0.6</v>
+      <c r="Z86" s="3">
+        <v>0.87</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">FB1</t>
+          <t xml:space="preserve">R6,R21</t>
         </is>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">1M</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">742792022</t>
+          <t xml:space="preserve">CRG0603F1M0-10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wurth Elektronik</t>
+          <t xml:space="preserve">TE Connectivity Holsworthy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inductor_SMD:L_0603_1608Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805 (2012 metric)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/742792022.pdf</t>
+          <t xml:space="preserve">https://www.te.com/commerce/DocumentDelivery/DDEController?Action=srchrtrv&amp;DocNm=1622877&amp;DocType=Customer+Drawing&amp;DocLang=English&amp;PartCntxt=1622877-2</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/742792022?qs=5twSNpOB8IBksnQcn3fDWA%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/TE-Connectivity-Holsworthy/CRG0603F1M0-10?qs=s1WWODT2SXVmMRw54xD%2FMg%3D%3D</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ferrite bead, small symbol</t>
+          <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9463,7 +9424,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taiwan</t>
+          <t xml:space="preserve">Thailand</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9473,17 +9434,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-742792022</t>
-        </is>
-      </c>
-      <c r="P87">
-        <v>0.16</v>
-      </c>
-      <c r="Q87">
-        <v>0.16</v>
+          <t xml:space="preserve">279-CRG0603F1M0/10</t>
+        </is>
+      </c>
+      <c r="P87" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0.48</v>
       </c>
       <c r="R87">
-        <v>145687</v>
+        <v>18188</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -9494,28 +9455,28 @@
         <v>1</v>
       </c>
       <c r="U87">
-        <v>3</v>
-      </c>
-      <c r="V87">
-        <v>0.16</v>
-      </c>
-      <c r="W87">
-        <v>0.48</v>
+        <v>10</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0.6</v>
       </c>
       <c r="X87">
         <v>0</v>
       </c>
-      <c r="Y87">
+      <c r="Y87" s="3">
         <v>0</v>
       </c>
-      <c r="Z87">
-        <v>0.48</v>
+      <c r="Z87" s="3">
+        <v>0.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">R5</t>
+          <t xml:space="preserve">FB1</t>
         </is>
       </c>
       <c r="B88">
@@ -9523,12 +9484,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.13k</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">560112116151</t>
+          <t xml:space="preserve">742792022</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9538,27 +9499,27 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
+          <t xml:space="preserve">Inductor_SMD:L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603</t>
+          <t xml:space="preserve">0805</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116151.pdf</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/742792022.pdf</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116151?qs=sGAEpiMZZMtG0KNrPCHnjRpfexHZHoPIOe63Hq9ISdAfX3qbuXrk3g%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/742792022?qs=5twSNpOB8IBksnQcn3fDWA%3D%3D</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistor, small symbol</t>
+          <t xml:space="preserve">Ferrite bead, small symbol</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9583,17 +9544,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve">710-560112116151</t>
-        </is>
-      </c>
-      <c r="P88">
-        <v>0.11</v>
-      </c>
-      <c r="Q88">
-        <v>0.11</v>
+          <t xml:space="preserve">710-742792022</t>
+        </is>
+      </c>
+      <c r="P88" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0.16</v>
       </c>
       <c r="R88">
-        <v>9795</v>
+        <v>145687</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -9606,69 +9567,69 @@
       <c r="U88">
         <v>3</v>
       </c>
-      <c r="V88">
-        <v>0.11</v>
-      </c>
-      <c r="W88">
-        <v>0.33</v>
+      <c r="V88" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0.48</v>
       </c>
       <c r="X88">
         <v>0</v>
       </c>
-      <c r="Y88">
+      <c r="Y88" s="3">
         <v>0</v>
       </c>
-      <c r="Z88">
-        <v>0.33</v>
+      <c r="Z88" s="3">
+        <v>0.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7,C9,C18,C30,C31,C70,C72,C75,C76,C77,C78,C80,C81,C82</t>
+          <t xml:space="preserve">R5</t>
         </is>
       </c>
       <c r="B89">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1uF</t>
+          <t xml:space="preserve">1.13k</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">CL10A105KB8NNNC</t>
+          <t xml:space="preserve">560112116151</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samsung</t>
+          <t xml:space="preserve">Wurth Elektronik</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capacitor_SMD:C_0603_1608Metric</t>
+          <t xml:space="preserve">Resistor_SMD:R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">0603 (1608 metric)</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL10A105KB8NNN</t>
+          <t xml:space="preserve">https://www.we-online.com/components/products/datasheet/560112116151.pdf</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Samsung-Electro-Mechanics/CL10A105KB8NNNC?qs=ktYoCbbtCSJz4pFCLWXd5g%3D%3D</t>
+          <t xml:space="preserve">https://www.mouser.com/en/ProductDetail/Wurth-Elektronik/560112116151?qs=sGAEpiMZZMtG0KNrPCHnjRpfexHZHoPIOe63Hq9ISdAfX3qbuXrk3g%3D%3D</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacitor, small US symbol</t>
+          <t xml:space="preserve">Resistor, small symbol</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9683,7 +9644,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines</t>
+          <t xml:space="preserve">Taiwan</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9693,43 +9654,81 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve">187-CL10A105KB8NNNC</t>
-        </is>
-      </c>
-      <c r="P89">
+          <t xml:space="preserve">710-560112116151</t>
+        </is>
+      </c>
+      <c r="P89" s="3">
         <v>0.11</v>
       </c>
-      <c r="Q89">
-        <v>1.54</v>
+      <c r="Q89" s="3">
+        <v>0.11</v>
       </c>
       <c r="R89">
+        <v>9795</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active</t>
+        </is>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0.33</v>
+      </c>
+      <c r="X89">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Active</t>
-        </is>
-      </c>
-      <c r="T89">
-        <v>1</v>
-      </c>
-      <c r="U89">
-        <v>42</v>
-      </c>
-      <c r="V89">
-        <v>0.044</v>
-      </c>
-      <c r="W89">
-        <v>1.848</v>
-      </c>
-      <c r="X89">
-        <v>8.18</v>
-      </c>
-      <c r="Y89">
-        <v>0.1512</v>
-      </c>
-      <c r="Z89">
-        <v>1.9992</v>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
+      <c r="L90"/>
+      <c r="M90"/>
+      <c r="N90"/>
+      <c r="O90"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90"/>
+      <c r="S90"/>
+      <c r="T90"/>
+      <c r="U90"/>
+      <c r="V90"/>
+      <c r="W90" s="4">
+        <v>886.825</v>
+      </c>
+      <c r="X90"/>
+      <c r="Y90" s="4">
+        <v>57.8504</v>
+      </c>
+      <c r="Z90" s="4">
+        <v>944.6754</v>
       </c>
     </row>
   </sheetData>
@@ -9797,8 +9796,8 @@
     <hyperlink ref="I31" r:id="rId60"/>
     <hyperlink ref="H32" r:id="rId61"/>
     <hyperlink ref="I32" r:id="rId62"/>
-    <hyperlink ref="I33" r:id="rId63"/>
-    <hyperlink ref="H34" r:id="rId64"/>
+    <hyperlink ref="H33" r:id="rId63"/>
+    <hyperlink ref="I33" r:id="rId64"/>
     <hyperlink ref="I34" r:id="rId65"/>
     <hyperlink ref="H35" r:id="rId66"/>
     <hyperlink ref="I35" r:id="rId67"/>
@@ -9898,8 +9897,8 @@
     <hyperlink ref="I82" r:id="rId161"/>
     <hyperlink ref="H83" r:id="rId162"/>
     <hyperlink ref="I83" r:id="rId163"/>
-    <hyperlink ref="I84" r:id="rId164"/>
-    <hyperlink ref="H85" r:id="rId165"/>
+    <hyperlink ref="H84" r:id="rId164"/>
+    <hyperlink ref="I84" r:id="rId165"/>
     <hyperlink ref="I85" r:id="rId166"/>
     <hyperlink ref="H86" r:id="rId167"/>
     <hyperlink ref="I86" r:id="rId168"/>

--- a/docs/FINALE_SAUCE_BOM.xlsx
+++ b/docs/FINALE_SAUCE_BOM.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -299,6 +300,7 @@
         <v>0.1</v>
       </c>
       <c r="Q2" s="3">
+        <f>P2*B2</f>
         <v>0.1</v>
       </c>
       <c r="R2">
@@ -319,15 +321,18 @@
         <v>0.016</v>
       </c>
       <c r="W2" s="3">
+        <f>V2*U2</f>
         <v>0.16</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2" s="3">
+        <f>W2*X2/100</f>
         <v>0</v>
       </c>
       <c r="Z2" s="3">
+        <f>W2+Y2</f>
         <v>0.16</v>
       </c>
     </row>
@@ -409,6 +414,7 @@
         <v>0.11</v>
       </c>
       <c r="Q3" s="3">
+        <f>P3*B3</f>
         <v>0.44</v>
       </c>
       <c r="R3">
@@ -420,7 +426,7 @@
         </is>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U3">
         <v>12</v>
@@ -429,15 +435,18 @@
         <v>0.102</v>
       </c>
       <c r="W3" s="3">
+        <f>V3*U3</f>
         <v>1.224</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3" s="3">
+        <f>W3*X3/100</f>
         <v>0</v>
       </c>
       <c r="Z3" s="3">
+        <f>W3+Y3</f>
         <v>1.224</v>
       </c>
     </row>
@@ -519,6 +528,7 @@
         <v>0.1</v>
       </c>
       <c r="Q4" s="3">
+        <f>P4*B4</f>
         <v>6</v>
       </c>
       <c r="R4">
@@ -530,7 +540,7 @@
         </is>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="U4">
         <v>180</v>
@@ -539,15 +549,18 @@
         <v>0.01</v>
       </c>
       <c r="W4" s="3">
+        <f>V4*U4</f>
         <v>1.8</v>
       </c>
       <c r="X4">
         <v>8</v>
       </c>
       <c r="Y4" s="3">
+        <f>W4*X4/100</f>
         <v>0.144</v>
       </c>
       <c r="Z4" s="3">
+        <f>W4+Y4</f>
         <v>1.944</v>
       </c>
     </row>
@@ -629,6 +642,7 @@
         <v>0.1</v>
       </c>
       <c r="Q5" s="3">
+        <f>P5*B5</f>
         <v>0.1</v>
       </c>
       <c r="R5">
@@ -649,15 +663,18 @@
         <v>0.025</v>
       </c>
       <c r="W5" s="3">
+        <f>V5*U5</f>
         <v>0.25</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5" s="3">
+        <f>W5*X5/100</f>
         <v>0.025</v>
       </c>
       <c r="Z5" s="3">
+        <f>W5+Y5</f>
         <v>0.275</v>
       </c>
     </row>
@@ -735,6 +752,7 @@
         <v>0.14</v>
       </c>
       <c r="Q6" s="3">
+        <f>P6*B6</f>
         <v>0.56</v>
       </c>
       <c r="R6">
@@ -746,7 +764,7 @@
         </is>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U6">
         <v>12</v>
@@ -755,15 +773,18 @@
         <v>0.092</v>
       </c>
       <c r="W6" s="3">
+        <f>V6*U6</f>
         <v>1.104</v>
       </c>
       <c r="X6">
         <v>37.86</v>
       </c>
       <c r="Y6" s="3">
+        <f>W6*X6/100</f>
         <v>0.418</v>
       </c>
       <c r="Z6" s="3">
+        <f>W6+Y6</f>
         <v>1.522</v>
       </c>
     </row>
@@ -841,6 +862,7 @@
         <v>0.6</v>
       </c>
       <c r="Q7" s="3">
+        <f>P7*B7</f>
         <v>0.6</v>
       </c>
       <c r="R7">
@@ -861,15 +883,18 @@
         <v>0.6</v>
       </c>
       <c r="W7" s="3">
+        <f>V7*U7</f>
         <v>1.8</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7" s="3">
+        <f>W7*X7/100</f>
         <v>0.144</v>
       </c>
       <c r="Z7" s="3">
+        <f>W7+Y7</f>
         <v>1.944</v>
       </c>
     </row>
@@ -951,6 +976,7 @@
         <v>0.1</v>
       </c>
       <c r="Q8" s="3">
+        <f>P8*B8</f>
         <v>0.2</v>
       </c>
       <c r="R8">
@@ -962,7 +988,7 @@
         </is>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -971,15 +997,18 @@
         <v>0.012</v>
       </c>
       <c r="W8" s="3">
+        <f>V8*U8</f>
         <v>0.12</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8" s="3">
+        <f>W8*X8/100</f>
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <f>W8+Y8</f>
         <v>0.12</v>
       </c>
     </row>
@@ -1057,6 +1086,7 @@
         <v>0.52</v>
       </c>
       <c r="Q9" s="3">
+        <f>P9*B9</f>
         <v>3.64</v>
       </c>
       <c r="R9">
@@ -1068,7 +1098,7 @@
         </is>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>21</v>
@@ -1077,15 +1107,18 @@
         <v>0.367</v>
       </c>
       <c r="W9" s="3">
+        <f>V9*U9</f>
         <v>7.707</v>
       </c>
       <c r="X9">
         <v>0</v>
       </c>
       <c r="Y9" s="3">
+        <f>W9*X9/100</f>
         <v>0</v>
       </c>
       <c r="Z9" s="3">
+        <f>W9+Y9</f>
         <v>7.707</v>
       </c>
     </row>
@@ -1163,6 +1196,7 @@
         <v>1.09</v>
       </c>
       <c r="Q10" s="3">
+        <f>P10*B10</f>
         <v>1.09</v>
       </c>
       <c r="R10">
@@ -1183,15 +1217,18 @@
         <v>1.09</v>
       </c>
       <c r="W10" s="3">
+        <f>V10*U10</f>
         <v>3.27</v>
       </c>
       <c r="X10">
         <v>7.98</v>
       </c>
       <c r="Y10" s="3">
+        <f>W10*X10/100</f>
         <v>0.2609</v>
       </c>
       <c r="Z10" s="3">
+        <f>W10+Y10</f>
         <v>3.5309</v>
       </c>
     </row>
@@ -1273,6 +1310,7 @@
         <v>0.46</v>
       </c>
       <c r="Q11" s="3">
+        <f>P11*B11</f>
         <v>2.3</v>
       </c>
       <c r="R11">
@@ -1284,7 +1322,7 @@
         </is>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>15</v>
@@ -1293,15 +1331,18 @@
         <v>0.306</v>
       </c>
       <c r="W11" s="3">
+        <f>V11*U11</f>
         <v>4.59</v>
       </c>
       <c r="X11">
         <v>8.04</v>
       </c>
       <c r="Y11" s="3">
+        <f>W11*X11/100</f>
         <v>0.369</v>
       </c>
       <c r="Z11" s="3">
+        <f>W11+Y11</f>
         <v>4.959</v>
       </c>
     </row>
@@ -1379,6 +1420,7 @@
         <v>3.19</v>
       </c>
       <c r="Q12" s="3">
+        <f>P12*B12</f>
         <v>3.19</v>
       </c>
       <c r="R12">
@@ -1399,15 +1441,18 @@
         <v>3.19</v>
       </c>
       <c r="W12" s="3">
+        <f>V12*U12</f>
         <v>9.57</v>
       </c>
       <c r="X12">
         <v>37.93</v>
       </c>
       <c r="Y12" s="3">
+        <f>W12*X12/100</f>
         <v>3.6299</v>
       </c>
       <c r="Z12" s="3">
+        <f>W12+Y12</f>
         <v>13.1999</v>
       </c>
     </row>
@@ -1489,6 +1534,7 @@
         <v>0.15</v>
       </c>
       <c r="Q13" s="3">
+        <f>P13*B13</f>
         <v>0.15</v>
       </c>
       <c r="R13">
@@ -1509,15 +1555,18 @@
         <v>0.15</v>
       </c>
       <c r="W13" s="3">
+        <f>V13*U13</f>
         <v>0.45</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="Y13" s="3">
+        <f>W13*X13/100</f>
         <v>0</v>
       </c>
       <c r="Z13" s="3">
+        <f>W13+Y13</f>
         <v>0.45</v>
       </c>
     </row>
@@ -1599,6 +1648,7 @@
         <v>0.11</v>
       </c>
       <c r="Q14" s="3">
+        <f>P14*B14</f>
         <v>0.88</v>
       </c>
       <c r="R14">
@@ -1610,7 +1660,7 @@
         </is>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>24</v>
@@ -1619,15 +1669,18 @@
         <v>0.102</v>
       </c>
       <c r="W14" s="3">
+        <f>V14*U14</f>
         <v>2.448</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <f>W14*X14/100</f>
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <f>W14+Y14</f>
         <v>2.448</v>
       </c>
     </row>
@@ -1709,6 +1762,7 @@
         <v>0.1</v>
       </c>
       <c r="Q15" s="3">
+        <f>P15*B15</f>
         <v>0.4</v>
       </c>
       <c r="R15">
@@ -1720,7 +1774,7 @@
         </is>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U15">
         <v>12</v>
@@ -1729,15 +1783,18 @@
         <v>0.033</v>
       </c>
       <c r="W15" s="3">
+        <f>V15*U15</f>
         <v>0.396</v>
       </c>
       <c r="X15">
         <v>8</v>
       </c>
       <c r="Y15" s="3">
+        <f>W15*X15/100</f>
         <v>0.0317</v>
       </c>
       <c r="Z15" s="3">
+        <f>W15+Y15</f>
         <v>0.4277</v>
       </c>
     </row>
@@ -1819,6 +1876,7 @@
         <v>0.1</v>
       </c>
       <c r="Q16" s="3">
+        <f>P16*B16</f>
         <v>0.1</v>
       </c>
       <c r="R16">
@@ -1839,15 +1897,18 @@
         <v>0.012</v>
       </c>
       <c r="W16" s="3">
+        <f>V16*U16</f>
         <v>0.12</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16" s="3">
+        <f>W16*X16/100</f>
         <v>0</v>
       </c>
       <c r="Z16" s="3">
+        <f>W16+Y16</f>
         <v>0.12</v>
       </c>
     </row>
@@ -1925,6 +1986,7 @@
         <v>2.73</v>
       </c>
       <c r="Q17" s="3">
+        <f>P17*B17</f>
         <v>2.73</v>
       </c>
       <c r="R17">
@@ -1945,15 +2007,18 @@
         <v>2.73</v>
       </c>
       <c r="W17" s="3">
+        <f>V17*U17</f>
         <v>8.19</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17" s="3">
+        <f>W17*X17/100</f>
         <v>0</v>
       </c>
       <c r="Z17" s="3">
+        <f>W17+Y17</f>
         <v>8.19</v>
       </c>
     </row>
@@ -2027,6 +2092,7 @@
         <v>0.39</v>
       </c>
       <c r="Q18" s="3">
+        <f>P18*B18</f>
         <v>3.12</v>
       </c>
       <c r="R18">
@@ -2038,7 +2104,7 @@
         </is>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>25</v>
@@ -2047,15 +2113,18 @@
         <v>0.28</v>
       </c>
       <c r="W18" s="3">
+        <f>V18*U18</f>
         <v>7</v>
       </c>
       <c r="X18">
         <v>0</v>
       </c>
       <c r="Y18" s="3">
+        <f>W18*X18/100</f>
         <v>0</v>
       </c>
       <c r="Z18" s="3">
+        <f>W18+Y18</f>
         <v>7</v>
       </c>
     </row>
@@ -2137,6 +2206,7 @@
         <v>0.1</v>
       </c>
       <c r="Q19" s="3">
+        <f>P19*B19</f>
         <v>0.2</v>
       </c>
       <c r="R19">
@@ -2148,7 +2218,7 @@
         </is>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2157,15 +2227,18 @@
         <v>0.015</v>
       </c>
       <c r="W19" s="3">
+        <f>V19*U19</f>
         <v>0.15</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19" s="3">
+        <f>W19*X19/100</f>
         <v>0.012</v>
       </c>
       <c r="Z19" s="3">
+        <f>W19+Y19</f>
         <v>0.162</v>
       </c>
     </row>
@@ -2247,6 +2320,7 @@
         <v>0.31</v>
       </c>
       <c r="Q20" s="3">
+        <f>P20*B20</f>
         <v>0.31</v>
       </c>
       <c r="R20">
@@ -2267,15 +2341,18 @@
         <v>0.31</v>
       </c>
       <c r="W20" s="3">
+        <f>V20*U20</f>
         <v>0.93</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <f>W20*X20/100</f>
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <f>W20+Y20</f>
         <v>0.93</v>
       </c>
     </row>
@@ -2357,6 +2434,7 @@
         <v>0.25</v>
       </c>
       <c r="Q21" s="3">
+        <f>P21*B21</f>
         <v>0.25</v>
       </c>
       <c r="R21">
@@ -2377,15 +2455,18 @@
         <v>0.063</v>
       </c>
       <c r="W21" s="3">
+        <f>V21*U21</f>
         <v>0.63</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21" s="3">
+        <f>W21*X21/100</f>
         <v>0</v>
       </c>
       <c r="Z21" s="3">
+        <f>W21+Y21</f>
         <v>0.63</v>
       </c>
     </row>
@@ -2463,6 +2544,7 @@
         <v>1.68</v>
       </c>
       <c r="Q22" s="3">
+        <f>P22*B22</f>
         <v>1.68</v>
       </c>
       <c r="R22">
@@ -2483,15 +2565,18 @@
         <v>1.68</v>
       </c>
       <c r="W22" s="3">
+        <f>V22*U22</f>
         <v>5.04</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <f>W22*X22/100</f>
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <f>W22+Y22</f>
         <v>5.04</v>
       </c>
     </row>
@@ -2573,6 +2658,7 @@
         <v>0.13</v>
       </c>
       <c r="Q23" s="3">
+        <f>P23*B23</f>
         <v>0.13</v>
       </c>
       <c r="R23">
@@ -2593,15 +2679,18 @@
         <v>0.033</v>
       </c>
       <c r="W23" s="3">
+        <f>V23*U23</f>
         <v>0.33</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
       <c r="Y23" s="3">
+        <f>W23*X23/100</f>
         <v>0</v>
       </c>
       <c r="Z23" s="3">
+        <f>W23+Y23</f>
         <v>0.33</v>
       </c>
     </row>
@@ -2683,6 +2772,7 @@
         <v>0.31</v>
       </c>
       <c r="Q24" s="3">
+        <f>P24*B24</f>
         <v>0.62</v>
       </c>
       <c r="R24">
@@ -2694,7 +2784,7 @@
         </is>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2703,15 +2793,18 @@
         <v>0.135</v>
       </c>
       <c r="W24" s="3">
+        <f>V24*U24</f>
         <v>1.35</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24" s="3">
+        <f>W24*X24/100</f>
         <v>0.135</v>
       </c>
       <c r="Z24" s="3">
+        <f>W24+Y24</f>
         <v>1.485</v>
       </c>
     </row>
@@ -2789,6 +2882,7 @@
         <v>0.76</v>
       </c>
       <c r="Q25" s="3">
+        <f>P25*B25</f>
         <v>1.52</v>
       </c>
       <c r="R25">
@@ -2800,7 +2894,7 @@
         </is>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25">
         <v>6</v>
@@ -2809,15 +2903,18 @@
         <v>0.76</v>
       </c>
       <c r="W25" s="3">
+        <f>V25*U25</f>
         <v>4.56</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25" s="3">
+        <f>W25*X25/100</f>
         <v>0</v>
       </c>
       <c r="Z25" s="3">
+        <f>W25+Y25</f>
         <v>4.56</v>
       </c>
     </row>
@@ -2895,6 +2992,7 @@
         <v>0.93</v>
       </c>
       <c r="Q26" s="3">
+        <f>P26*B26</f>
         <v>0.93</v>
       </c>
       <c r="R26">
@@ -2915,15 +3013,18 @@
         <v>0.93</v>
       </c>
       <c r="W26" s="3">
+        <f>V26*U26</f>
         <v>2.79</v>
       </c>
       <c r="X26">
         <v>30</v>
       </c>
       <c r="Y26" s="3">
+        <f>W26*X26/100</f>
         <v>0.837</v>
       </c>
       <c r="Z26" s="3">
+        <f>W26+Y26</f>
         <v>3.627</v>
       </c>
     </row>
@@ -3005,6 +3106,7 @@
         <v>0.65</v>
       </c>
       <c r="Q27" s="3">
+        <f>P27*B27</f>
         <v>5.2</v>
       </c>
       <c r="R27">
@@ -3016,7 +3118,7 @@
         </is>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>24</v>
@@ -3025,15 +3127,18 @@
         <v>0.431</v>
       </c>
       <c r="W27" s="3">
+        <f>V27*U27</f>
         <v>10.344</v>
       </c>
       <c r="X27">
         <v>8</v>
       </c>
       <c r="Y27" s="3">
+        <f>W27*X27/100</f>
         <v>0.8275</v>
       </c>
       <c r="Z27" s="3">
+        <f>W27+Y27</f>
         <v>11.1715</v>
       </c>
     </row>
@@ -3115,6 +3220,7 @@
         <v>0.23</v>
       </c>
       <c r="Q28" s="3">
+        <f>P28*B28</f>
         <v>7.82</v>
       </c>
       <c r="R28">
@@ -3126,7 +3232,7 @@
         </is>
       </c>
       <c r="T28">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="U28">
         <v>102</v>
@@ -3135,15 +3241,18 @@
         <v>0.072</v>
       </c>
       <c r="W28" s="3">
+        <f>V28*U28</f>
         <v>7.344</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28" s="3">
+        <f>W28*X28/100</f>
         <v>0</v>
       </c>
       <c r="Z28" s="3">
+        <f>W28+Y28</f>
         <v>7.344</v>
       </c>
     </row>
@@ -3221,6 +3330,7 @@
         <v>4.05</v>
       </c>
       <c r="Q29" s="3">
+        <f>P29*B29</f>
         <v>4.05</v>
       </c>
       <c r="R29">
@@ -3241,15 +3351,18 @@
         <v>4.05</v>
       </c>
       <c r="W29" s="3">
+        <f>V29*U29</f>
         <v>12.15</v>
       </c>
       <c r="X29">
         <v>35.06</v>
       </c>
       <c r="Y29" s="3">
+        <f>W29*X29/100</f>
         <v>4.2598</v>
       </c>
       <c r="Z29" s="3">
+        <f>W29+Y29</f>
         <v>16.4098</v>
       </c>
     </row>
@@ -3331,6 +3444,7 @@
         <v>0.13</v>
       </c>
       <c r="Q30" s="3">
+        <f>P30*B30</f>
         <v>0.13</v>
       </c>
       <c r="R30">
@@ -3351,15 +3465,18 @@
         <v>0.033</v>
       </c>
       <c r="W30" s="3">
+        <f>V30*U30</f>
         <v>0.33</v>
       </c>
       <c r="X30">
         <v>0</v>
       </c>
       <c r="Y30" s="3">
+        <f>W30*X30/100</f>
         <v>0</v>
       </c>
       <c r="Z30" s="3">
+        <f>W30+Y30</f>
         <v>0.33</v>
       </c>
     </row>
@@ -3437,6 +3554,7 @@
         <v>1.43</v>
       </c>
       <c r="Q31" s="3">
+        <f>P31*B31</f>
         <v>1.43</v>
       </c>
       <c r="R31">
@@ -3457,15 +3575,18 @@
         <v>1.43</v>
       </c>
       <c r="W31" s="3">
+        <f>V31*U31</f>
         <v>4.29</v>
       </c>
       <c r="X31">
         <v>0</v>
       </c>
       <c r="Y31" s="3">
+        <f>W31*X31/100</f>
         <v>0</v>
       </c>
       <c r="Z31" s="3">
+        <f>W31+Y31</f>
         <v>4.29</v>
       </c>
     </row>
@@ -3539,6 +3660,7 @@
         <v>126.53</v>
       </c>
       <c r="Q32" s="3">
+        <f>P32*B32</f>
         <v>126.53</v>
       </c>
       <c r="R32">
@@ -3559,15 +3681,18 @@
         <v>126.53</v>
       </c>
       <c r="W32" s="3">
+        <f>V32*U32</f>
         <v>379.59</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32" s="3">
+        <f>W32*X32/100</f>
         <v>30.3672</v>
       </c>
       <c r="Z32" s="3">
+        <f>W32+Y32</f>
         <v>409.9572</v>
       </c>
     </row>
@@ -3645,6 +3770,7 @@
         <v>0.16</v>
       </c>
       <c r="Q33" s="3">
+        <f>P33*B33</f>
         <v>0.8</v>
       </c>
       <c r="R33">
@@ -3656,7 +3782,7 @@
         </is>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>15</v>
@@ -3665,15 +3791,18 @@
         <v>0.101</v>
       </c>
       <c r="W33" s="3">
+        <f>V33*U33</f>
         <v>1.515</v>
       </c>
       <c r="X33">
         <v>0</v>
       </c>
       <c r="Y33" s="3">
+        <f>W33*X33/100</f>
         <v>0</v>
       </c>
       <c r="Z33" s="3">
+        <f>W33+Y33</f>
         <v>1.515</v>
       </c>
     </row>
@@ -3747,6 +3876,7 @@
         <v>0.71</v>
       </c>
       <c r="Q34" s="3">
+        <f>P34*B34</f>
         <v>0.71</v>
       </c>
       <c r="R34">
@@ -3767,15 +3897,18 @@
         <v>0.71</v>
       </c>
       <c r="W34" s="3">
+        <f>V34*U34</f>
         <v>2.13</v>
       </c>
       <c r="X34">
         <v>30</v>
       </c>
       <c r="Y34" s="3">
+        <f>W34*X34/100</f>
         <v>0.639</v>
       </c>
       <c r="Z34" s="3">
+        <f>W34+Y34</f>
         <v>2.769</v>
       </c>
     </row>
@@ -3845,6 +3978,7 @@
         <v>19.95</v>
       </c>
       <c r="Q35" s="3">
+        <f>P35*B35</f>
         <v>19.95</v>
       </c>
       <c r="R35"/>
@@ -3863,6 +3997,7 @@
         <v>19.95</v>
       </c>
       <c r="W35" s="3">
+        <f>V35*U35</f>
         <v>59.85</v>
       </c>
       <c r="X35"/>
@@ -3870,6 +4005,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3">
+        <f>W35+Y35</f>
         <v>59.85</v>
       </c>
     </row>
@@ -3943,6 +4079,7 @@
         <v>22.49</v>
       </c>
       <c r="Q36" s="3">
+        <f>P36*B36</f>
         <v>44.98</v>
       </c>
       <c r="R36">
@@ -3954,7 +4091,7 @@
         </is>
       </c>
       <c r="T36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3963,15 +4100,18 @@
         <v>22.49</v>
       </c>
       <c r="W36" s="3">
+        <f>V36*U36</f>
         <v>134.94</v>
       </c>
       <c r="X36">
         <v>6.98</v>
       </c>
       <c r="Y36" s="3">
+        <f>W36*X36/100</f>
         <v>9.4188</v>
       </c>
       <c r="Z36" s="3">
+        <f>W36+Y36</f>
         <v>144.3588</v>
       </c>
     </row>
@@ -4053,6 +4193,7 @@
         <v>0.15</v>
       </c>
       <c r="Q37" s="3">
+        <f>P37*B37</f>
         <v>0.15</v>
       </c>
       <c r="R37">
@@ -4073,15 +4214,18 @@
         <v>0.15</v>
       </c>
       <c r="W37" s="3">
+        <f>V37*U37</f>
         <v>0.45</v>
       </c>
       <c r="X37">
         <v>10</v>
       </c>
       <c r="Y37" s="3">
+        <f>W37*X37/100</f>
         <v>0.045</v>
       </c>
       <c r="Z37" s="3">
+        <f>W37+Y37</f>
         <v>0.495</v>
       </c>
     </row>
@@ -4159,6 +4303,7 @@
         <v>0.43</v>
       </c>
       <c r="Q38" s="3">
+        <f>P38*B38</f>
         <v>1.72</v>
       </c>
       <c r="R38">
@@ -4170,7 +4315,7 @@
         </is>
       </c>
       <c r="T38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U38">
         <v>12</v>
@@ -4179,15 +4324,18 @@
         <v>0.302</v>
       </c>
       <c r="W38" s="3">
+        <f>V38*U38</f>
         <v>3.624</v>
       </c>
       <c r="X38">
         <v>7.91</v>
       </c>
       <c r="Y38" s="3">
+        <f>W38*X38/100</f>
         <v>0.2867</v>
       </c>
       <c r="Z38" s="3">
+        <f>W38+Y38</f>
         <v>3.9107</v>
       </c>
     </row>
@@ -4269,6 +4417,7 @@
         <v>0.11</v>
       </c>
       <c r="Q39" s="3">
+        <f>P39*B39</f>
         <v>0.66</v>
       </c>
       <c r="R39">
@@ -4280,7 +4429,7 @@
         </is>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U39">
         <v>18</v>
@@ -4289,15 +4438,18 @@
         <v>0.102</v>
       </c>
       <c r="W39" s="3">
+        <f>V39*U39</f>
         <v>1.836</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
       <c r="Y39" s="3">
+        <f>W39*X39/100</f>
         <v>0</v>
       </c>
       <c r="Z39" s="3">
+        <f>W39+Y39</f>
         <v>1.836</v>
       </c>
     </row>
@@ -4379,6 +4531,7 @@
         <v>0.23</v>
       </c>
       <c r="Q40" s="3">
+        <f>P40*B40</f>
         <v>3.22</v>
       </c>
       <c r="R40">
@@ -4390,7 +4543,7 @@
         </is>
       </c>
       <c r="T40">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="U40">
         <v>42</v>
@@ -4399,15 +4552,18 @@
         <v>0.096</v>
       </c>
       <c r="W40" s="3">
+        <f>V40*U40</f>
         <v>4.032</v>
       </c>
       <c r="X40">
         <v>7.83</v>
       </c>
       <c r="Y40" s="3">
+        <f>W40*X40/100</f>
         <v>0.3157</v>
       </c>
       <c r="Z40" s="3">
+        <f>W40+Y40</f>
         <v>4.3477</v>
       </c>
     </row>
@@ -4481,6 +4637,7 @@
         <v>0.19</v>
       </c>
       <c r="Q41" s="3">
+        <f>P41*B41</f>
         <v>0.57</v>
       </c>
       <c r="R41">
@@ -4492,7 +4649,7 @@
         </is>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -4501,15 +4658,18 @@
         <v>0.163</v>
       </c>
       <c r="W41" s="3">
+        <f>V41*U41</f>
         <v>1.63</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
       <c r="Y41" s="3">
+        <f>W41*X41/100</f>
         <v>0</v>
       </c>
       <c r="Z41" s="3">
+        <f>W41+Y41</f>
         <v>1.63</v>
       </c>
     </row>
@@ -4591,6 +4751,7 @@
         <v>0.1</v>
       </c>
       <c r="Q42" s="3">
+        <f>P42*B42</f>
         <v>0.1</v>
       </c>
       <c r="R42">
@@ -4611,15 +4772,18 @@
         <v>0.016</v>
       </c>
       <c r="W42" s="3">
+        <f>V42*U42</f>
         <v>0.16</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <f>W42*X42/100</f>
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <f>W42+Y42</f>
         <v>0.16</v>
       </c>
     </row>
@@ -4701,6 +4865,7 @@
         <v>0.28</v>
       </c>
       <c r="Q43" s="3">
+        <f>P43*B43</f>
         <v>0.28</v>
       </c>
       <c r="R43">
@@ -4721,15 +4886,18 @@
         <v>0.28</v>
       </c>
       <c r="W43" s="3">
+        <f>V43*U43</f>
         <v>0.84</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <f>W43*X43/100</f>
         <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <f>W43+Y43</f>
         <v>0.84</v>
       </c>
     </row>
@@ -4811,6 +4979,7 @@
         <v>0.16</v>
       </c>
       <c r="Q44" s="3">
+        <f>P44*B44</f>
         <v>0.16</v>
       </c>
       <c r="R44">
@@ -4831,15 +5000,18 @@
         <v>0.16</v>
       </c>
       <c r="W44" s="3">
+        <f>V44*U44</f>
         <v>0.48</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
       <c r="Y44" s="3">
+        <f>W44*X44/100</f>
         <v>0</v>
       </c>
       <c r="Z44" s="3">
+        <f>W44+Y44</f>
         <v>0.48</v>
       </c>
     </row>
@@ -4917,6 +5089,7 @@
         <v>0.9</v>
       </c>
       <c r="Q45" s="3">
+        <f>P45*B45</f>
         <v>4.5</v>
       </c>
       <c r="R45">
@@ -4928,7 +5101,7 @@
         </is>
       </c>
       <c r="T45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U45">
         <v>15</v>
@@ -4937,15 +5110,18 @@
         <v>0.643</v>
       </c>
       <c r="W45" s="3">
+        <f>V45*U45</f>
         <v>9.645</v>
       </c>
       <c r="X45">
         <v>8</v>
       </c>
       <c r="Y45" s="3">
+        <f>W45*X45/100</f>
         <v>0.7716</v>
       </c>
       <c r="Z45" s="3">
+        <f>W45+Y45</f>
         <v>10.4166</v>
       </c>
     </row>
@@ -5027,6 +5203,7 @@
         <v>0.1</v>
       </c>
       <c r="Q46" s="3">
+        <f>P46*B46</f>
         <v>0.1</v>
       </c>
       <c r="R46">
@@ -5047,15 +5224,18 @@
         <v>0.016</v>
       </c>
       <c r="W46" s="3">
+        <f>V46*U46</f>
         <v>0.16</v>
       </c>
       <c r="X46">
         <v>8</v>
       </c>
       <c r="Y46" s="3">
+        <f>W46*X46/100</f>
         <v>0.0128</v>
       </c>
       <c r="Z46" s="3">
+        <f>W46+Y46</f>
         <v>0.1728</v>
       </c>
     </row>
@@ -5133,6 +5313,7 @@
         <v>0.29</v>
       </c>
       <c r="Q47" s="3">
+        <f>P47*B47</f>
         <v>0.87</v>
       </c>
       <c r="R47">
@@ -5144,7 +5325,7 @@
         </is>
       </c>
       <c r="T47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U47">
         <v>10</v>
@@ -5153,15 +5334,18 @@
         <v>0.195</v>
       </c>
       <c r="W47" s="3">
+        <f>V47*U47</f>
         <v>1.95</v>
       </c>
       <c r="X47">
         <v>7.93</v>
       </c>
       <c r="Y47" s="3">
+        <f>W47*X47/100</f>
         <v>0.1546</v>
       </c>
       <c r="Z47" s="3">
+        <f>W47+Y47</f>
         <v>2.1046</v>
       </c>
     </row>
@@ -5239,6 +5423,7 @@
         <v>1.71</v>
       </c>
       <c r="Q48" s="3">
+        <f>P48*B48</f>
         <v>1.71</v>
       </c>
       <c r="R48">
@@ -5259,15 +5444,18 @@
         <v>1.71</v>
       </c>
       <c r="W48" s="3">
+        <f>V48*U48</f>
         <v>5.13</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48" s="3">
+        <f>W48*X48/100</f>
         <v>0</v>
       </c>
       <c r="Z48" s="3">
+        <f>W48+Y48</f>
         <v>5.13</v>
       </c>
     </row>
@@ -5345,6 +5533,7 @@
         <v>1.38</v>
       </c>
       <c r="Q49" s="3">
+        <f>P49*B49</f>
         <v>2.76</v>
       </c>
       <c r="R49">
@@ -5356,7 +5545,7 @@
         </is>
       </c>
       <c r="T49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49">
         <v>6</v>
@@ -5365,15 +5554,18 @@
         <v>1.38</v>
       </c>
       <c r="W49" s="3">
+        <f>V49*U49</f>
         <v>8.28</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49" s="3">
+        <f>W49*X49/100</f>
         <v>0</v>
       </c>
       <c r="Z49" s="3">
+        <f>W49+Y49</f>
         <v>8.28</v>
       </c>
     </row>
@@ -5455,6 +5647,7 @@
         <v>0.1</v>
       </c>
       <c r="Q50" s="3">
+        <f>P50*B50</f>
         <v>0.4</v>
       </c>
       <c r="R50">
@@ -5466,7 +5659,7 @@
         </is>
       </c>
       <c r="T50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U50">
         <v>12</v>
@@ -5475,15 +5668,18 @@
         <v>0.012</v>
       </c>
       <c r="W50" s="3">
+        <f>V50*U50</f>
         <v>0.144</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50" s="3">
+        <f>W50*X50/100</f>
         <v>0</v>
       </c>
       <c r="Z50" s="3">
+        <f>W50+Y50</f>
         <v>0.144</v>
       </c>
     </row>
@@ -5565,6 +5761,7 @@
         <v>0.39</v>
       </c>
       <c r="Q51" s="3">
+        <f>P51*B51</f>
         <v>0.78</v>
       </c>
       <c r="R51">
@@ -5576,7 +5773,7 @@
         </is>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U51">
         <v>10</v>
@@ -5585,15 +5782,18 @@
         <v>0.17</v>
       </c>
       <c r="W51" s="3">
+        <f>V51*U51</f>
         <v>1.7</v>
       </c>
       <c r="X51">
         <v>7.95</v>
       </c>
       <c r="Y51" s="3">
+        <f>W51*X51/100</f>
         <v>0.1351</v>
       </c>
       <c r="Z51" s="3">
+        <f>W51+Y51</f>
         <v>1.8351</v>
       </c>
     </row>
@@ -5671,6 +5871,7 @@
         <v>0.16</v>
       </c>
       <c r="Q52" s="3">
+        <f>P52*B52</f>
         <v>0.16</v>
       </c>
       <c r="R52">
@@ -5691,15 +5892,18 @@
         <v>0.16</v>
       </c>
       <c r="W52" s="3">
+        <f>V52*U52</f>
         <v>0.48</v>
       </c>
       <c r="X52">
         <v>35</v>
       </c>
       <c r="Y52" s="3">
+        <f>W52*X52/100</f>
         <v>0.168</v>
       </c>
       <c r="Z52" s="3">
+        <f>W52+Y52</f>
         <v>0.648</v>
       </c>
     </row>
@@ -5777,6 +5981,7 @@
         <v>17.13</v>
       </c>
       <c r="Q53" s="3">
+        <f>P53*B53</f>
         <v>17.13</v>
       </c>
       <c r="R53">
@@ -5797,15 +6002,18 @@
         <v>17.13</v>
       </c>
       <c r="W53" s="3">
+        <f>V53*U53</f>
         <v>51.39</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53" s="3">
+        <f>W53*X53/100</f>
         <v>0</v>
       </c>
       <c r="Z53" s="3">
+        <f>W53+Y53</f>
         <v>51.39</v>
       </c>
     </row>
@@ -5879,6 +6087,7 @@
         <v>2.99</v>
       </c>
       <c r="Q54" s="3">
+        <f>P54*B54</f>
         <v>2.99</v>
       </c>
       <c r="R54">
@@ -5899,15 +6108,18 @@
         <v>2.99</v>
       </c>
       <c r="W54" s="3">
+        <f>V54*U54</f>
         <v>8.97</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54" s="3">
+        <f>W54*X54/100</f>
         <v>0</v>
       </c>
       <c r="Z54" s="3">
+        <f>W54+Y54</f>
         <v>8.97</v>
       </c>
     </row>
@@ -5989,6 +6201,7 @@
         <v>0.1</v>
       </c>
       <c r="Q55" s="3">
+        <f>P55*B55</f>
         <v>0.1</v>
       </c>
       <c r="R55">
@@ -6009,15 +6222,18 @@
         <v>0.017</v>
       </c>
       <c r="W55" s="3">
+        <f>V55*U55</f>
         <v>0.17</v>
       </c>
       <c r="X55">
         <v>30</v>
       </c>
       <c r="Y55" s="3">
+        <f>W55*X55/100</f>
         <v>0.051</v>
       </c>
       <c r="Z55" s="3">
+        <f>W55+Y55</f>
         <v>0.221</v>
       </c>
     </row>
@@ -6099,6 +6315,7 @@
         <v>0.23</v>
       </c>
       <c r="Q56" s="3">
+        <f>P56*B56</f>
         <v>0.69</v>
       </c>
       <c r="R56">
@@ -6110,7 +6327,7 @@
         </is>
       </c>
       <c r="T56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U56">
         <v>10</v>
@@ -6119,15 +6336,18 @@
         <v>0.081</v>
       </c>
       <c r="W56" s="3">
+        <f>V56*U56</f>
         <v>0.81</v>
       </c>
       <c r="X56">
         <v>7.83</v>
       </c>
       <c r="Y56" s="3">
+        <f>W56*X56/100</f>
         <v>0.0634</v>
       </c>
       <c r="Z56" s="3">
+        <f>W56+Y56</f>
         <v>0.8734</v>
       </c>
     </row>
@@ -6205,6 +6425,7 @@
         <v>2.75</v>
       </c>
       <c r="Q57" s="3">
+        <f>P57*B57</f>
         <v>2.75</v>
       </c>
       <c r="R57">
@@ -6225,15 +6446,18 @@
         <v>2.75</v>
       </c>
       <c r="W57" s="3">
+        <f>V57*U57</f>
         <v>8.25</v>
       </c>
       <c r="X57">
         <v>0</v>
       </c>
       <c r="Y57" s="3">
+        <f>W57*X57/100</f>
         <v>0</v>
       </c>
       <c r="Z57" s="3">
+        <f>W57+Y57</f>
         <v>8.25</v>
       </c>
     </row>
@@ -6315,6 +6539,7 @@
         <v>0.1</v>
       </c>
       <c r="Q58" s="3">
+        <f>P58*B58</f>
         <v>0.1</v>
       </c>
       <c r="R58">
@@ -6335,15 +6560,18 @@
         <v>0.1</v>
       </c>
       <c r="W58" s="3">
+        <f>V58*U58</f>
         <v>0.3</v>
       </c>
       <c r="X58">
         <v>8</v>
       </c>
       <c r="Y58" s="3">
+        <f>W58*X58/100</f>
         <v>0.024</v>
       </c>
       <c r="Z58" s="3">
+        <f>W58+Y58</f>
         <v>0.324</v>
       </c>
     </row>
@@ -6425,6 +6653,7 @@
         <v>0.1</v>
       </c>
       <c r="Q59" s="3">
+        <f>P59*B59</f>
         <v>0.1</v>
       </c>
       <c r="R59">
@@ -6445,15 +6674,18 @@
         <v>0.021</v>
       </c>
       <c r="W59" s="3">
+        <f>V59*U59</f>
         <v>0.21</v>
       </c>
       <c r="X59">
         <v>8</v>
       </c>
       <c r="Y59" s="3">
+        <f>W59*X59/100</f>
         <v>0.0168</v>
       </c>
       <c r="Z59" s="3">
+        <f>W59+Y59</f>
         <v>0.2268</v>
       </c>
     </row>
@@ -6527,6 +6759,7 @@
         <v>5.75</v>
       </c>
       <c r="Q60" s="3">
+        <f>P60*B60</f>
         <v>11.5</v>
       </c>
       <c r="R60">
@@ -6538,7 +6771,7 @@
         </is>
       </c>
       <c r="T60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U60">
         <v>6</v>
@@ -6547,15 +6780,18 @@
         <v>5.75</v>
       </c>
       <c r="W60" s="3">
+        <f>V60*U60</f>
         <v>34.5</v>
       </c>
       <c r="X60">
         <v>8</v>
       </c>
       <c r="Y60" s="3">
+        <f>W60*X60/100</f>
         <v>2.76</v>
       </c>
       <c r="Z60" s="3">
+        <f>W60+Y60</f>
         <v>37.26</v>
       </c>
     </row>
@@ -6637,6 +6873,7 @@
         <v>0.1</v>
       </c>
       <c r="Q61" s="3">
+        <f>P61*B61</f>
         <v>0.1</v>
       </c>
       <c r="R61">
@@ -6657,15 +6894,18 @@
         <v>0.012</v>
       </c>
       <c r="W61" s="3">
+        <f>V61*U61</f>
         <v>0.12</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <f>W61*X61/100</f>
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <f>W61+Y61</f>
         <v>0.12</v>
       </c>
     </row>
@@ -6739,6 +6979,7 @@
         <v>1.1</v>
       </c>
       <c r="Q62" s="3">
+        <f>P62*B62</f>
         <v>1.1</v>
       </c>
       <c r="R62">
@@ -6759,15 +7000,18 @@
         <v>1.1</v>
       </c>
       <c r="W62" s="3">
+        <f>V62*U62</f>
         <v>3.3</v>
       </c>
       <c r="X62">
         <v>8</v>
       </c>
       <c r="Y62" s="3">
+        <f>W62*X62/100</f>
         <v>0.264</v>
       </c>
       <c r="Z62" s="3">
+        <f>W62+Y62</f>
         <v>3.564</v>
       </c>
     </row>
@@ -6845,6 +7089,7 @@
         <v>2.44</v>
       </c>
       <c r="Q63" s="3">
+        <f>P63*B63</f>
         <v>2.44</v>
       </c>
       <c r="R63">
@@ -6865,15 +7110,18 @@
         <v>2.44</v>
       </c>
       <c r="W63" s="3">
+        <f>V63*U63</f>
         <v>7.32</v>
       </c>
       <c r="X63">
         <v>0</v>
       </c>
       <c r="Y63" s="3">
+        <f>W63*X63/100</f>
         <v>0</v>
       </c>
       <c r="Z63" s="3">
+        <f>W63+Y63</f>
         <v>7.32</v>
       </c>
     </row>
@@ -6955,6 +7203,7 @@
         <v>0.1</v>
       </c>
       <c r="Q64" s="3">
+        <f>P64*B64</f>
         <v>0.1</v>
       </c>
       <c r="R64">
@@ -6975,15 +7224,18 @@
         <v>0.016</v>
       </c>
       <c r="W64" s="3">
+        <f>V64*U64</f>
         <v>0.16</v>
       </c>
       <c r="X64">
         <v>0</v>
       </c>
       <c r="Y64" s="3">
+        <f>W64*X64/100</f>
         <v>0</v>
       </c>
       <c r="Z64" s="3">
+        <f>W64+Y64</f>
         <v>0.16</v>
       </c>
     </row>
@@ -7065,6 +7317,7 @@
         <v>0.1</v>
       </c>
       <c r="Q65" s="3">
+        <f>P65*B65</f>
         <v>0.1</v>
       </c>
       <c r="R65">
@@ -7085,15 +7338,18 @@
         <v>0.013</v>
       </c>
       <c r="W65" s="3">
+        <f>V65*U65</f>
         <v>0.13</v>
       </c>
       <c r="X65">
         <v>10</v>
       </c>
       <c r="Y65" s="3">
+        <f>W65*X65/100</f>
         <v>0.013</v>
       </c>
       <c r="Z65" s="3">
+        <f>W65+Y65</f>
         <v>0.143</v>
       </c>
     </row>
@@ -7175,6 +7431,7 @@
         <v>0.1</v>
       </c>
       <c r="Q66" s="3">
+        <f>P66*B66</f>
         <v>0.1</v>
       </c>
       <c r="R66">
@@ -7195,15 +7452,18 @@
         <v>0.023</v>
       </c>
       <c r="W66" s="3">
+        <f>V66*U66</f>
         <v>0.23</v>
       </c>
       <c r="X66">
         <v>8</v>
       </c>
       <c r="Y66" s="3">
+        <f>W66*X66/100</f>
         <v>0.0184</v>
       </c>
       <c r="Z66" s="3">
+        <f>W66+Y66</f>
         <v>0.2484</v>
       </c>
     </row>
@@ -7285,6 +7545,7 @@
         <v>0.1</v>
       </c>
       <c r="Q67" s="3">
+        <f>P67*B67</f>
         <v>0.1</v>
       </c>
       <c r="R67">
@@ -7305,15 +7566,18 @@
         <v>0.009</v>
       </c>
       <c r="W67" s="3">
+        <f>V67*U67</f>
         <v>0.09</v>
       </c>
       <c r="X67">
         <v>8</v>
       </c>
       <c r="Y67" s="3">
+        <f>W67*X67/100</f>
         <v>0.0072</v>
       </c>
       <c r="Z67" s="3">
+        <f>W67+Y67</f>
         <v>0.0972</v>
       </c>
     </row>
@@ -7391,6 +7655,7 @@
         <v>0.79</v>
       </c>
       <c r="Q68" s="3">
+        <f>P68*B68</f>
         <v>0.79</v>
       </c>
       <c r="R68">
@@ -7411,15 +7676,18 @@
         <v>0.79</v>
       </c>
       <c r="W68" s="3">
+        <f>V68*U68</f>
         <v>2.37</v>
       </c>
       <c r="X68">
         <v>0</v>
       </c>
       <c r="Y68" s="3">
+        <f>W68*X68/100</f>
         <v>0</v>
       </c>
       <c r="Z68" s="3">
+        <f>W68+Y68</f>
         <v>2.37</v>
       </c>
     </row>
@@ -7497,6 +7765,7 @@
         <v>6.99</v>
       </c>
       <c r="Q69" s="3">
+        <f>P69*B69</f>
         <v>6.99</v>
       </c>
       <c r="R69">
@@ -7517,15 +7786,18 @@
         <v>6.99</v>
       </c>
       <c r="W69" s="3">
+        <f>V69*U69</f>
         <v>20.97</v>
       </c>
       <c r="X69">
         <v>0</v>
       </c>
       <c r="Y69" s="3">
+        <f>W69*X69/100</f>
         <v>0</v>
       </c>
       <c r="Z69" s="3">
+        <f>W69+Y69</f>
         <v>20.97</v>
       </c>
     </row>
@@ -7607,6 +7879,7 @@
         <v>0.1</v>
       </c>
       <c r="Q70" s="3">
+        <f>P70*B70</f>
         <v>0.2</v>
       </c>
       <c r="R70">
@@ -7618,7 +7891,7 @@
         </is>
       </c>
       <c r="T70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U70">
         <v>10</v>
@@ -7627,15 +7900,18 @@
         <v>0.012</v>
       </c>
       <c r="W70" s="3">
+        <f>V70*U70</f>
         <v>0.12</v>
       </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <f>W70*X70/100</f>
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <f>W70+Y70</f>
         <v>0.12</v>
       </c>
     </row>
@@ -7713,6 +7989,7 @@
         <v>0.16</v>
       </c>
       <c r="Q71" s="3">
+        <f>P71*B71</f>
         <v>0.16</v>
       </c>
       <c r="R71">
@@ -7733,15 +8010,18 @@
         <v>0.16</v>
       </c>
       <c r="W71" s="3">
+        <f>V71*U71</f>
         <v>0.48</v>
       </c>
       <c r="X71">
         <v>35</v>
       </c>
       <c r="Y71" s="3">
+        <f>W71*X71/100</f>
         <v>0.168</v>
       </c>
       <c r="Z71" s="3">
+        <f>W71+Y71</f>
         <v>0.648</v>
       </c>
     </row>
@@ -7823,6 +8103,7 @@
         <v>0.1</v>
       </c>
       <c r="Q72" s="3">
+        <f>P72*B72</f>
         <v>0.1</v>
       </c>
       <c r="R72">
@@ -7843,15 +8124,18 @@
         <v>0.011</v>
       </c>
       <c r="W72" s="3">
+        <f>V72*U72</f>
         <v>0.11</v>
       </c>
       <c r="X72">
         <v>0</v>
       </c>
       <c r="Y72" s="3">
+        <f>W72*X72/100</f>
         <v>0</v>
       </c>
       <c r="Z72" s="3">
+        <f>W72+Y72</f>
         <v>0.11</v>
       </c>
     </row>
@@ -7929,6 +8213,7 @@
         <v>0.22</v>
       </c>
       <c r="Q73" s="3">
+        <f>P73*B73</f>
         <v>2.64</v>
       </c>
       <c r="R73">
@@ -7940,7 +8225,7 @@
         </is>
       </c>
       <c r="T73">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U73">
         <v>36</v>
@@ -7949,15 +8234,18 @@
         <v>0.131</v>
       </c>
       <c r="W73" s="3">
+        <f>V73*U73</f>
         <v>4.716</v>
       </c>
       <c r="X73">
         <v>0</v>
       </c>
       <c r="Y73" s="3">
+        <f>W73*X73/100</f>
         <v>0</v>
       </c>
       <c r="Z73" s="3">
+        <f>W73+Y73</f>
         <v>4.716</v>
       </c>
     </row>
@@ -8039,6 +8327,7 @@
         <v>0.28</v>
       </c>
       <c r="Q74" s="3">
+        <f>P74*B74</f>
         <v>0.28</v>
       </c>
       <c r="R74">
@@ -8059,15 +8348,18 @@
         <v>0.28</v>
       </c>
       <c r="W74" s="3">
+        <f>V74*U74</f>
         <v>0.84</v>
       </c>
       <c r="X74">
         <v>0</v>
       </c>
       <c r="Y74" s="3">
+        <f>W74*X74/100</f>
         <v>0</v>
       </c>
       <c r="Z74" s="3">
+        <f>W74+Y74</f>
         <v>0.84</v>
       </c>
     </row>
@@ -8149,6 +8441,7 @@
         <v>0.28</v>
       </c>
       <c r="Q75" s="3">
+        <f>P75*B75</f>
         <v>0.28</v>
       </c>
       <c r="R75">
@@ -8169,15 +8462,18 @@
         <v>0.28</v>
       </c>
       <c r="W75" s="3">
+        <f>V75*U75</f>
         <v>0.84</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75" s="3">
+        <f>W75*X75/100</f>
         <v>0</v>
       </c>
       <c r="Z75" s="3">
+        <f>W75+Y75</f>
         <v>0.84</v>
       </c>
     </row>
@@ -8255,6 +8551,7 @@
         <v>0.36</v>
       </c>
       <c r="Q76" s="3">
+        <f>P76*B76</f>
         <v>2.52</v>
       </c>
       <c r="R76">
@@ -8266,7 +8563,7 @@
         </is>
       </c>
       <c r="T76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U76">
         <v>21</v>
@@ -8275,15 +8572,18 @@
         <v>0.246</v>
       </c>
       <c r="W76" s="3">
+        <f>V76*U76</f>
         <v>5.166</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76" s="3">
+        <f>W76*X76/100</f>
         <v>0</v>
       </c>
       <c r="Z76" s="3">
+        <f>W76+Y76</f>
         <v>5.166</v>
       </c>
     </row>
@@ -8365,6 +8665,7 @@
         <v>0.12</v>
       </c>
       <c r="Q77" s="3">
+        <f>P77*B77</f>
         <v>0.12</v>
       </c>
       <c r="R77">
@@ -8385,15 +8686,18 @@
         <v>0.12</v>
       </c>
       <c r="W77" s="3">
+        <f>V77*U77</f>
         <v>0.36</v>
       </c>
       <c r="X77">
         <v>8.33</v>
       </c>
       <c r="Y77" s="3">
+        <f>W77*X77/100</f>
         <v>0.03</v>
       </c>
       <c r="Z77" s="3">
+        <f>W77+Y77</f>
         <v>0.39</v>
       </c>
     </row>
@@ -8471,6 +8775,7 @@
         <v>0.5</v>
       </c>
       <c r="Q78" s="3">
+        <f>P78*B78</f>
         <v>0.5</v>
       </c>
       <c r="R78">
@@ -8491,15 +8796,18 @@
         <v>0.5</v>
       </c>
       <c r="W78" s="3">
+        <f>V78*U78</f>
         <v>1.5</v>
       </c>
       <c r="X78">
         <v>30</v>
       </c>
       <c r="Y78" s="3">
+        <f>W78*X78/100</f>
         <v>0.45</v>
       </c>
       <c r="Z78" s="3">
+        <f>W78+Y78</f>
         <v>1.95</v>
       </c>
     </row>
@@ -8577,6 +8885,7 @@
         <v>0.63</v>
       </c>
       <c r="Q79" s="3">
+        <f>P79*B79</f>
         <v>1.26</v>
       </c>
       <c r="R79">
@@ -8588,7 +8897,7 @@
         </is>
       </c>
       <c r="T79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U79">
         <v>6</v>
@@ -8597,15 +8906,18 @@
         <v>0.63</v>
       </c>
       <c r="W79" s="3">
+        <f>V79*U79</f>
         <v>3.78</v>
       </c>
       <c r="X79">
         <v>0</v>
       </c>
       <c r="Y79" s="3">
+        <f>W79*X79/100</f>
         <v>0</v>
       </c>
       <c r="Z79" s="3">
+        <f>W79+Y79</f>
         <v>3.78</v>
       </c>
     </row>
@@ -8687,6 +8999,7 @@
         <v>0.1</v>
       </c>
       <c r="Q80" s="3">
+        <f>P80*B80</f>
         <v>0.3</v>
       </c>
       <c r="R80">
@@ -8698,7 +9011,7 @@
         </is>
       </c>
       <c r="T80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U80">
         <v>10</v>
@@ -8707,15 +9020,18 @@
         <v>0.029</v>
       </c>
       <c r="W80" s="3">
+        <f>V80*U80</f>
         <v>0.29</v>
       </c>
       <c r="X80">
         <v>0</v>
       </c>
       <c r="Y80" s="3">
+        <f>W80*X80/100</f>
         <v>0</v>
       </c>
       <c r="Z80" s="3">
+        <f>W80+Y80</f>
         <v>0.29</v>
       </c>
     </row>
@@ -8797,6 +9113,7 @@
         <v>0.1</v>
       </c>
       <c r="Q81" s="3">
+        <f>P81*B81</f>
         <v>0.1</v>
       </c>
       <c r="R81">
@@ -8817,15 +9134,18 @@
         <v>0.012</v>
       </c>
       <c r="W81" s="3">
+        <f>V81*U81</f>
         <v>0.12</v>
       </c>
       <c r="X81">
         <v>0</v>
       </c>
       <c r="Y81" s="3">
+        <f>W81*X81/100</f>
         <v>0</v>
       </c>
       <c r="Z81" s="3">
+        <f>W81+Y81</f>
         <v>0.12</v>
       </c>
     </row>
@@ -8899,6 +9219,7 @@
         <v>0.84</v>
       </c>
       <c r="Q82" s="3">
+        <f>P82*B82</f>
         <v>1.68</v>
       </c>
       <c r="R82">
@@ -8910,7 +9231,7 @@
         </is>
       </c>
       <c r="T82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U82">
         <v>6</v>
@@ -8919,15 +9240,18 @@
         <v>0.84</v>
       </c>
       <c r="W82" s="3">
+        <f>V82*U82</f>
         <v>5.04</v>
       </c>
       <c r="X82">
         <v>7.98</v>
       </c>
       <c r="Y82" s="3">
+        <f>W82*X82/100</f>
         <v>0.4022</v>
       </c>
       <c r="Z82" s="3">
+        <f>W82+Y82</f>
         <v>5.4422</v>
       </c>
     </row>
@@ -9009,6 +9333,7 @@
         <v>0.1</v>
       </c>
       <c r="Q83" s="3">
+        <f>P83*B83</f>
         <v>0.1</v>
       </c>
       <c r="R83">
@@ -9029,15 +9354,18 @@
         <v>0.016</v>
       </c>
       <c r="W83" s="3">
+        <f>V83*U83</f>
         <v>0.16</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83" s="3">
+        <f>W83*X83/100</f>
         <v>0</v>
       </c>
       <c r="Z83" s="3">
+        <f>W83+Y83</f>
         <v>0.16</v>
       </c>
     </row>
@@ -9119,6 +9447,7 @@
         <v>0.19</v>
       </c>
       <c r="Q84" s="3">
+        <f>P84*B84</f>
         <v>0.19</v>
       </c>
       <c r="R84">
@@ -9139,15 +9468,18 @@
         <v>0.19</v>
       </c>
       <c r="W84" s="3">
+        <f>V84*U84</f>
         <v>0.57</v>
       </c>
       <c r="X84">
         <v>0</v>
       </c>
       <c r="Y84" s="3">
+        <f>W84*X84/100</f>
         <v>0</v>
       </c>
       <c r="Z84" s="3">
+        <f>W84+Y84</f>
         <v>0.57</v>
       </c>
     </row>
@@ -9221,6 +9553,7 @@
         <v>0.36</v>
       </c>
       <c r="Q85" s="3">
+        <f>P85*B85</f>
         <v>0.72</v>
       </c>
       <c r="R85">
@@ -9232,7 +9565,7 @@
         </is>
       </c>
       <c r="T85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U85">
         <v>6</v>
@@ -9241,15 +9574,18 @@
         <v>0.36</v>
       </c>
       <c r="W85" s="3">
+        <f>V85*U85</f>
         <v>2.16</v>
       </c>
       <c r="X85">
         <v>8.06</v>
       </c>
       <c r="Y85" s="3">
+        <f>W85*X85/100</f>
         <v>0.1741</v>
       </c>
       <c r="Z85" s="3">
+        <f>W85+Y85</f>
         <v>2.3341</v>
       </c>
     </row>
@@ -9331,6 +9667,7 @@
         <v>0.29</v>
       </c>
       <c r="Q86" s="3">
+        <f>P86*B86</f>
         <v>0.29</v>
       </c>
       <c r="R86">
@@ -9351,15 +9688,18 @@
         <v>0.29</v>
       </c>
       <c r="W86" s="3">
+        <f>V86*U86</f>
         <v>0.87</v>
       </c>
       <c r="X86">
         <v>0</v>
       </c>
       <c r="Y86" s="3">
+        <f>W86*X86/100</f>
         <v>0</v>
       </c>
       <c r="Z86" s="3">
+        <f>W86+Y86</f>
         <v>0.87</v>
       </c>
     </row>
@@ -9441,6 +9781,7 @@
         <v>0.24</v>
       </c>
       <c r="Q87" s="3">
+        <f>P87*B87</f>
         <v>0.48</v>
       </c>
       <c r="R87">
@@ -9452,7 +9793,7 @@
         </is>
       </c>
       <c r="T87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U87">
         <v>10</v>
@@ -9461,15 +9802,18 @@
         <v>0.06</v>
       </c>
       <c r="W87" s="3">
+        <f>V87*U87</f>
         <v>0.6</v>
       </c>
       <c r="X87">
         <v>0</v>
       </c>
       <c r="Y87" s="3">
+        <f>W87*X87/100</f>
         <v>0</v>
       </c>
       <c r="Z87" s="3">
+        <f>W87+Y87</f>
         <v>0.6</v>
       </c>
     </row>
@@ -9551,6 +9895,7 @@
         <v>0.16</v>
       </c>
       <c r="Q88" s="3">
+        <f>P88*B88</f>
         <v>0.16</v>
       </c>
       <c r="R88">
@@ -9571,15 +9916,18 @@
         <v>0.16</v>
       </c>
       <c r="W88" s="3">
+        <f>V88*U88</f>
         <v>0.48</v>
       </c>
       <c r="X88">
         <v>0</v>
       </c>
       <c r="Y88" s="3">
+        <f>W88*X88/100</f>
         <v>0</v>
       </c>
       <c r="Z88" s="3">
+        <f>W88+Y88</f>
         <v>0.48</v>
       </c>
     </row>
@@ -9661,6 +10009,7 @@
         <v>0.11</v>
       </c>
       <c r="Q89" s="3">
+        <f>P89*B89</f>
         <v>0.11</v>
       </c>
       <c r="R89">
@@ -9681,15 +10030,18 @@
         <v>0.11</v>
       </c>
       <c r="W89" s="3">
+        <f>V89*U89</f>
         <v>0.33</v>
       </c>
       <c r="X89">
         <v>0</v>
       </c>
       <c r="Y89" s="3">
+        <f>W89*X89/100</f>
         <v>0</v>
       </c>
       <c r="Z89" s="3">
+        <f>W89+Y89</f>
         <v>0.33</v>
       </c>
     </row>
@@ -9721,13 +10073,16 @@
       <c r="U90"/>
       <c r="V90"/>
       <c r="W90" s="4">
+        <f>SUM(W2:W89)</f>
         <v>886.825</v>
       </c>
       <c r="X90"/>
       <c r="Y90" s="4">
+        <f>SUM(Y2:Y89)</f>
         <v>57.8504</v>
       </c>
       <c r="Z90" s="4">
+        <f>SUM(Z2:Z89)</f>
         <v>944.6754</v>
       </c>
     </row>
